--- a/inventaire_bibliotheque.xlsx
+++ b/inventaire_bibliotheque.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="1" r:id="Reb12bd263ff04acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="2" r:id="Reded369017c540c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping_ISBN" sheetId="3" r:id="R4b5f123fbeb147ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal_pipeline" sheetId="4" r:id="Rc8083011ebaa45d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="1" r:id="R3e0ffdc6965a4258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="2" r:id="Re917f57e070c4cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping_ISBN" sheetId="3" r:id="R31185a1c196246b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Journal_pipeline" sheetId="4" r:id="R56a5447a58c34e5b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,9 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="203" formatCode="0.0000"/>
+    <x:numFmt numFmtId="204" formatCode="#,##0 &quot;€&quot;"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -32,7 +35,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +47,11 @@
         <x:fgColor rgb="FF4B3621"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B3A29"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -52,7 +60,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -90,6 +98,29 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -405,9 +436,21 @@
     <x:col min="37" max="37" width="28" hidden="0" customWidth="1"/>
     <x:col min="38" max="38" width="36" hidden="0" customWidth="1"/>
     <x:col min="39" max="39" width="12" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="15" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="19" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="18" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="13" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="13" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="17" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="20" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="20" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="20" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="16" hidden="0" customWidth="1"/>
+    <x:col min="50" max="50" width="14" hidden="0" customWidth="1"/>
+    <x:col min="51" max="51" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="42" customHeight="1">
+    <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>ID</x:v>
       </x:c>
@@ -524,6 +567,42 @@
       </x:c>
       <x:c r="AM1" s="6" t="str">
         <x:v>Publie</x:v>
+      </x:c>
+      <x:c r="AN1" s="21" t="str">
+        <x:v>Nombre_volumes</x:v>
+      </x:c>
+      <x:c r="AO1" s="21" t="str">
+        <x:v>Ville_normalisee</x:v>
+      </x:c>
+      <x:c r="AP1" s="21" t="str">
+        <x:v>Pays_normalise</x:v>
+      </x:c>
+      <x:c r="AQ1" s="21" t="str">
+        <x:v>Latitude</x:v>
+      </x:c>
+      <x:c r="AR1" s="21" t="str">
+        <x:v>Longitude</x:v>
+      </x:c>
+      <x:c r="AS1" s="21" t="str">
+        <x:v>Lieu_incertitude</x:v>
+      </x:c>
+      <x:c r="AT1" s="21" t="str">
+        <x:v>Estimation_basse_EUR</x:v>
+      </x:c>
+      <x:c r="AU1" s="21" t="str">
+        <x:v>Estimation_haute_EUR</x:v>
+      </x:c>
+      <x:c r="AV1" s="21" t="str">
+        <x:v>Interet_patrimonial</x:v>
+      </x:c>
+      <x:c r="AW1" s="21" t="str">
+        <x:v>Completude</x:v>
+      </x:c>
+      <x:c r="AX1" s="21" t="str">
+        <x:v>Illustre</x:v>
+      </x:c>
+      <x:c r="AY1" s="21" t="str">
+        <x:v>Marques_exemplaire</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -620,6 +699,36 @@
       <x:c r="AM2" s="12" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="AN2" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO2" s="22" t="str">
+        <x:v>Paris</x:v>
+      </x:c>
+      <x:c r="AP2" s="22" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="AQ2" s="24" t="n">
+        <x:v>48.8566</x:v>
+      </x:c>
+      <x:c r="AR2" s="24" t="n">
+        <x:v>2.3522</x:v>
+      </x:c>
+      <x:c r="AS2" s="22" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="AT2" s="25"/>
+      <x:c r="AU2" s="25"/>
+      <x:c r="AV2" s="22" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="AW2" s="22" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="AX2" s="22" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="AY2" s="22"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
@@ -711,6 +820,28 @@
       <x:c r="AM3" s="12" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="AN3" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO3" s="22"/>
+      <x:c r="AP3" s="22"/>
+      <x:c r="AQ3" s="24"/>
+      <x:c r="AR3" s="24"/>
+      <x:c r="AS3" s="22" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="AT3" s="25"/>
+      <x:c r="AU3" s="25"/>
+      <x:c r="AV3" s="22" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="AW3" s="22" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="AX3" s="22" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="AY3" s="22"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12"/>
@@ -752,6 +883,18 @@
       <x:c r="AK4" s="12"/>
       <x:c r="AL4" s="12"/>
       <x:c r="AM4" s="12"/>
+      <x:c r="AN4" s="23"/>
+      <x:c r="AO4" s="22"/>
+      <x:c r="AP4" s="22"/>
+      <x:c r="AQ4" s="24"/>
+      <x:c r="AR4" s="24"/>
+      <x:c r="AS4" s="22"/>
+      <x:c r="AT4" s="25"/>
+      <x:c r="AU4" s="25"/>
+      <x:c r="AV4" s="22"/>
+      <x:c r="AW4" s="22"/>
+      <x:c r="AX4" s="22"/>
+      <x:c r="AY4" s="22"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12"/>
@@ -793,6 +936,18 @@
       <x:c r="AK5" s="12"/>
       <x:c r="AL5" s="12"/>
       <x:c r="AM5" s="12"/>
+      <x:c r="AN5" s="23"/>
+      <x:c r="AO5" s="22"/>
+      <x:c r="AP5" s="22"/>
+      <x:c r="AQ5" s="24"/>
+      <x:c r="AR5" s="24"/>
+      <x:c r="AS5" s="22"/>
+      <x:c r="AT5" s="25"/>
+      <x:c r="AU5" s="25"/>
+      <x:c r="AV5" s="22"/>
+      <x:c r="AW5" s="22"/>
+      <x:c r="AX5" s="22"/>
+      <x:c r="AY5" s="22"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12"/>
@@ -834,6 +989,18 @@
       <x:c r="AK6" s="12"/>
       <x:c r="AL6" s="12"/>
       <x:c r="AM6" s="12"/>
+      <x:c r="AN6" s="23"/>
+      <x:c r="AO6" s="22"/>
+      <x:c r="AP6" s="22"/>
+      <x:c r="AQ6" s="24"/>
+      <x:c r="AR6" s="24"/>
+      <x:c r="AS6" s="22"/>
+      <x:c r="AT6" s="25"/>
+      <x:c r="AU6" s="25"/>
+      <x:c r="AV6" s="22"/>
+      <x:c r="AW6" s="22"/>
+      <x:c r="AX6" s="22"/>
+      <x:c r="AY6" s="22"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12"/>
@@ -875,6 +1042,18 @@
       <x:c r="AK7" s="12"/>
       <x:c r="AL7" s="12"/>
       <x:c r="AM7" s="12"/>
+      <x:c r="AN7" s="23"/>
+      <x:c r="AO7" s="22"/>
+      <x:c r="AP7" s="22"/>
+      <x:c r="AQ7" s="24"/>
+      <x:c r="AR7" s="24"/>
+      <x:c r="AS7" s="22"/>
+      <x:c r="AT7" s="25"/>
+      <x:c r="AU7" s="25"/>
+      <x:c r="AV7" s="22"/>
+      <x:c r="AW7" s="22"/>
+      <x:c r="AX7" s="22"/>
+      <x:c r="AY7" s="22"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12"/>
@@ -916,6 +1095,18 @@
       <x:c r="AK8" s="12"/>
       <x:c r="AL8" s="12"/>
       <x:c r="AM8" s="12"/>
+      <x:c r="AN8" s="23"/>
+      <x:c r="AO8" s="22"/>
+      <x:c r="AP8" s="22"/>
+      <x:c r="AQ8" s="24"/>
+      <x:c r="AR8" s="24"/>
+      <x:c r="AS8" s="22"/>
+      <x:c r="AT8" s="25"/>
+      <x:c r="AU8" s="25"/>
+      <x:c r="AV8" s="22"/>
+      <x:c r="AW8" s="22"/>
+      <x:c r="AX8" s="22"/>
+      <x:c r="AY8" s="22"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12"/>
@@ -957,6 +1148,18 @@
       <x:c r="AK9" s="12"/>
       <x:c r="AL9" s="12"/>
       <x:c r="AM9" s="12"/>
+      <x:c r="AN9" s="23"/>
+      <x:c r="AO9" s="22"/>
+      <x:c r="AP9" s="22"/>
+      <x:c r="AQ9" s="24"/>
+      <x:c r="AR9" s="24"/>
+      <x:c r="AS9" s="22"/>
+      <x:c r="AT9" s="25"/>
+      <x:c r="AU9" s="25"/>
+      <x:c r="AV9" s="22"/>
+      <x:c r="AW9" s="22"/>
+      <x:c r="AX9" s="22"/>
+      <x:c r="AY9" s="22"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12"/>
@@ -998,6 +1201,18 @@
       <x:c r="AK10" s="12"/>
       <x:c r="AL10" s="12"/>
       <x:c r="AM10" s="12"/>
+      <x:c r="AN10" s="23"/>
+      <x:c r="AO10" s="22"/>
+      <x:c r="AP10" s="22"/>
+      <x:c r="AQ10" s="24"/>
+      <x:c r="AR10" s="24"/>
+      <x:c r="AS10" s="22"/>
+      <x:c r="AT10" s="25"/>
+      <x:c r="AU10" s="25"/>
+      <x:c r="AV10" s="22"/>
+      <x:c r="AW10" s="22"/>
+      <x:c r="AX10" s="22"/>
+      <x:c r="AY10" s="22"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12"/>
@@ -1039,6 +1254,18 @@
       <x:c r="AK11" s="12"/>
       <x:c r="AL11" s="12"/>
       <x:c r="AM11" s="12"/>
+      <x:c r="AN11" s="23"/>
+      <x:c r="AO11" s="22"/>
+      <x:c r="AP11" s="22"/>
+      <x:c r="AQ11" s="24"/>
+      <x:c r="AR11" s="24"/>
+      <x:c r="AS11" s="22"/>
+      <x:c r="AT11" s="25"/>
+      <x:c r="AU11" s="25"/>
+      <x:c r="AV11" s="22"/>
+      <x:c r="AW11" s="22"/>
+      <x:c r="AX11" s="22"/>
+      <x:c r="AY11" s="22"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12"/>
@@ -1080,6 +1307,18 @@
       <x:c r="AK12" s="12"/>
       <x:c r="AL12" s="12"/>
       <x:c r="AM12" s="12"/>
+      <x:c r="AN12" s="23"/>
+      <x:c r="AO12" s="22"/>
+      <x:c r="AP12" s="22"/>
+      <x:c r="AQ12" s="24"/>
+      <x:c r="AR12" s="24"/>
+      <x:c r="AS12" s="22"/>
+      <x:c r="AT12" s="25"/>
+      <x:c r="AU12" s="25"/>
+      <x:c r="AV12" s="22"/>
+      <x:c r="AW12" s="22"/>
+      <x:c r="AX12" s="22"/>
+      <x:c r="AY12" s="22"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="12"/>
@@ -1121,6 +1360,18 @@
       <x:c r="AK13" s="12"/>
       <x:c r="AL13" s="12"/>
       <x:c r="AM13" s="12"/>
+      <x:c r="AN13" s="23"/>
+      <x:c r="AO13" s="22"/>
+      <x:c r="AP13" s="22"/>
+      <x:c r="AQ13" s="24"/>
+      <x:c r="AR13" s="24"/>
+      <x:c r="AS13" s="22"/>
+      <x:c r="AT13" s="25"/>
+      <x:c r="AU13" s="25"/>
+      <x:c r="AV13" s="22"/>
+      <x:c r="AW13" s="22"/>
+      <x:c r="AX13" s="22"/>
+      <x:c r="AY13" s="22"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12"/>
@@ -1162,6 +1413,18 @@
       <x:c r="AK14" s="12"/>
       <x:c r="AL14" s="12"/>
       <x:c r="AM14" s="12"/>
+      <x:c r="AN14" s="23"/>
+      <x:c r="AO14" s="22"/>
+      <x:c r="AP14" s="22"/>
+      <x:c r="AQ14" s="24"/>
+      <x:c r="AR14" s="24"/>
+      <x:c r="AS14" s="22"/>
+      <x:c r="AT14" s="25"/>
+      <x:c r="AU14" s="25"/>
+      <x:c r="AV14" s="22"/>
+      <x:c r="AW14" s="22"/>
+      <x:c r="AX14" s="22"/>
+      <x:c r="AY14" s="22"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12"/>
@@ -1203,6 +1466,18 @@
       <x:c r="AK15" s="12"/>
       <x:c r="AL15" s="12"/>
       <x:c r="AM15" s="12"/>
+      <x:c r="AN15" s="23"/>
+      <x:c r="AO15" s="22"/>
+      <x:c r="AP15" s="22"/>
+      <x:c r="AQ15" s="24"/>
+      <x:c r="AR15" s="24"/>
+      <x:c r="AS15" s="22"/>
+      <x:c r="AT15" s="25"/>
+      <x:c r="AU15" s="25"/>
+      <x:c r="AV15" s="22"/>
+      <x:c r="AW15" s="22"/>
+      <x:c r="AX15" s="22"/>
+      <x:c r="AY15" s="22"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="12"/>
@@ -1244,6 +1519,18 @@
       <x:c r="AK16" s="12"/>
       <x:c r="AL16" s="12"/>
       <x:c r="AM16" s="12"/>
+      <x:c r="AN16" s="23"/>
+      <x:c r="AO16" s="22"/>
+      <x:c r="AP16" s="22"/>
+      <x:c r="AQ16" s="24"/>
+      <x:c r="AR16" s="24"/>
+      <x:c r="AS16" s="22"/>
+      <x:c r="AT16" s="25"/>
+      <x:c r="AU16" s="25"/>
+      <x:c r="AV16" s="22"/>
+      <x:c r="AW16" s="22"/>
+      <x:c r="AX16" s="22"/>
+      <x:c r="AY16" s="22"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="12"/>
@@ -1285,6 +1572,18 @@
       <x:c r="AK17" s="12"/>
       <x:c r="AL17" s="12"/>
       <x:c r="AM17" s="12"/>
+      <x:c r="AN17" s="23"/>
+      <x:c r="AO17" s="22"/>
+      <x:c r="AP17" s="22"/>
+      <x:c r="AQ17" s="24"/>
+      <x:c r="AR17" s="24"/>
+      <x:c r="AS17" s="22"/>
+      <x:c r="AT17" s="25"/>
+      <x:c r="AU17" s="25"/>
+      <x:c r="AV17" s="22"/>
+      <x:c r="AW17" s="22"/>
+      <x:c r="AX17" s="22"/>
+      <x:c r="AY17" s="22"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="12"/>
@@ -1326,6 +1625,18 @@
       <x:c r="AK18" s="12"/>
       <x:c r="AL18" s="12"/>
       <x:c r="AM18" s="12"/>
+      <x:c r="AN18" s="23"/>
+      <x:c r="AO18" s="22"/>
+      <x:c r="AP18" s="22"/>
+      <x:c r="AQ18" s="24"/>
+      <x:c r="AR18" s="24"/>
+      <x:c r="AS18" s="22"/>
+      <x:c r="AT18" s="25"/>
+      <x:c r="AU18" s="25"/>
+      <x:c r="AV18" s="22"/>
+      <x:c r="AW18" s="22"/>
+      <x:c r="AX18" s="22"/>
+      <x:c r="AY18" s="22"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="12"/>
@@ -1367,6 +1678,18 @@
       <x:c r="AK19" s="12"/>
       <x:c r="AL19" s="12"/>
       <x:c r="AM19" s="12"/>
+      <x:c r="AN19" s="23"/>
+      <x:c r="AO19" s="22"/>
+      <x:c r="AP19" s="22"/>
+      <x:c r="AQ19" s="24"/>
+      <x:c r="AR19" s="24"/>
+      <x:c r="AS19" s="22"/>
+      <x:c r="AT19" s="25"/>
+      <x:c r="AU19" s="25"/>
+      <x:c r="AV19" s="22"/>
+      <x:c r="AW19" s="22"/>
+      <x:c r="AX19" s="22"/>
+      <x:c r="AY19" s="22"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="12"/>
@@ -1408,6 +1731,18 @@
       <x:c r="AK20" s="12"/>
       <x:c r="AL20" s="12"/>
       <x:c r="AM20" s="12"/>
+      <x:c r="AN20" s="23"/>
+      <x:c r="AO20" s="22"/>
+      <x:c r="AP20" s="22"/>
+      <x:c r="AQ20" s="24"/>
+      <x:c r="AR20" s="24"/>
+      <x:c r="AS20" s="22"/>
+      <x:c r="AT20" s="25"/>
+      <x:c r="AU20" s="25"/>
+      <x:c r="AV20" s="22"/>
+      <x:c r="AW20" s="22"/>
+      <x:c r="AX20" s="22"/>
+      <x:c r="AY20" s="22"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="12"/>
@@ -1449,6 +1784,18 @@
       <x:c r="AK21" s="12"/>
       <x:c r="AL21" s="12"/>
       <x:c r="AM21" s="12"/>
+      <x:c r="AN21" s="23"/>
+      <x:c r="AO21" s="22"/>
+      <x:c r="AP21" s="22"/>
+      <x:c r="AQ21" s="24"/>
+      <x:c r="AR21" s="24"/>
+      <x:c r="AS21" s="22"/>
+      <x:c r="AT21" s="25"/>
+      <x:c r="AU21" s="25"/>
+      <x:c r="AV21" s="22"/>
+      <x:c r="AW21" s="22"/>
+      <x:c r="AX21" s="22"/>
+      <x:c r="AY21" s="22"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12"/>
@@ -1490,6 +1837,18 @@
       <x:c r="AK22" s="12"/>
       <x:c r="AL22" s="12"/>
       <x:c r="AM22" s="12"/>
+      <x:c r="AN22" s="23"/>
+      <x:c r="AO22" s="22"/>
+      <x:c r="AP22" s="22"/>
+      <x:c r="AQ22" s="24"/>
+      <x:c r="AR22" s="24"/>
+      <x:c r="AS22" s="22"/>
+      <x:c r="AT22" s="25"/>
+      <x:c r="AU22" s="25"/>
+      <x:c r="AV22" s="22"/>
+      <x:c r="AW22" s="22"/>
+      <x:c r="AX22" s="22"/>
+      <x:c r="AY22" s="22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="12"/>
@@ -1531,6 +1890,18 @@
       <x:c r="AK23" s="12"/>
       <x:c r="AL23" s="12"/>
       <x:c r="AM23" s="12"/>
+      <x:c r="AN23" s="23"/>
+      <x:c r="AO23" s="22"/>
+      <x:c r="AP23" s="22"/>
+      <x:c r="AQ23" s="24"/>
+      <x:c r="AR23" s="24"/>
+      <x:c r="AS23" s="22"/>
+      <x:c r="AT23" s="25"/>
+      <x:c r="AU23" s="25"/>
+      <x:c r="AV23" s="22"/>
+      <x:c r="AW23" s="22"/>
+      <x:c r="AX23" s="22"/>
+      <x:c r="AY23" s="22"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="12"/>
@@ -1572,6 +1943,18 @@
       <x:c r="AK24" s="12"/>
       <x:c r="AL24" s="12"/>
       <x:c r="AM24" s="12"/>
+      <x:c r="AN24" s="23"/>
+      <x:c r="AO24" s="22"/>
+      <x:c r="AP24" s="22"/>
+      <x:c r="AQ24" s="24"/>
+      <x:c r="AR24" s="24"/>
+      <x:c r="AS24" s="22"/>
+      <x:c r="AT24" s="25"/>
+      <x:c r="AU24" s="25"/>
+      <x:c r="AV24" s="22"/>
+      <x:c r="AW24" s="22"/>
+      <x:c r="AX24" s="22"/>
+      <x:c r="AY24" s="22"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="12"/>
@@ -1613,6 +1996,18 @@
       <x:c r="AK25" s="12"/>
       <x:c r="AL25" s="12"/>
       <x:c r="AM25" s="12"/>
+      <x:c r="AN25" s="23"/>
+      <x:c r="AO25" s="22"/>
+      <x:c r="AP25" s="22"/>
+      <x:c r="AQ25" s="24"/>
+      <x:c r="AR25" s="24"/>
+      <x:c r="AS25" s="22"/>
+      <x:c r="AT25" s="25"/>
+      <x:c r="AU25" s="25"/>
+      <x:c r="AV25" s="22"/>
+      <x:c r="AW25" s="22"/>
+      <x:c r="AX25" s="22"/>
+      <x:c r="AY25" s="22"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="12"/>
@@ -1654,6 +2049,18 @@
       <x:c r="AK26" s="12"/>
       <x:c r="AL26" s="12"/>
       <x:c r="AM26" s="12"/>
+      <x:c r="AN26" s="23"/>
+      <x:c r="AO26" s="22"/>
+      <x:c r="AP26" s="22"/>
+      <x:c r="AQ26" s="24"/>
+      <x:c r="AR26" s="24"/>
+      <x:c r="AS26" s="22"/>
+      <x:c r="AT26" s="25"/>
+      <x:c r="AU26" s="25"/>
+      <x:c r="AV26" s="22"/>
+      <x:c r="AW26" s="22"/>
+      <x:c r="AX26" s="22"/>
+      <x:c r="AY26" s="22"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="12"/>
@@ -1695,6 +2102,18 @@
       <x:c r="AK27" s="12"/>
       <x:c r="AL27" s="12"/>
       <x:c r="AM27" s="12"/>
+      <x:c r="AN27" s="23"/>
+      <x:c r="AO27" s="22"/>
+      <x:c r="AP27" s="22"/>
+      <x:c r="AQ27" s="24"/>
+      <x:c r="AR27" s="24"/>
+      <x:c r="AS27" s="22"/>
+      <x:c r="AT27" s="25"/>
+      <x:c r="AU27" s="25"/>
+      <x:c r="AV27" s="22"/>
+      <x:c r="AW27" s="22"/>
+      <x:c r="AX27" s="22"/>
+      <x:c r="AY27" s="22"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="12"/>
@@ -1736,6 +2155,18 @@
       <x:c r="AK28" s="12"/>
       <x:c r="AL28" s="12"/>
       <x:c r="AM28" s="12"/>
+      <x:c r="AN28" s="23"/>
+      <x:c r="AO28" s="22"/>
+      <x:c r="AP28" s="22"/>
+      <x:c r="AQ28" s="24"/>
+      <x:c r="AR28" s="24"/>
+      <x:c r="AS28" s="22"/>
+      <x:c r="AT28" s="25"/>
+      <x:c r="AU28" s="25"/>
+      <x:c r="AV28" s="22"/>
+      <x:c r="AW28" s="22"/>
+      <x:c r="AX28" s="22"/>
+      <x:c r="AY28" s="22"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="12"/>
@@ -1777,6 +2208,18 @@
       <x:c r="AK29" s="12"/>
       <x:c r="AL29" s="12"/>
       <x:c r="AM29" s="12"/>
+      <x:c r="AN29" s="23"/>
+      <x:c r="AO29" s="22"/>
+      <x:c r="AP29" s="22"/>
+      <x:c r="AQ29" s="24"/>
+      <x:c r="AR29" s="24"/>
+      <x:c r="AS29" s="22"/>
+      <x:c r="AT29" s="25"/>
+      <x:c r="AU29" s="25"/>
+      <x:c r="AV29" s="22"/>
+      <x:c r="AW29" s="22"/>
+      <x:c r="AX29" s="22"/>
+      <x:c r="AY29" s="22"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="12"/>
@@ -1818,6 +2261,18 @@
       <x:c r="AK30" s="12"/>
       <x:c r="AL30" s="12"/>
       <x:c r="AM30" s="12"/>
+      <x:c r="AN30" s="23"/>
+      <x:c r="AO30" s="22"/>
+      <x:c r="AP30" s="22"/>
+      <x:c r="AQ30" s="24"/>
+      <x:c r="AR30" s="24"/>
+      <x:c r="AS30" s="22"/>
+      <x:c r="AT30" s="25"/>
+      <x:c r="AU30" s="25"/>
+      <x:c r="AV30" s="22"/>
+      <x:c r="AW30" s="22"/>
+      <x:c r="AX30" s="22"/>
+      <x:c r="AY30" s="22"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12"/>
@@ -1859,6 +2314,18 @@
       <x:c r="AK31" s="12"/>
       <x:c r="AL31" s="12"/>
       <x:c r="AM31" s="12"/>
+      <x:c r="AN31" s="23"/>
+      <x:c r="AO31" s="22"/>
+      <x:c r="AP31" s="22"/>
+      <x:c r="AQ31" s="24"/>
+      <x:c r="AR31" s="24"/>
+      <x:c r="AS31" s="22"/>
+      <x:c r="AT31" s="25"/>
+      <x:c r="AU31" s="25"/>
+      <x:c r="AV31" s="22"/>
+      <x:c r="AW31" s="22"/>
+      <x:c r="AX31" s="22"/>
+      <x:c r="AY31" s="22"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="12"/>
@@ -1900,6 +2367,18 @@
       <x:c r="AK32" s="12"/>
       <x:c r="AL32" s="12"/>
       <x:c r="AM32" s="12"/>
+      <x:c r="AN32" s="23"/>
+      <x:c r="AO32" s="22"/>
+      <x:c r="AP32" s="22"/>
+      <x:c r="AQ32" s="24"/>
+      <x:c r="AR32" s="24"/>
+      <x:c r="AS32" s="22"/>
+      <x:c r="AT32" s="25"/>
+      <x:c r="AU32" s="25"/>
+      <x:c r="AV32" s="22"/>
+      <x:c r="AW32" s="22"/>
+      <x:c r="AX32" s="22"/>
+      <x:c r="AY32" s="22"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="12"/>
@@ -1941,6 +2420,18 @@
       <x:c r="AK33" s="12"/>
       <x:c r="AL33" s="12"/>
       <x:c r="AM33" s="12"/>
+      <x:c r="AN33" s="23"/>
+      <x:c r="AO33" s="22"/>
+      <x:c r="AP33" s="22"/>
+      <x:c r="AQ33" s="24"/>
+      <x:c r="AR33" s="24"/>
+      <x:c r="AS33" s="22"/>
+      <x:c r="AT33" s="25"/>
+      <x:c r="AU33" s="25"/>
+      <x:c r="AV33" s="22"/>
+      <x:c r="AW33" s="22"/>
+      <x:c r="AX33" s="22"/>
+      <x:c r="AY33" s="22"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="12"/>
@@ -1982,6 +2473,18 @@
       <x:c r="AK34" s="12"/>
       <x:c r="AL34" s="12"/>
       <x:c r="AM34" s="12"/>
+      <x:c r="AN34" s="23"/>
+      <x:c r="AO34" s="22"/>
+      <x:c r="AP34" s="22"/>
+      <x:c r="AQ34" s="24"/>
+      <x:c r="AR34" s="24"/>
+      <x:c r="AS34" s="22"/>
+      <x:c r="AT34" s="25"/>
+      <x:c r="AU34" s="25"/>
+      <x:c r="AV34" s="22"/>
+      <x:c r="AW34" s="22"/>
+      <x:c r="AX34" s="22"/>
+      <x:c r="AY34" s="22"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="12"/>
@@ -2023,6 +2526,18 @@
       <x:c r="AK35" s="12"/>
       <x:c r="AL35" s="12"/>
       <x:c r="AM35" s="12"/>
+      <x:c r="AN35" s="23"/>
+      <x:c r="AO35" s="22"/>
+      <x:c r="AP35" s="22"/>
+      <x:c r="AQ35" s="24"/>
+      <x:c r="AR35" s="24"/>
+      <x:c r="AS35" s="22"/>
+      <x:c r="AT35" s="25"/>
+      <x:c r="AU35" s="25"/>
+      <x:c r="AV35" s="22"/>
+      <x:c r="AW35" s="22"/>
+      <x:c r="AX35" s="22"/>
+      <x:c r="AY35" s="22"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="12"/>
@@ -2064,6 +2579,18 @@
       <x:c r="AK36" s="12"/>
       <x:c r="AL36" s="12"/>
       <x:c r="AM36" s="12"/>
+      <x:c r="AN36" s="23"/>
+      <x:c r="AO36" s="22"/>
+      <x:c r="AP36" s="22"/>
+      <x:c r="AQ36" s="24"/>
+      <x:c r="AR36" s="24"/>
+      <x:c r="AS36" s="22"/>
+      <x:c r="AT36" s="25"/>
+      <x:c r="AU36" s="25"/>
+      <x:c r="AV36" s="22"/>
+      <x:c r="AW36" s="22"/>
+      <x:c r="AX36" s="22"/>
+      <x:c r="AY36" s="22"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="12"/>
@@ -2105,6 +2632,18 @@
       <x:c r="AK37" s="12"/>
       <x:c r="AL37" s="12"/>
       <x:c r="AM37" s="12"/>
+      <x:c r="AN37" s="23"/>
+      <x:c r="AO37" s="22"/>
+      <x:c r="AP37" s="22"/>
+      <x:c r="AQ37" s="24"/>
+      <x:c r="AR37" s="24"/>
+      <x:c r="AS37" s="22"/>
+      <x:c r="AT37" s="25"/>
+      <x:c r="AU37" s="25"/>
+      <x:c r="AV37" s="22"/>
+      <x:c r="AW37" s="22"/>
+      <x:c r="AX37" s="22"/>
+      <x:c r="AY37" s="22"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="12"/>
@@ -2146,6 +2685,18 @@
       <x:c r="AK38" s="12"/>
       <x:c r="AL38" s="12"/>
       <x:c r="AM38" s="12"/>
+      <x:c r="AN38" s="23"/>
+      <x:c r="AO38" s="22"/>
+      <x:c r="AP38" s="22"/>
+      <x:c r="AQ38" s="24"/>
+      <x:c r="AR38" s="24"/>
+      <x:c r="AS38" s="22"/>
+      <x:c r="AT38" s="25"/>
+      <x:c r="AU38" s="25"/>
+      <x:c r="AV38" s="22"/>
+      <x:c r="AW38" s="22"/>
+      <x:c r="AX38" s="22"/>
+      <x:c r="AY38" s="22"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="12"/>
@@ -2187,6 +2738,18 @@
       <x:c r="AK39" s="12"/>
       <x:c r="AL39" s="12"/>
       <x:c r="AM39" s="12"/>
+      <x:c r="AN39" s="23"/>
+      <x:c r="AO39" s="22"/>
+      <x:c r="AP39" s="22"/>
+      <x:c r="AQ39" s="24"/>
+      <x:c r="AR39" s="24"/>
+      <x:c r="AS39" s="22"/>
+      <x:c r="AT39" s="25"/>
+      <x:c r="AU39" s="25"/>
+      <x:c r="AV39" s="22"/>
+      <x:c r="AW39" s="22"/>
+      <x:c r="AX39" s="22"/>
+      <x:c r="AY39" s="22"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="12"/>
@@ -2228,6 +2791,18 @@
       <x:c r="AK40" s="12"/>
       <x:c r="AL40" s="12"/>
       <x:c r="AM40" s="12"/>
+      <x:c r="AN40" s="23"/>
+      <x:c r="AO40" s="22"/>
+      <x:c r="AP40" s="22"/>
+      <x:c r="AQ40" s="24"/>
+      <x:c r="AR40" s="24"/>
+      <x:c r="AS40" s="22"/>
+      <x:c r="AT40" s="25"/>
+      <x:c r="AU40" s="25"/>
+      <x:c r="AV40" s="22"/>
+      <x:c r="AW40" s="22"/>
+      <x:c r="AX40" s="22"/>
+      <x:c r="AY40" s="22"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="12"/>
@@ -2269,6 +2844,18 @@
       <x:c r="AK41" s="12"/>
       <x:c r="AL41" s="12"/>
       <x:c r="AM41" s="12"/>
+      <x:c r="AN41" s="23"/>
+      <x:c r="AO41" s="22"/>
+      <x:c r="AP41" s="22"/>
+      <x:c r="AQ41" s="24"/>
+      <x:c r="AR41" s="24"/>
+      <x:c r="AS41" s="22"/>
+      <x:c r="AT41" s="25"/>
+      <x:c r="AU41" s="25"/>
+      <x:c r="AV41" s="22"/>
+      <x:c r="AW41" s="22"/>
+      <x:c r="AX41" s="22"/>
+      <x:c r="AY41" s="22"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="12"/>
@@ -2310,6 +2897,18 @@
       <x:c r="AK42" s="12"/>
       <x:c r="AL42" s="12"/>
       <x:c r="AM42" s="12"/>
+      <x:c r="AN42" s="23"/>
+      <x:c r="AO42" s="22"/>
+      <x:c r="AP42" s="22"/>
+      <x:c r="AQ42" s="24"/>
+      <x:c r="AR42" s="24"/>
+      <x:c r="AS42" s="22"/>
+      <x:c r="AT42" s="25"/>
+      <x:c r="AU42" s="25"/>
+      <x:c r="AV42" s="22"/>
+      <x:c r="AW42" s="22"/>
+      <x:c r="AX42" s="22"/>
+      <x:c r="AY42" s="22"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="12"/>
@@ -2351,6 +2950,18 @@
       <x:c r="AK43" s="12"/>
       <x:c r="AL43" s="12"/>
       <x:c r="AM43" s="12"/>
+      <x:c r="AN43" s="23"/>
+      <x:c r="AO43" s="22"/>
+      <x:c r="AP43" s="22"/>
+      <x:c r="AQ43" s="24"/>
+      <x:c r="AR43" s="24"/>
+      <x:c r="AS43" s="22"/>
+      <x:c r="AT43" s="25"/>
+      <x:c r="AU43" s="25"/>
+      <x:c r="AV43" s="22"/>
+      <x:c r="AW43" s="22"/>
+      <x:c r="AX43" s="22"/>
+      <x:c r="AY43" s="22"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="12"/>
@@ -2392,6 +3003,18 @@
       <x:c r="AK44" s="12"/>
       <x:c r="AL44" s="12"/>
       <x:c r="AM44" s="12"/>
+      <x:c r="AN44" s="23"/>
+      <x:c r="AO44" s="22"/>
+      <x:c r="AP44" s="22"/>
+      <x:c r="AQ44" s="24"/>
+      <x:c r="AR44" s="24"/>
+      <x:c r="AS44" s="22"/>
+      <x:c r="AT44" s="25"/>
+      <x:c r="AU44" s="25"/>
+      <x:c r="AV44" s="22"/>
+      <x:c r="AW44" s="22"/>
+      <x:c r="AX44" s="22"/>
+      <x:c r="AY44" s="22"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="12"/>
@@ -2433,6 +3056,18 @@
       <x:c r="AK45" s="12"/>
       <x:c r="AL45" s="12"/>
       <x:c r="AM45" s="12"/>
+      <x:c r="AN45" s="23"/>
+      <x:c r="AO45" s="22"/>
+      <x:c r="AP45" s="22"/>
+      <x:c r="AQ45" s="24"/>
+      <x:c r="AR45" s="24"/>
+      <x:c r="AS45" s="22"/>
+      <x:c r="AT45" s="25"/>
+      <x:c r="AU45" s="25"/>
+      <x:c r="AV45" s="22"/>
+      <x:c r="AW45" s="22"/>
+      <x:c r="AX45" s="22"/>
+      <x:c r="AY45" s="22"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="12"/>
@@ -2474,6 +3109,18 @@
       <x:c r="AK46" s="12"/>
       <x:c r="AL46" s="12"/>
       <x:c r="AM46" s="12"/>
+      <x:c r="AN46" s="23"/>
+      <x:c r="AO46" s="22"/>
+      <x:c r="AP46" s="22"/>
+      <x:c r="AQ46" s="24"/>
+      <x:c r="AR46" s="24"/>
+      <x:c r="AS46" s="22"/>
+      <x:c r="AT46" s="25"/>
+      <x:c r="AU46" s="25"/>
+      <x:c r="AV46" s="22"/>
+      <x:c r="AW46" s="22"/>
+      <x:c r="AX46" s="22"/>
+      <x:c r="AY46" s="22"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="12"/>
@@ -2515,6 +3162,18 @@
       <x:c r="AK47" s="12"/>
       <x:c r="AL47" s="12"/>
       <x:c r="AM47" s="12"/>
+      <x:c r="AN47" s="23"/>
+      <x:c r="AO47" s="22"/>
+      <x:c r="AP47" s="22"/>
+      <x:c r="AQ47" s="24"/>
+      <x:c r="AR47" s="24"/>
+      <x:c r="AS47" s="22"/>
+      <x:c r="AT47" s="25"/>
+      <x:c r="AU47" s="25"/>
+      <x:c r="AV47" s="22"/>
+      <x:c r="AW47" s="22"/>
+      <x:c r="AX47" s="22"/>
+      <x:c r="AY47" s="22"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="12"/>
@@ -2556,6 +3215,18 @@
       <x:c r="AK48" s="12"/>
       <x:c r="AL48" s="12"/>
       <x:c r="AM48" s="12"/>
+      <x:c r="AN48" s="23"/>
+      <x:c r="AO48" s="22"/>
+      <x:c r="AP48" s="22"/>
+      <x:c r="AQ48" s="24"/>
+      <x:c r="AR48" s="24"/>
+      <x:c r="AS48" s="22"/>
+      <x:c r="AT48" s="25"/>
+      <x:c r="AU48" s="25"/>
+      <x:c r="AV48" s="22"/>
+      <x:c r="AW48" s="22"/>
+      <x:c r="AX48" s="22"/>
+      <x:c r="AY48" s="22"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="12"/>
@@ -2597,6 +3268,18 @@
       <x:c r="AK49" s="12"/>
       <x:c r="AL49" s="12"/>
       <x:c r="AM49" s="12"/>
+      <x:c r="AN49" s="23"/>
+      <x:c r="AO49" s="22"/>
+      <x:c r="AP49" s="22"/>
+      <x:c r="AQ49" s="24"/>
+      <x:c r="AR49" s="24"/>
+      <x:c r="AS49" s="22"/>
+      <x:c r="AT49" s="25"/>
+      <x:c r="AU49" s="25"/>
+      <x:c r="AV49" s="22"/>
+      <x:c r="AW49" s="22"/>
+      <x:c r="AX49" s="22"/>
+      <x:c r="AY49" s="22"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="12"/>
@@ -2638,6 +3321,18 @@
       <x:c r="AK50" s="12"/>
       <x:c r="AL50" s="12"/>
       <x:c r="AM50" s="12"/>
+      <x:c r="AN50" s="23"/>
+      <x:c r="AO50" s="22"/>
+      <x:c r="AP50" s="22"/>
+      <x:c r="AQ50" s="24"/>
+      <x:c r="AR50" s="24"/>
+      <x:c r="AS50" s="22"/>
+      <x:c r="AT50" s="25"/>
+      <x:c r="AU50" s="25"/>
+      <x:c r="AV50" s="22"/>
+      <x:c r="AW50" s="22"/>
+      <x:c r="AX50" s="22"/>
+      <x:c r="AY50" s="22"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="12"/>
@@ -2679,6 +3374,18 @@
       <x:c r="AK51" s="12"/>
       <x:c r="AL51" s="12"/>
       <x:c r="AM51" s="12"/>
+      <x:c r="AN51" s="23"/>
+      <x:c r="AO51" s="22"/>
+      <x:c r="AP51" s="22"/>
+      <x:c r="AQ51" s="24"/>
+      <x:c r="AR51" s="24"/>
+      <x:c r="AS51" s="22"/>
+      <x:c r="AT51" s="25"/>
+      <x:c r="AU51" s="25"/>
+      <x:c r="AV51" s="22"/>
+      <x:c r="AW51" s="22"/>
+      <x:c r="AX51" s="22"/>
+      <x:c r="AY51" s="22"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="12"/>
@@ -2720,6 +3427,18 @@
       <x:c r="AK52" s="12"/>
       <x:c r="AL52" s="12"/>
       <x:c r="AM52" s="12"/>
+      <x:c r="AN52" s="23"/>
+      <x:c r="AO52" s="22"/>
+      <x:c r="AP52" s="22"/>
+      <x:c r="AQ52" s="24"/>
+      <x:c r="AR52" s="24"/>
+      <x:c r="AS52" s="22"/>
+      <x:c r="AT52" s="25"/>
+      <x:c r="AU52" s="25"/>
+      <x:c r="AV52" s="22"/>
+      <x:c r="AW52" s="22"/>
+      <x:c r="AX52" s="22"/>
+      <x:c r="AY52" s="22"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="12"/>
@@ -2761,6 +3480,18 @@
       <x:c r="AK53" s="12"/>
       <x:c r="AL53" s="12"/>
       <x:c r="AM53" s="12"/>
+      <x:c r="AN53" s="23"/>
+      <x:c r="AO53" s="22"/>
+      <x:c r="AP53" s="22"/>
+      <x:c r="AQ53" s="24"/>
+      <x:c r="AR53" s="24"/>
+      <x:c r="AS53" s="22"/>
+      <x:c r="AT53" s="25"/>
+      <x:c r="AU53" s="25"/>
+      <x:c r="AV53" s="22"/>
+      <x:c r="AW53" s="22"/>
+      <x:c r="AX53" s="22"/>
+      <x:c r="AY53" s="22"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="12"/>
@@ -2802,6 +3533,18 @@
       <x:c r="AK54" s="12"/>
       <x:c r="AL54" s="12"/>
       <x:c r="AM54" s="12"/>
+      <x:c r="AN54" s="23"/>
+      <x:c r="AO54" s="22"/>
+      <x:c r="AP54" s="22"/>
+      <x:c r="AQ54" s="24"/>
+      <x:c r="AR54" s="24"/>
+      <x:c r="AS54" s="22"/>
+      <x:c r="AT54" s="25"/>
+      <x:c r="AU54" s="25"/>
+      <x:c r="AV54" s="22"/>
+      <x:c r="AW54" s="22"/>
+      <x:c r="AX54" s="22"/>
+      <x:c r="AY54" s="22"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="12"/>
@@ -2843,6 +3586,18 @@
       <x:c r="AK55" s="12"/>
       <x:c r="AL55" s="12"/>
       <x:c r="AM55" s="12"/>
+      <x:c r="AN55" s="23"/>
+      <x:c r="AO55" s="22"/>
+      <x:c r="AP55" s="22"/>
+      <x:c r="AQ55" s="24"/>
+      <x:c r="AR55" s="24"/>
+      <x:c r="AS55" s="22"/>
+      <x:c r="AT55" s="25"/>
+      <x:c r="AU55" s="25"/>
+      <x:c r="AV55" s="22"/>
+      <x:c r="AW55" s="22"/>
+      <x:c r="AX55" s="22"/>
+      <x:c r="AY55" s="22"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="12"/>
@@ -2884,6 +3639,18 @@
       <x:c r="AK56" s="12"/>
       <x:c r="AL56" s="12"/>
       <x:c r="AM56" s="12"/>
+      <x:c r="AN56" s="23"/>
+      <x:c r="AO56" s="22"/>
+      <x:c r="AP56" s="22"/>
+      <x:c r="AQ56" s="24"/>
+      <x:c r="AR56" s="24"/>
+      <x:c r="AS56" s="22"/>
+      <x:c r="AT56" s="25"/>
+      <x:c r="AU56" s="25"/>
+      <x:c r="AV56" s="22"/>
+      <x:c r="AW56" s="22"/>
+      <x:c r="AX56" s="22"/>
+      <x:c r="AY56" s="22"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="12"/>
@@ -2925,6 +3692,18 @@
       <x:c r="AK57" s="12"/>
       <x:c r="AL57" s="12"/>
       <x:c r="AM57" s="12"/>
+      <x:c r="AN57" s="23"/>
+      <x:c r="AO57" s="22"/>
+      <x:c r="AP57" s="22"/>
+      <x:c r="AQ57" s="24"/>
+      <x:c r="AR57" s="24"/>
+      <x:c r="AS57" s="22"/>
+      <x:c r="AT57" s="25"/>
+      <x:c r="AU57" s="25"/>
+      <x:c r="AV57" s="22"/>
+      <x:c r="AW57" s="22"/>
+      <x:c r="AX57" s="22"/>
+      <x:c r="AY57" s="22"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="12"/>
@@ -2966,6 +3745,18 @@
       <x:c r="AK58" s="12"/>
       <x:c r="AL58" s="12"/>
       <x:c r="AM58" s="12"/>
+      <x:c r="AN58" s="23"/>
+      <x:c r="AO58" s="22"/>
+      <x:c r="AP58" s="22"/>
+      <x:c r="AQ58" s="24"/>
+      <x:c r="AR58" s="24"/>
+      <x:c r="AS58" s="22"/>
+      <x:c r="AT58" s="25"/>
+      <x:c r="AU58" s="25"/>
+      <x:c r="AV58" s="22"/>
+      <x:c r="AW58" s="22"/>
+      <x:c r="AX58" s="22"/>
+      <x:c r="AY58" s="22"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="12"/>
@@ -3007,6 +3798,18 @@
       <x:c r="AK59" s="12"/>
       <x:c r="AL59" s="12"/>
       <x:c r="AM59" s="12"/>
+      <x:c r="AN59" s="23"/>
+      <x:c r="AO59" s="22"/>
+      <x:c r="AP59" s="22"/>
+      <x:c r="AQ59" s="24"/>
+      <x:c r="AR59" s="24"/>
+      <x:c r="AS59" s="22"/>
+      <x:c r="AT59" s="25"/>
+      <x:c r="AU59" s="25"/>
+      <x:c r="AV59" s="22"/>
+      <x:c r="AW59" s="22"/>
+      <x:c r="AX59" s="22"/>
+      <x:c r="AY59" s="22"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="12"/>
@@ -3048,6 +3851,18 @@
       <x:c r="AK60" s="12"/>
       <x:c r="AL60" s="12"/>
       <x:c r="AM60" s="12"/>
+      <x:c r="AN60" s="23"/>
+      <x:c r="AO60" s="22"/>
+      <x:c r="AP60" s="22"/>
+      <x:c r="AQ60" s="24"/>
+      <x:c r="AR60" s="24"/>
+      <x:c r="AS60" s="22"/>
+      <x:c r="AT60" s="25"/>
+      <x:c r="AU60" s="25"/>
+      <x:c r="AV60" s="22"/>
+      <x:c r="AW60" s="22"/>
+      <x:c r="AX60" s="22"/>
+      <x:c r="AY60" s="22"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="12"/>
@@ -3089,6 +3904,18 @@
       <x:c r="AK61" s="12"/>
       <x:c r="AL61" s="12"/>
       <x:c r="AM61" s="12"/>
+      <x:c r="AN61" s="23"/>
+      <x:c r="AO61" s="22"/>
+      <x:c r="AP61" s="22"/>
+      <x:c r="AQ61" s="24"/>
+      <x:c r="AR61" s="24"/>
+      <x:c r="AS61" s="22"/>
+      <x:c r="AT61" s="25"/>
+      <x:c r="AU61" s="25"/>
+      <x:c r="AV61" s="22"/>
+      <x:c r="AW61" s="22"/>
+      <x:c r="AX61" s="22"/>
+      <x:c r="AY61" s="22"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="12"/>
@@ -3130,6 +3957,18 @@
       <x:c r="AK62" s="12"/>
       <x:c r="AL62" s="12"/>
       <x:c r="AM62" s="12"/>
+      <x:c r="AN62" s="23"/>
+      <x:c r="AO62" s="22"/>
+      <x:c r="AP62" s="22"/>
+      <x:c r="AQ62" s="24"/>
+      <x:c r="AR62" s="24"/>
+      <x:c r="AS62" s="22"/>
+      <x:c r="AT62" s="25"/>
+      <x:c r="AU62" s="25"/>
+      <x:c r="AV62" s="22"/>
+      <x:c r="AW62" s="22"/>
+      <x:c r="AX62" s="22"/>
+      <x:c r="AY62" s="22"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="12"/>
@@ -3171,6 +4010,18 @@
       <x:c r="AK63" s="12"/>
       <x:c r="AL63" s="12"/>
       <x:c r="AM63" s="12"/>
+      <x:c r="AN63" s="23"/>
+      <x:c r="AO63" s="22"/>
+      <x:c r="AP63" s="22"/>
+      <x:c r="AQ63" s="24"/>
+      <x:c r="AR63" s="24"/>
+      <x:c r="AS63" s="22"/>
+      <x:c r="AT63" s="25"/>
+      <x:c r="AU63" s="25"/>
+      <x:c r="AV63" s="22"/>
+      <x:c r="AW63" s="22"/>
+      <x:c r="AX63" s="22"/>
+      <x:c r="AY63" s="22"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="12"/>
@@ -3212,6 +4063,18 @@
       <x:c r="AK64" s="12"/>
       <x:c r="AL64" s="12"/>
       <x:c r="AM64" s="12"/>
+      <x:c r="AN64" s="23"/>
+      <x:c r="AO64" s="22"/>
+      <x:c r="AP64" s="22"/>
+      <x:c r="AQ64" s="24"/>
+      <x:c r="AR64" s="24"/>
+      <x:c r="AS64" s="22"/>
+      <x:c r="AT64" s="25"/>
+      <x:c r="AU64" s="25"/>
+      <x:c r="AV64" s="22"/>
+      <x:c r="AW64" s="22"/>
+      <x:c r="AX64" s="22"/>
+      <x:c r="AY64" s="22"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="12"/>
@@ -3253,6 +4116,18 @@
       <x:c r="AK65" s="12"/>
       <x:c r="AL65" s="12"/>
       <x:c r="AM65" s="12"/>
+      <x:c r="AN65" s="23"/>
+      <x:c r="AO65" s="22"/>
+      <x:c r="AP65" s="22"/>
+      <x:c r="AQ65" s="24"/>
+      <x:c r="AR65" s="24"/>
+      <x:c r="AS65" s="22"/>
+      <x:c r="AT65" s="25"/>
+      <x:c r="AU65" s="25"/>
+      <x:c r="AV65" s="22"/>
+      <x:c r="AW65" s="22"/>
+      <x:c r="AX65" s="22"/>
+      <x:c r="AY65" s="22"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="12"/>
@@ -3294,6 +4169,18 @@
       <x:c r="AK66" s="12"/>
       <x:c r="AL66" s="12"/>
       <x:c r="AM66" s="12"/>
+      <x:c r="AN66" s="23"/>
+      <x:c r="AO66" s="22"/>
+      <x:c r="AP66" s="22"/>
+      <x:c r="AQ66" s="24"/>
+      <x:c r="AR66" s="24"/>
+      <x:c r="AS66" s="22"/>
+      <x:c r="AT66" s="25"/>
+      <x:c r="AU66" s="25"/>
+      <x:c r="AV66" s="22"/>
+      <x:c r="AW66" s="22"/>
+      <x:c r="AX66" s="22"/>
+      <x:c r="AY66" s="22"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="12"/>
@@ -3335,6 +4222,18 @@
       <x:c r="AK67" s="12"/>
       <x:c r="AL67" s="12"/>
       <x:c r="AM67" s="12"/>
+      <x:c r="AN67" s="23"/>
+      <x:c r="AO67" s="22"/>
+      <x:c r="AP67" s="22"/>
+      <x:c r="AQ67" s="24"/>
+      <x:c r="AR67" s="24"/>
+      <x:c r="AS67" s="22"/>
+      <x:c r="AT67" s="25"/>
+      <x:c r="AU67" s="25"/>
+      <x:c r="AV67" s="22"/>
+      <x:c r="AW67" s="22"/>
+      <x:c r="AX67" s="22"/>
+      <x:c r="AY67" s="22"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="12"/>
@@ -3376,6 +4275,18 @@
       <x:c r="AK68" s="12"/>
       <x:c r="AL68" s="12"/>
       <x:c r="AM68" s="12"/>
+      <x:c r="AN68" s="23"/>
+      <x:c r="AO68" s="22"/>
+      <x:c r="AP68" s="22"/>
+      <x:c r="AQ68" s="24"/>
+      <x:c r="AR68" s="24"/>
+      <x:c r="AS68" s="22"/>
+      <x:c r="AT68" s="25"/>
+      <x:c r="AU68" s="25"/>
+      <x:c r="AV68" s="22"/>
+      <x:c r="AW68" s="22"/>
+      <x:c r="AX68" s="22"/>
+      <x:c r="AY68" s="22"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="12"/>
@@ -3417,6 +4328,18 @@
       <x:c r="AK69" s="12"/>
       <x:c r="AL69" s="12"/>
       <x:c r="AM69" s="12"/>
+      <x:c r="AN69" s="23"/>
+      <x:c r="AO69" s="22"/>
+      <x:c r="AP69" s="22"/>
+      <x:c r="AQ69" s="24"/>
+      <x:c r="AR69" s="24"/>
+      <x:c r="AS69" s="22"/>
+      <x:c r="AT69" s="25"/>
+      <x:c r="AU69" s="25"/>
+      <x:c r="AV69" s="22"/>
+      <x:c r="AW69" s="22"/>
+      <x:c r="AX69" s="22"/>
+      <x:c r="AY69" s="22"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="12"/>
@@ -3458,6 +4381,18 @@
       <x:c r="AK70" s="12"/>
       <x:c r="AL70" s="12"/>
       <x:c r="AM70" s="12"/>
+      <x:c r="AN70" s="23"/>
+      <x:c r="AO70" s="22"/>
+      <x:c r="AP70" s="22"/>
+      <x:c r="AQ70" s="24"/>
+      <x:c r="AR70" s="24"/>
+      <x:c r="AS70" s="22"/>
+      <x:c r="AT70" s="25"/>
+      <x:c r="AU70" s="25"/>
+      <x:c r="AV70" s="22"/>
+      <x:c r="AW70" s="22"/>
+      <x:c r="AX70" s="22"/>
+      <x:c r="AY70" s="22"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="12"/>
@@ -3499,6 +4434,18 @@
       <x:c r="AK71" s="12"/>
       <x:c r="AL71" s="12"/>
       <x:c r="AM71" s="12"/>
+      <x:c r="AN71" s="23"/>
+      <x:c r="AO71" s="22"/>
+      <x:c r="AP71" s="22"/>
+      <x:c r="AQ71" s="24"/>
+      <x:c r="AR71" s="24"/>
+      <x:c r="AS71" s="22"/>
+      <x:c r="AT71" s="25"/>
+      <x:c r="AU71" s="25"/>
+      <x:c r="AV71" s="22"/>
+      <x:c r="AW71" s="22"/>
+      <x:c r="AX71" s="22"/>
+      <x:c r="AY71" s="22"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="12"/>
@@ -3540,6 +4487,18 @@
       <x:c r="AK72" s="12"/>
       <x:c r="AL72" s="12"/>
       <x:c r="AM72" s="12"/>
+      <x:c r="AN72" s="23"/>
+      <x:c r="AO72" s="22"/>
+      <x:c r="AP72" s="22"/>
+      <x:c r="AQ72" s="24"/>
+      <x:c r="AR72" s="24"/>
+      <x:c r="AS72" s="22"/>
+      <x:c r="AT72" s="25"/>
+      <x:c r="AU72" s="25"/>
+      <x:c r="AV72" s="22"/>
+      <x:c r="AW72" s="22"/>
+      <x:c r="AX72" s="22"/>
+      <x:c r="AY72" s="22"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="12"/>
@@ -3581,6 +4540,18 @@
       <x:c r="AK73" s="12"/>
       <x:c r="AL73" s="12"/>
       <x:c r="AM73" s="12"/>
+      <x:c r="AN73" s="23"/>
+      <x:c r="AO73" s="22"/>
+      <x:c r="AP73" s="22"/>
+      <x:c r="AQ73" s="24"/>
+      <x:c r="AR73" s="24"/>
+      <x:c r="AS73" s="22"/>
+      <x:c r="AT73" s="25"/>
+      <x:c r="AU73" s="25"/>
+      <x:c r="AV73" s="22"/>
+      <x:c r="AW73" s="22"/>
+      <x:c r="AX73" s="22"/>
+      <x:c r="AY73" s="22"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="12"/>
@@ -3622,6 +4593,18 @@
       <x:c r="AK74" s="12"/>
       <x:c r="AL74" s="12"/>
       <x:c r="AM74" s="12"/>
+      <x:c r="AN74" s="23"/>
+      <x:c r="AO74" s="22"/>
+      <x:c r="AP74" s="22"/>
+      <x:c r="AQ74" s="24"/>
+      <x:c r="AR74" s="24"/>
+      <x:c r="AS74" s="22"/>
+      <x:c r="AT74" s="25"/>
+      <x:c r="AU74" s="25"/>
+      <x:c r="AV74" s="22"/>
+      <x:c r="AW74" s="22"/>
+      <x:c r="AX74" s="22"/>
+      <x:c r="AY74" s="22"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="12"/>
@@ -3663,6 +4646,18 @@
       <x:c r="AK75" s="12"/>
       <x:c r="AL75" s="12"/>
       <x:c r="AM75" s="12"/>
+      <x:c r="AN75" s="23"/>
+      <x:c r="AO75" s="22"/>
+      <x:c r="AP75" s="22"/>
+      <x:c r="AQ75" s="24"/>
+      <x:c r="AR75" s="24"/>
+      <x:c r="AS75" s="22"/>
+      <x:c r="AT75" s="25"/>
+      <x:c r="AU75" s="25"/>
+      <x:c r="AV75" s="22"/>
+      <x:c r="AW75" s="22"/>
+      <x:c r="AX75" s="22"/>
+      <x:c r="AY75" s="22"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="12"/>
@@ -3704,6 +4699,18 @@
       <x:c r="AK76" s="12"/>
       <x:c r="AL76" s="12"/>
       <x:c r="AM76" s="12"/>
+      <x:c r="AN76" s="23"/>
+      <x:c r="AO76" s="22"/>
+      <x:c r="AP76" s="22"/>
+      <x:c r="AQ76" s="24"/>
+      <x:c r="AR76" s="24"/>
+      <x:c r="AS76" s="22"/>
+      <x:c r="AT76" s="25"/>
+      <x:c r="AU76" s="25"/>
+      <x:c r="AV76" s="22"/>
+      <x:c r="AW76" s="22"/>
+      <x:c r="AX76" s="22"/>
+      <x:c r="AY76" s="22"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="12"/>
@@ -3745,6 +4752,18 @@
       <x:c r="AK77" s="12"/>
       <x:c r="AL77" s="12"/>
       <x:c r="AM77" s="12"/>
+      <x:c r="AN77" s="23"/>
+      <x:c r="AO77" s="22"/>
+      <x:c r="AP77" s="22"/>
+      <x:c r="AQ77" s="24"/>
+      <x:c r="AR77" s="24"/>
+      <x:c r="AS77" s="22"/>
+      <x:c r="AT77" s="25"/>
+      <x:c r="AU77" s="25"/>
+      <x:c r="AV77" s="22"/>
+      <x:c r="AW77" s="22"/>
+      <x:c r="AX77" s="22"/>
+      <x:c r="AY77" s="22"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="12"/>
@@ -3786,6 +4805,18 @@
       <x:c r="AK78" s="12"/>
       <x:c r="AL78" s="12"/>
       <x:c r="AM78" s="12"/>
+      <x:c r="AN78" s="23"/>
+      <x:c r="AO78" s="22"/>
+      <x:c r="AP78" s="22"/>
+      <x:c r="AQ78" s="24"/>
+      <x:c r="AR78" s="24"/>
+      <x:c r="AS78" s="22"/>
+      <x:c r="AT78" s="25"/>
+      <x:c r="AU78" s="25"/>
+      <x:c r="AV78" s="22"/>
+      <x:c r="AW78" s="22"/>
+      <x:c r="AX78" s="22"/>
+      <x:c r="AY78" s="22"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="12"/>
@@ -3827,6 +4858,18 @@
       <x:c r="AK79" s="12"/>
       <x:c r="AL79" s="12"/>
       <x:c r="AM79" s="12"/>
+      <x:c r="AN79" s="23"/>
+      <x:c r="AO79" s="22"/>
+      <x:c r="AP79" s="22"/>
+      <x:c r="AQ79" s="24"/>
+      <x:c r="AR79" s="24"/>
+      <x:c r="AS79" s="22"/>
+      <x:c r="AT79" s="25"/>
+      <x:c r="AU79" s="25"/>
+      <x:c r="AV79" s="22"/>
+      <x:c r="AW79" s="22"/>
+      <x:c r="AX79" s="22"/>
+      <x:c r="AY79" s="22"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="12"/>
@@ -3868,6 +4911,18 @@
       <x:c r="AK80" s="12"/>
       <x:c r="AL80" s="12"/>
       <x:c r="AM80" s="12"/>
+      <x:c r="AN80" s="23"/>
+      <x:c r="AO80" s="22"/>
+      <x:c r="AP80" s="22"/>
+      <x:c r="AQ80" s="24"/>
+      <x:c r="AR80" s="24"/>
+      <x:c r="AS80" s="22"/>
+      <x:c r="AT80" s="25"/>
+      <x:c r="AU80" s="25"/>
+      <x:c r="AV80" s="22"/>
+      <x:c r="AW80" s="22"/>
+      <x:c r="AX80" s="22"/>
+      <x:c r="AY80" s="22"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="12"/>
@@ -3909,6 +4964,18 @@
       <x:c r="AK81" s="12"/>
       <x:c r="AL81" s="12"/>
       <x:c r="AM81" s="12"/>
+      <x:c r="AN81" s="23"/>
+      <x:c r="AO81" s="22"/>
+      <x:c r="AP81" s="22"/>
+      <x:c r="AQ81" s="24"/>
+      <x:c r="AR81" s="24"/>
+      <x:c r="AS81" s="22"/>
+      <x:c r="AT81" s="25"/>
+      <x:c r="AU81" s="25"/>
+      <x:c r="AV81" s="22"/>
+      <x:c r="AW81" s="22"/>
+      <x:c r="AX81" s="22"/>
+      <x:c r="AY81" s="22"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="12"/>
@@ -3950,6 +5017,18 @@
       <x:c r="AK82" s="12"/>
       <x:c r="AL82" s="12"/>
       <x:c r="AM82" s="12"/>
+      <x:c r="AN82" s="23"/>
+      <x:c r="AO82" s="22"/>
+      <x:c r="AP82" s="22"/>
+      <x:c r="AQ82" s="24"/>
+      <x:c r="AR82" s="24"/>
+      <x:c r="AS82" s="22"/>
+      <x:c r="AT82" s="25"/>
+      <x:c r="AU82" s="25"/>
+      <x:c r="AV82" s="22"/>
+      <x:c r="AW82" s="22"/>
+      <x:c r="AX82" s="22"/>
+      <x:c r="AY82" s="22"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="12"/>
@@ -3991,6 +5070,18 @@
       <x:c r="AK83" s="12"/>
       <x:c r="AL83" s="12"/>
       <x:c r="AM83" s="12"/>
+      <x:c r="AN83" s="23"/>
+      <x:c r="AO83" s="22"/>
+      <x:c r="AP83" s="22"/>
+      <x:c r="AQ83" s="24"/>
+      <x:c r="AR83" s="24"/>
+      <x:c r="AS83" s="22"/>
+      <x:c r="AT83" s="25"/>
+      <x:c r="AU83" s="25"/>
+      <x:c r="AV83" s="22"/>
+      <x:c r="AW83" s="22"/>
+      <x:c r="AX83" s="22"/>
+      <x:c r="AY83" s="22"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="12"/>
@@ -4032,6 +5123,18 @@
       <x:c r="AK84" s="12"/>
       <x:c r="AL84" s="12"/>
       <x:c r="AM84" s="12"/>
+      <x:c r="AN84" s="23"/>
+      <x:c r="AO84" s="22"/>
+      <x:c r="AP84" s="22"/>
+      <x:c r="AQ84" s="24"/>
+      <x:c r="AR84" s="24"/>
+      <x:c r="AS84" s="22"/>
+      <x:c r="AT84" s="25"/>
+      <x:c r="AU84" s="25"/>
+      <x:c r="AV84" s="22"/>
+      <x:c r="AW84" s="22"/>
+      <x:c r="AX84" s="22"/>
+      <x:c r="AY84" s="22"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="12"/>
@@ -4073,6 +5176,18 @@
       <x:c r="AK85" s="12"/>
       <x:c r="AL85" s="12"/>
       <x:c r="AM85" s="12"/>
+      <x:c r="AN85" s="23"/>
+      <x:c r="AO85" s="22"/>
+      <x:c r="AP85" s="22"/>
+      <x:c r="AQ85" s="24"/>
+      <x:c r="AR85" s="24"/>
+      <x:c r="AS85" s="22"/>
+      <x:c r="AT85" s="25"/>
+      <x:c r="AU85" s="25"/>
+      <x:c r="AV85" s="22"/>
+      <x:c r="AW85" s="22"/>
+      <x:c r="AX85" s="22"/>
+      <x:c r="AY85" s="22"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="12"/>
@@ -4114,6 +5229,18 @@
       <x:c r="AK86" s="12"/>
       <x:c r="AL86" s="12"/>
       <x:c r="AM86" s="12"/>
+      <x:c r="AN86" s="23"/>
+      <x:c r="AO86" s="22"/>
+      <x:c r="AP86" s="22"/>
+      <x:c r="AQ86" s="24"/>
+      <x:c r="AR86" s="24"/>
+      <x:c r="AS86" s="22"/>
+      <x:c r="AT86" s="25"/>
+      <x:c r="AU86" s="25"/>
+      <x:c r="AV86" s="22"/>
+      <x:c r="AW86" s="22"/>
+      <x:c r="AX86" s="22"/>
+      <x:c r="AY86" s="22"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="12"/>
@@ -4155,6 +5282,18 @@
       <x:c r="AK87" s="12"/>
       <x:c r="AL87" s="12"/>
       <x:c r="AM87" s="12"/>
+      <x:c r="AN87" s="23"/>
+      <x:c r="AO87" s="22"/>
+      <x:c r="AP87" s="22"/>
+      <x:c r="AQ87" s="24"/>
+      <x:c r="AR87" s="24"/>
+      <x:c r="AS87" s="22"/>
+      <x:c r="AT87" s="25"/>
+      <x:c r="AU87" s="25"/>
+      <x:c r="AV87" s="22"/>
+      <x:c r="AW87" s="22"/>
+      <x:c r="AX87" s="22"/>
+      <x:c r="AY87" s="22"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="12"/>
@@ -4196,6 +5335,18 @@
       <x:c r="AK88" s="12"/>
       <x:c r="AL88" s="12"/>
       <x:c r="AM88" s="12"/>
+      <x:c r="AN88" s="23"/>
+      <x:c r="AO88" s="22"/>
+      <x:c r="AP88" s="22"/>
+      <x:c r="AQ88" s="24"/>
+      <x:c r="AR88" s="24"/>
+      <x:c r="AS88" s="22"/>
+      <x:c r="AT88" s="25"/>
+      <x:c r="AU88" s="25"/>
+      <x:c r="AV88" s="22"/>
+      <x:c r="AW88" s="22"/>
+      <x:c r="AX88" s="22"/>
+      <x:c r="AY88" s="22"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="12"/>
@@ -4237,6 +5388,18 @@
       <x:c r="AK89" s="12"/>
       <x:c r="AL89" s="12"/>
       <x:c r="AM89" s="12"/>
+      <x:c r="AN89" s="23"/>
+      <x:c r="AO89" s="22"/>
+      <x:c r="AP89" s="22"/>
+      <x:c r="AQ89" s="24"/>
+      <x:c r="AR89" s="24"/>
+      <x:c r="AS89" s="22"/>
+      <x:c r="AT89" s="25"/>
+      <x:c r="AU89" s="25"/>
+      <x:c r="AV89" s="22"/>
+      <x:c r="AW89" s="22"/>
+      <x:c r="AX89" s="22"/>
+      <x:c r="AY89" s="22"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="12"/>
@@ -4278,6 +5441,18 @@
       <x:c r="AK90" s="12"/>
       <x:c r="AL90" s="12"/>
       <x:c r="AM90" s="12"/>
+      <x:c r="AN90" s="23"/>
+      <x:c r="AO90" s="22"/>
+      <x:c r="AP90" s="22"/>
+      <x:c r="AQ90" s="24"/>
+      <x:c r="AR90" s="24"/>
+      <x:c r="AS90" s="22"/>
+      <x:c r="AT90" s="25"/>
+      <x:c r="AU90" s="25"/>
+      <x:c r="AV90" s="22"/>
+      <x:c r="AW90" s="22"/>
+      <x:c r="AX90" s="22"/>
+      <x:c r="AY90" s="22"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="12"/>
@@ -4319,6 +5494,18 @@
       <x:c r="AK91" s="12"/>
       <x:c r="AL91" s="12"/>
       <x:c r="AM91" s="12"/>
+      <x:c r="AN91" s="23"/>
+      <x:c r="AO91" s="22"/>
+      <x:c r="AP91" s="22"/>
+      <x:c r="AQ91" s="24"/>
+      <x:c r="AR91" s="24"/>
+      <x:c r="AS91" s="22"/>
+      <x:c r="AT91" s="25"/>
+      <x:c r="AU91" s="25"/>
+      <x:c r="AV91" s="22"/>
+      <x:c r="AW91" s="22"/>
+      <x:c r="AX91" s="22"/>
+      <x:c r="AY91" s="22"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="12"/>
@@ -4360,6 +5547,18 @@
       <x:c r="AK92" s="12"/>
       <x:c r="AL92" s="12"/>
       <x:c r="AM92" s="12"/>
+      <x:c r="AN92" s="23"/>
+      <x:c r="AO92" s="22"/>
+      <x:c r="AP92" s="22"/>
+      <x:c r="AQ92" s="24"/>
+      <x:c r="AR92" s="24"/>
+      <x:c r="AS92" s="22"/>
+      <x:c r="AT92" s="25"/>
+      <x:c r="AU92" s="25"/>
+      <x:c r="AV92" s="22"/>
+      <x:c r="AW92" s="22"/>
+      <x:c r="AX92" s="22"/>
+      <x:c r="AY92" s="22"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="12"/>
@@ -4401,6 +5600,18 @@
       <x:c r="AK93" s="12"/>
       <x:c r="AL93" s="12"/>
       <x:c r="AM93" s="12"/>
+      <x:c r="AN93" s="23"/>
+      <x:c r="AO93" s="22"/>
+      <x:c r="AP93" s="22"/>
+      <x:c r="AQ93" s="24"/>
+      <x:c r="AR93" s="24"/>
+      <x:c r="AS93" s="22"/>
+      <x:c r="AT93" s="25"/>
+      <x:c r="AU93" s="25"/>
+      <x:c r="AV93" s="22"/>
+      <x:c r="AW93" s="22"/>
+      <x:c r="AX93" s="22"/>
+      <x:c r="AY93" s="22"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="12"/>
@@ -4442,6 +5653,18 @@
       <x:c r="AK94" s="12"/>
       <x:c r="AL94" s="12"/>
       <x:c r="AM94" s="12"/>
+      <x:c r="AN94" s="23"/>
+      <x:c r="AO94" s="22"/>
+      <x:c r="AP94" s="22"/>
+      <x:c r="AQ94" s="24"/>
+      <x:c r="AR94" s="24"/>
+      <x:c r="AS94" s="22"/>
+      <x:c r="AT94" s="25"/>
+      <x:c r="AU94" s="25"/>
+      <x:c r="AV94" s="22"/>
+      <x:c r="AW94" s="22"/>
+      <x:c r="AX94" s="22"/>
+      <x:c r="AY94" s="22"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="12"/>
@@ -4483,6 +5706,18 @@
       <x:c r="AK95" s="12"/>
       <x:c r="AL95" s="12"/>
       <x:c r="AM95" s="12"/>
+      <x:c r="AN95" s="23"/>
+      <x:c r="AO95" s="22"/>
+      <x:c r="AP95" s="22"/>
+      <x:c r="AQ95" s="24"/>
+      <x:c r="AR95" s="24"/>
+      <x:c r="AS95" s="22"/>
+      <x:c r="AT95" s="25"/>
+      <x:c r="AU95" s="25"/>
+      <x:c r="AV95" s="22"/>
+      <x:c r="AW95" s="22"/>
+      <x:c r="AX95" s="22"/>
+      <x:c r="AY95" s="22"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="12"/>
@@ -4524,6 +5759,18 @@
       <x:c r="AK96" s="12"/>
       <x:c r="AL96" s="12"/>
       <x:c r="AM96" s="12"/>
+      <x:c r="AN96" s="23"/>
+      <x:c r="AO96" s="22"/>
+      <x:c r="AP96" s="22"/>
+      <x:c r="AQ96" s="24"/>
+      <x:c r="AR96" s="24"/>
+      <x:c r="AS96" s="22"/>
+      <x:c r="AT96" s="25"/>
+      <x:c r="AU96" s="25"/>
+      <x:c r="AV96" s="22"/>
+      <x:c r="AW96" s="22"/>
+      <x:c r="AX96" s="22"/>
+      <x:c r="AY96" s="22"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="12"/>
@@ -4565,6 +5812,18 @@
       <x:c r="AK97" s="12"/>
       <x:c r="AL97" s="12"/>
       <x:c r="AM97" s="12"/>
+      <x:c r="AN97" s="23"/>
+      <x:c r="AO97" s="22"/>
+      <x:c r="AP97" s="22"/>
+      <x:c r="AQ97" s="24"/>
+      <x:c r="AR97" s="24"/>
+      <x:c r="AS97" s="22"/>
+      <x:c r="AT97" s="25"/>
+      <x:c r="AU97" s="25"/>
+      <x:c r="AV97" s="22"/>
+      <x:c r="AW97" s="22"/>
+      <x:c r="AX97" s="22"/>
+      <x:c r="AY97" s="22"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="12"/>
@@ -4606,6 +5865,18 @@
       <x:c r="AK98" s="12"/>
       <x:c r="AL98" s="12"/>
       <x:c r="AM98" s="12"/>
+      <x:c r="AN98" s="23"/>
+      <x:c r="AO98" s="22"/>
+      <x:c r="AP98" s="22"/>
+      <x:c r="AQ98" s="24"/>
+      <x:c r="AR98" s="24"/>
+      <x:c r="AS98" s="22"/>
+      <x:c r="AT98" s="25"/>
+      <x:c r="AU98" s="25"/>
+      <x:c r="AV98" s="22"/>
+      <x:c r="AW98" s="22"/>
+      <x:c r="AX98" s="22"/>
+      <x:c r="AY98" s="22"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="12"/>
@@ -4647,6 +5918,18 @@
       <x:c r="AK99" s="12"/>
       <x:c r="AL99" s="12"/>
       <x:c r="AM99" s="12"/>
+      <x:c r="AN99" s="23"/>
+      <x:c r="AO99" s="22"/>
+      <x:c r="AP99" s="22"/>
+      <x:c r="AQ99" s="24"/>
+      <x:c r="AR99" s="24"/>
+      <x:c r="AS99" s="22"/>
+      <x:c r="AT99" s="25"/>
+      <x:c r="AU99" s="25"/>
+      <x:c r="AV99" s="22"/>
+      <x:c r="AW99" s="22"/>
+      <x:c r="AX99" s="22"/>
+      <x:c r="AY99" s="22"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="12"/>
@@ -4688,6 +5971,18 @@
       <x:c r="AK100" s="12"/>
       <x:c r="AL100" s="12"/>
       <x:c r="AM100" s="12"/>
+      <x:c r="AN100" s="23"/>
+      <x:c r="AO100" s="22"/>
+      <x:c r="AP100" s="22"/>
+      <x:c r="AQ100" s="24"/>
+      <x:c r="AR100" s="24"/>
+      <x:c r="AS100" s="22"/>
+      <x:c r="AT100" s="25"/>
+      <x:c r="AU100" s="25"/>
+      <x:c r="AV100" s="22"/>
+      <x:c r="AW100" s="22"/>
+      <x:c r="AX100" s="22"/>
+      <x:c r="AY100" s="22"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="12"/>
@@ -4729,6 +6024,18 @@
       <x:c r="AK101" s="12"/>
       <x:c r="AL101" s="12"/>
       <x:c r="AM101" s="12"/>
+      <x:c r="AN101" s="23"/>
+      <x:c r="AO101" s="22"/>
+      <x:c r="AP101" s="22"/>
+      <x:c r="AQ101" s="24"/>
+      <x:c r="AR101" s="24"/>
+      <x:c r="AS101" s="22"/>
+      <x:c r="AT101" s="25"/>
+      <x:c r="AU101" s="25"/>
+      <x:c r="AV101" s="22"/>
+      <x:c r="AW101" s="22"/>
+      <x:c r="AX101" s="22"/>
+      <x:c r="AY101" s="22"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="12"/>
@@ -4770,6 +6077,18 @@
       <x:c r="AK102" s="12"/>
       <x:c r="AL102" s="12"/>
       <x:c r="AM102" s="12"/>
+      <x:c r="AN102" s="23"/>
+      <x:c r="AO102" s="22"/>
+      <x:c r="AP102" s="22"/>
+      <x:c r="AQ102" s="24"/>
+      <x:c r="AR102" s="24"/>
+      <x:c r="AS102" s="22"/>
+      <x:c r="AT102" s="25"/>
+      <x:c r="AU102" s="25"/>
+      <x:c r="AV102" s="22"/>
+      <x:c r="AW102" s="22"/>
+      <x:c r="AX102" s="22"/>
+      <x:c r="AY102" s="22"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="12"/>
@@ -4811,6 +6130,18 @@
       <x:c r="AK103" s="12"/>
       <x:c r="AL103" s="12"/>
       <x:c r="AM103" s="12"/>
+      <x:c r="AN103" s="23"/>
+      <x:c r="AO103" s="22"/>
+      <x:c r="AP103" s="22"/>
+      <x:c r="AQ103" s="24"/>
+      <x:c r="AR103" s="24"/>
+      <x:c r="AS103" s="22"/>
+      <x:c r="AT103" s="25"/>
+      <x:c r="AU103" s="25"/>
+      <x:c r="AV103" s="22"/>
+      <x:c r="AW103" s="22"/>
+      <x:c r="AX103" s="22"/>
+      <x:c r="AY103" s="22"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="12"/>
@@ -4852,6 +6183,18 @@
       <x:c r="AK104" s="12"/>
       <x:c r="AL104" s="12"/>
       <x:c r="AM104" s="12"/>
+      <x:c r="AN104" s="23"/>
+      <x:c r="AO104" s="22"/>
+      <x:c r="AP104" s="22"/>
+      <x:c r="AQ104" s="24"/>
+      <x:c r="AR104" s="24"/>
+      <x:c r="AS104" s="22"/>
+      <x:c r="AT104" s="25"/>
+      <x:c r="AU104" s="25"/>
+      <x:c r="AV104" s="22"/>
+      <x:c r="AW104" s="22"/>
+      <x:c r="AX104" s="22"/>
+      <x:c r="AY104" s="22"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="12"/>
@@ -4893,6 +6236,18 @@
       <x:c r="AK105" s="12"/>
       <x:c r="AL105" s="12"/>
       <x:c r="AM105" s="12"/>
+      <x:c r="AN105" s="23"/>
+      <x:c r="AO105" s="22"/>
+      <x:c r="AP105" s="22"/>
+      <x:c r="AQ105" s="24"/>
+      <x:c r="AR105" s="24"/>
+      <x:c r="AS105" s="22"/>
+      <x:c r="AT105" s="25"/>
+      <x:c r="AU105" s="25"/>
+      <x:c r="AV105" s="22"/>
+      <x:c r="AW105" s="22"/>
+      <x:c r="AX105" s="22"/>
+      <x:c r="AY105" s="22"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="12"/>
@@ -4934,6 +6289,18 @@
       <x:c r="AK106" s="12"/>
       <x:c r="AL106" s="12"/>
       <x:c r="AM106" s="12"/>
+      <x:c r="AN106" s="23"/>
+      <x:c r="AO106" s="22"/>
+      <x:c r="AP106" s="22"/>
+      <x:c r="AQ106" s="24"/>
+      <x:c r="AR106" s="24"/>
+      <x:c r="AS106" s="22"/>
+      <x:c r="AT106" s="25"/>
+      <x:c r="AU106" s="25"/>
+      <x:c r="AV106" s="22"/>
+      <x:c r="AW106" s="22"/>
+      <x:c r="AX106" s="22"/>
+      <x:c r="AY106" s="22"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="12"/>
@@ -4975,6 +6342,18 @@
       <x:c r="AK107" s="12"/>
       <x:c r="AL107" s="12"/>
       <x:c r="AM107" s="12"/>
+      <x:c r="AN107" s="23"/>
+      <x:c r="AO107" s="22"/>
+      <x:c r="AP107" s="22"/>
+      <x:c r="AQ107" s="24"/>
+      <x:c r="AR107" s="24"/>
+      <x:c r="AS107" s="22"/>
+      <x:c r="AT107" s="25"/>
+      <x:c r="AU107" s="25"/>
+      <x:c r="AV107" s="22"/>
+      <x:c r="AW107" s="22"/>
+      <x:c r="AX107" s="22"/>
+      <x:c r="AY107" s="22"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="12"/>
@@ -5016,6 +6395,18 @@
       <x:c r="AK108" s="12"/>
       <x:c r="AL108" s="12"/>
       <x:c r="AM108" s="12"/>
+      <x:c r="AN108" s="23"/>
+      <x:c r="AO108" s="22"/>
+      <x:c r="AP108" s="22"/>
+      <x:c r="AQ108" s="24"/>
+      <x:c r="AR108" s="24"/>
+      <x:c r="AS108" s="22"/>
+      <x:c r="AT108" s="25"/>
+      <x:c r="AU108" s="25"/>
+      <x:c r="AV108" s="22"/>
+      <x:c r="AW108" s="22"/>
+      <x:c r="AX108" s="22"/>
+      <x:c r="AY108" s="22"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="12"/>
@@ -5057,6 +6448,18 @@
       <x:c r="AK109" s="12"/>
       <x:c r="AL109" s="12"/>
       <x:c r="AM109" s="12"/>
+      <x:c r="AN109" s="23"/>
+      <x:c r="AO109" s="22"/>
+      <x:c r="AP109" s="22"/>
+      <x:c r="AQ109" s="24"/>
+      <x:c r="AR109" s="24"/>
+      <x:c r="AS109" s="22"/>
+      <x:c r="AT109" s="25"/>
+      <x:c r="AU109" s="25"/>
+      <x:c r="AV109" s="22"/>
+      <x:c r="AW109" s="22"/>
+      <x:c r="AX109" s="22"/>
+      <x:c r="AY109" s="22"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="12"/>
@@ -5098,6 +6501,18 @@
       <x:c r="AK110" s="12"/>
       <x:c r="AL110" s="12"/>
       <x:c r="AM110" s="12"/>
+      <x:c r="AN110" s="23"/>
+      <x:c r="AO110" s="22"/>
+      <x:c r="AP110" s="22"/>
+      <x:c r="AQ110" s="24"/>
+      <x:c r="AR110" s="24"/>
+      <x:c r="AS110" s="22"/>
+      <x:c r="AT110" s="25"/>
+      <x:c r="AU110" s="25"/>
+      <x:c r="AV110" s="22"/>
+      <x:c r="AW110" s="22"/>
+      <x:c r="AX110" s="22"/>
+      <x:c r="AY110" s="22"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="12"/>
@@ -5139,6 +6554,18 @@
       <x:c r="AK111" s="12"/>
       <x:c r="AL111" s="12"/>
       <x:c r="AM111" s="12"/>
+      <x:c r="AN111" s="23"/>
+      <x:c r="AO111" s="22"/>
+      <x:c r="AP111" s="22"/>
+      <x:c r="AQ111" s="24"/>
+      <x:c r="AR111" s="24"/>
+      <x:c r="AS111" s="22"/>
+      <x:c r="AT111" s="25"/>
+      <x:c r="AU111" s="25"/>
+      <x:c r="AV111" s="22"/>
+      <x:c r="AW111" s="22"/>
+      <x:c r="AX111" s="22"/>
+      <x:c r="AY111" s="22"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="12"/>
@@ -5180,6 +6607,18 @@
       <x:c r="AK112" s="12"/>
       <x:c r="AL112" s="12"/>
       <x:c r="AM112" s="12"/>
+      <x:c r="AN112" s="23"/>
+      <x:c r="AO112" s="22"/>
+      <x:c r="AP112" s="22"/>
+      <x:c r="AQ112" s="24"/>
+      <x:c r="AR112" s="24"/>
+      <x:c r="AS112" s="22"/>
+      <x:c r="AT112" s="25"/>
+      <x:c r="AU112" s="25"/>
+      <x:c r="AV112" s="22"/>
+      <x:c r="AW112" s="22"/>
+      <x:c r="AX112" s="22"/>
+      <x:c r="AY112" s="22"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="12"/>
@@ -5221,6 +6660,18 @@
       <x:c r="AK113" s="12"/>
       <x:c r="AL113" s="12"/>
       <x:c r="AM113" s="12"/>
+      <x:c r="AN113" s="23"/>
+      <x:c r="AO113" s="22"/>
+      <x:c r="AP113" s="22"/>
+      <x:c r="AQ113" s="24"/>
+      <x:c r="AR113" s="24"/>
+      <x:c r="AS113" s="22"/>
+      <x:c r="AT113" s="25"/>
+      <x:c r="AU113" s="25"/>
+      <x:c r="AV113" s="22"/>
+      <x:c r="AW113" s="22"/>
+      <x:c r="AX113" s="22"/>
+      <x:c r="AY113" s="22"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="12"/>
@@ -5262,6 +6713,18 @@
       <x:c r="AK114" s="12"/>
       <x:c r="AL114" s="12"/>
       <x:c r="AM114" s="12"/>
+      <x:c r="AN114" s="23"/>
+      <x:c r="AO114" s="22"/>
+      <x:c r="AP114" s="22"/>
+      <x:c r="AQ114" s="24"/>
+      <x:c r="AR114" s="24"/>
+      <x:c r="AS114" s="22"/>
+      <x:c r="AT114" s="25"/>
+      <x:c r="AU114" s="25"/>
+      <x:c r="AV114" s="22"/>
+      <x:c r="AW114" s="22"/>
+      <x:c r="AX114" s="22"/>
+      <x:c r="AY114" s="22"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="12"/>
@@ -5303,6 +6766,18 @@
       <x:c r="AK115" s="12"/>
       <x:c r="AL115" s="12"/>
       <x:c r="AM115" s="12"/>
+      <x:c r="AN115" s="23"/>
+      <x:c r="AO115" s="22"/>
+      <x:c r="AP115" s="22"/>
+      <x:c r="AQ115" s="24"/>
+      <x:c r="AR115" s="24"/>
+      <x:c r="AS115" s="22"/>
+      <x:c r="AT115" s="25"/>
+      <x:c r="AU115" s="25"/>
+      <x:c r="AV115" s="22"/>
+      <x:c r="AW115" s="22"/>
+      <x:c r="AX115" s="22"/>
+      <x:c r="AY115" s="22"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="12"/>
@@ -5344,6 +6819,18 @@
       <x:c r="AK116" s="12"/>
       <x:c r="AL116" s="12"/>
       <x:c r="AM116" s="12"/>
+      <x:c r="AN116" s="23"/>
+      <x:c r="AO116" s="22"/>
+      <x:c r="AP116" s="22"/>
+      <x:c r="AQ116" s="24"/>
+      <x:c r="AR116" s="24"/>
+      <x:c r="AS116" s="22"/>
+      <x:c r="AT116" s="25"/>
+      <x:c r="AU116" s="25"/>
+      <x:c r="AV116" s="22"/>
+      <x:c r="AW116" s="22"/>
+      <x:c r="AX116" s="22"/>
+      <x:c r="AY116" s="22"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="12"/>
@@ -5385,6 +6872,18 @@
       <x:c r="AK117" s="12"/>
       <x:c r="AL117" s="12"/>
       <x:c r="AM117" s="12"/>
+      <x:c r="AN117" s="23"/>
+      <x:c r="AO117" s="22"/>
+      <x:c r="AP117" s="22"/>
+      <x:c r="AQ117" s="24"/>
+      <x:c r="AR117" s="24"/>
+      <x:c r="AS117" s="22"/>
+      <x:c r="AT117" s="25"/>
+      <x:c r="AU117" s="25"/>
+      <x:c r="AV117" s="22"/>
+      <x:c r="AW117" s="22"/>
+      <x:c r="AX117" s="22"/>
+      <x:c r="AY117" s="22"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="12"/>
@@ -5426,6 +6925,18 @@
       <x:c r="AK118" s="12"/>
       <x:c r="AL118" s="12"/>
       <x:c r="AM118" s="12"/>
+      <x:c r="AN118" s="23"/>
+      <x:c r="AO118" s="22"/>
+      <x:c r="AP118" s="22"/>
+      <x:c r="AQ118" s="24"/>
+      <x:c r="AR118" s="24"/>
+      <x:c r="AS118" s="22"/>
+      <x:c r="AT118" s="25"/>
+      <x:c r="AU118" s="25"/>
+      <x:c r="AV118" s="22"/>
+      <x:c r="AW118" s="22"/>
+      <x:c r="AX118" s="22"/>
+      <x:c r="AY118" s="22"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="12"/>
@@ -5467,6 +6978,18 @@
       <x:c r="AK119" s="12"/>
       <x:c r="AL119" s="12"/>
       <x:c r="AM119" s="12"/>
+      <x:c r="AN119" s="23"/>
+      <x:c r="AO119" s="22"/>
+      <x:c r="AP119" s="22"/>
+      <x:c r="AQ119" s="24"/>
+      <x:c r="AR119" s="24"/>
+      <x:c r="AS119" s="22"/>
+      <x:c r="AT119" s="25"/>
+      <x:c r="AU119" s="25"/>
+      <x:c r="AV119" s="22"/>
+      <x:c r="AW119" s="22"/>
+      <x:c r="AX119" s="22"/>
+      <x:c r="AY119" s="22"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="12"/>
@@ -5508,6 +7031,18 @@
       <x:c r="AK120" s="12"/>
       <x:c r="AL120" s="12"/>
       <x:c r="AM120" s="12"/>
+      <x:c r="AN120" s="23"/>
+      <x:c r="AO120" s="22"/>
+      <x:c r="AP120" s="22"/>
+      <x:c r="AQ120" s="24"/>
+      <x:c r="AR120" s="24"/>
+      <x:c r="AS120" s="22"/>
+      <x:c r="AT120" s="25"/>
+      <x:c r="AU120" s="25"/>
+      <x:c r="AV120" s="22"/>
+      <x:c r="AW120" s="22"/>
+      <x:c r="AX120" s="22"/>
+      <x:c r="AY120" s="22"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="12"/>
@@ -5549,6 +7084,18 @@
       <x:c r="AK121" s="12"/>
       <x:c r="AL121" s="12"/>
       <x:c r="AM121" s="12"/>
+      <x:c r="AN121" s="23"/>
+      <x:c r="AO121" s="22"/>
+      <x:c r="AP121" s="22"/>
+      <x:c r="AQ121" s="24"/>
+      <x:c r="AR121" s="24"/>
+      <x:c r="AS121" s="22"/>
+      <x:c r="AT121" s="25"/>
+      <x:c r="AU121" s="25"/>
+      <x:c r="AV121" s="22"/>
+      <x:c r="AW121" s="22"/>
+      <x:c r="AX121" s="22"/>
+      <x:c r="AY121" s="22"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="12"/>
@@ -5590,6 +7137,18 @@
       <x:c r="AK122" s="12"/>
       <x:c r="AL122" s="12"/>
       <x:c r="AM122" s="12"/>
+      <x:c r="AN122" s="23"/>
+      <x:c r="AO122" s="22"/>
+      <x:c r="AP122" s="22"/>
+      <x:c r="AQ122" s="24"/>
+      <x:c r="AR122" s="24"/>
+      <x:c r="AS122" s="22"/>
+      <x:c r="AT122" s="25"/>
+      <x:c r="AU122" s="25"/>
+      <x:c r="AV122" s="22"/>
+      <x:c r="AW122" s="22"/>
+      <x:c r="AX122" s="22"/>
+      <x:c r="AY122" s="22"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="12"/>
@@ -5631,6 +7190,18 @@
       <x:c r="AK123" s="12"/>
       <x:c r="AL123" s="12"/>
       <x:c r="AM123" s="12"/>
+      <x:c r="AN123" s="23"/>
+      <x:c r="AO123" s="22"/>
+      <x:c r="AP123" s="22"/>
+      <x:c r="AQ123" s="24"/>
+      <x:c r="AR123" s="24"/>
+      <x:c r="AS123" s="22"/>
+      <x:c r="AT123" s="25"/>
+      <x:c r="AU123" s="25"/>
+      <x:c r="AV123" s="22"/>
+      <x:c r="AW123" s="22"/>
+      <x:c r="AX123" s="22"/>
+      <x:c r="AY123" s="22"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="12"/>
@@ -5672,6 +7243,18 @@
       <x:c r="AK124" s="12"/>
       <x:c r="AL124" s="12"/>
       <x:c r="AM124" s="12"/>
+      <x:c r="AN124" s="23"/>
+      <x:c r="AO124" s="22"/>
+      <x:c r="AP124" s="22"/>
+      <x:c r="AQ124" s="24"/>
+      <x:c r="AR124" s="24"/>
+      <x:c r="AS124" s="22"/>
+      <x:c r="AT124" s="25"/>
+      <x:c r="AU124" s="25"/>
+      <x:c r="AV124" s="22"/>
+      <x:c r="AW124" s="22"/>
+      <x:c r="AX124" s="22"/>
+      <x:c r="AY124" s="22"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="12"/>
@@ -5713,6 +7296,18 @@
       <x:c r="AK125" s="12"/>
       <x:c r="AL125" s="12"/>
       <x:c r="AM125" s="12"/>
+      <x:c r="AN125" s="23"/>
+      <x:c r="AO125" s="22"/>
+      <x:c r="AP125" s="22"/>
+      <x:c r="AQ125" s="24"/>
+      <x:c r="AR125" s="24"/>
+      <x:c r="AS125" s="22"/>
+      <x:c r="AT125" s="25"/>
+      <x:c r="AU125" s="25"/>
+      <x:c r="AV125" s="22"/>
+      <x:c r="AW125" s="22"/>
+      <x:c r="AX125" s="22"/>
+      <x:c r="AY125" s="22"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="12"/>
@@ -5754,6 +7349,18 @@
       <x:c r="AK126" s="12"/>
       <x:c r="AL126" s="12"/>
       <x:c r="AM126" s="12"/>
+      <x:c r="AN126" s="23"/>
+      <x:c r="AO126" s="22"/>
+      <x:c r="AP126" s="22"/>
+      <x:c r="AQ126" s="24"/>
+      <x:c r="AR126" s="24"/>
+      <x:c r="AS126" s="22"/>
+      <x:c r="AT126" s="25"/>
+      <x:c r="AU126" s="25"/>
+      <x:c r="AV126" s="22"/>
+      <x:c r="AW126" s="22"/>
+      <x:c r="AX126" s="22"/>
+      <x:c r="AY126" s="22"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="12"/>
@@ -5795,6 +7402,18 @@
       <x:c r="AK127" s="12"/>
       <x:c r="AL127" s="12"/>
       <x:c r="AM127" s="12"/>
+      <x:c r="AN127" s="23"/>
+      <x:c r="AO127" s="22"/>
+      <x:c r="AP127" s="22"/>
+      <x:c r="AQ127" s="24"/>
+      <x:c r="AR127" s="24"/>
+      <x:c r="AS127" s="22"/>
+      <x:c r="AT127" s="25"/>
+      <x:c r="AU127" s="25"/>
+      <x:c r="AV127" s="22"/>
+      <x:c r="AW127" s="22"/>
+      <x:c r="AX127" s="22"/>
+      <x:c r="AY127" s="22"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="12"/>
@@ -5836,6 +7455,18 @@
       <x:c r="AK128" s="12"/>
       <x:c r="AL128" s="12"/>
       <x:c r="AM128" s="12"/>
+      <x:c r="AN128" s="23"/>
+      <x:c r="AO128" s="22"/>
+      <x:c r="AP128" s="22"/>
+      <x:c r="AQ128" s="24"/>
+      <x:c r="AR128" s="24"/>
+      <x:c r="AS128" s="22"/>
+      <x:c r="AT128" s="25"/>
+      <x:c r="AU128" s="25"/>
+      <x:c r="AV128" s="22"/>
+      <x:c r="AW128" s="22"/>
+      <x:c r="AX128" s="22"/>
+      <x:c r="AY128" s="22"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="12"/>
@@ -5877,6 +7508,18 @@
       <x:c r="AK129" s="12"/>
       <x:c r="AL129" s="12"/>
       <x:c r="AM129" s="12"/>
+      <x:c r="AN129" s="23"/>
+      <x:c r="AO129" s="22"/>
+      <x:c r="AP129" s="22"/>
+      <x:c r="AQ129" s="24"/>
+      <x:c r="AR129" s="24"/>
+      <x:c r="AS129" s="22"/>
+      <x:c r="AT129" s="25"/>
+      <x:c r="AU129" s="25"/>
+      <x:c r="AV129" s="22"/>
+      <x:c r="AW129" s="22"/>
+      <x:c r="AX129" s="22"/>
+      <x:c r="AY129" s="22"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="12"/>
@@ -5918,6 +7561,18 @@
       <x:c r="AK130" s="12"/>
       <x:c r="AL130" s="12"/>
       <x:c r="AM130" s="12"/>
+      <x:c r="AN130" s="23"/>
+      <x:c r="AO130" s="22"/>
+      <x:c r="AP130" s="22"/>
+      <x:c r="AQ130" s="24"/>
+      <x:c r="AR130" s="24"/>
+      <x:c r="AS130" s="22"/>
+      <x:c r="AT130" s="25"/>
+      <x:c r="AU130" s="25"/>
+      <x:c r="AV130" s="22"/>
+      <x:c r="AW130" s="22"/>
+      <x:c r="AX130" s="22"/>
+      <x:c r="AY130" s="22"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="12"/>
@@ -5959,6 +7614,18 @@
       <x:c r="AK131" s="12"/>
       <x:c r="AL131" s="12"/>
       <x:c r="AM131" s="12"/>
+      <x:c r="AN131" s="23"/>
+      <x:c r="AO131" s="22"/>
+      <x:c r="AP131" s="22"/>
+      <x:c r="AQ131" s="24"/>
+      <x:c r="AR131" s="24"/>
+      <x:c r="AS131" s="22"/>
+      <x:c r="AT131" s="25"/>
+      <x:c r="AU131" s="25"/>
+      <x:c r="AV131" s="22"/>
+      <x:c r="AW131" s="22"/>
+      <x:c r="AX131" s="22"/>
+      <x:c r="AY131" s="22"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="12"/>
@@ -6000,6 +7667,18 @@
       <x:c r="AK132" s="12"/>
       <x:c r="AL132" s="12"/>
       <x:c r="AM132" s="12"/>
+      <x:c r="AN132" s="23"/>
+      <x:c r="AO132" s="22"/>
+      <x:c r="AP132" s="22"/>
+      <x:c r="AQ132" s="24"/>
+      <x:c r="AR132" s="24"/>
+      <x:c r="AS132" s="22"/>
+      <x:c r="AT132" s="25"/>
+      <x:c r="AU132" s="25"/>
+      <x:c r="AV132" s="22"/>
+      <x:c r="AW132" s="22"/>
+      <x:c r="AX132" s="22"/>
+      <x:c r="AY132" s="22"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="12"/>
@@ -6041,6 +7720,18 @@
       <x:c r="AK133" s="12"/>
       <x:c r="AL133" s="12"/>
       <x:c r="AM133" s="12"/>
+      <x:c r="AN133" s="23"/>
+      <x:c r="AO133" s="22"/>
+      <x:c r="AP133" s="22"/>
+      <x:c r="AQ133" s="24"/>
+      <x:c r="AR133" s="24"/>
+      <x:c r="AS133" s="22"/>
+      <x:c r="AT133" s="25"/>
+      <x:c r="AU133" s="25"/>
+      <x:c r="AV133" s="22"/>
+      <x:c r="AW133" s="22"/>
+      <x:c r="AX133" s="22"/>
+      <x:c r="AY133" s="22"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="12"/>
@@ -6082,6 +7773,18 @@
       <x:c r="AK134" s="12"/>
       <x:c r="AL134" s="12"/>
       <x:c r="AM134" s="12"/>
+      <x:c r="AN134" s="23"/>
+      <x:c r="AO134" s="22"/>
+      <x:c r="AP134" s="22"/>
+      <x:c r="AQ134" s="24"/>
+      <x:c r="AR134" s="24"/>
+      <x:c r="AS134" s="22"/>
+      <x:c r="AT134" s="25"/>
+      <x:c r="AU134" s="25"/>
+      <x:c r="AV134" s="22"/>
+      <x:c r="AW134" s="22"/>
+      <x:c r="AX134" s="22"/>
+      <x:c r="AY134" s="22"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="12"/>
@@ -6123,6 +7826,18 @@
       <x:c r="AK135" s="12"/>
       <x:c r="AL135" s="12"/>
       <x:c r="AM135" s="12"/>
+      <x:c r="AN135" s="23"/>
+      <x:c r="AO135" s="22"/>
+      <x:c r="AP135" s="22"/>
+      <x:c r="AQ135" s="24"/>
+      <x:c r="AR135" s="24"/>
+      <x:c r="AS135" s="22"/>
+      <x:c r="AT135" s="25"/>
+      <x:c r="AU135" s="25"/>
+      <x:c r="AV135" s="22"/>
+      <x:c r="AW135" s="22"/>
+      <x:c r="AX135" s="22"/>
+      <x:c r="AY135" s="22"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="12"/>
@@ -6164,6 +7879,18 @@
       <x:c r="AK136" s="12"/>
       <x:c r="AL136" s="12"/>
       <x:c r="AM136" s="12"/>
+      <x:c r="AN136" s="23"/>
+      <x:c r="AO136" s="22"/>
+      <x:c r="AP136" s="22"/>
+      <x:c r="AQ136" s="24"/>
+      <x:c r="AR136" s="24"/>
+      <x:c r="AS136" s="22"/>
+      <x:c r="AT136" s="25"/>
+      <x:c r="AU136" s="25"/>
+      <x:c r="AV136" s="22"/>
+      <x:c r="AW136" s="22"/>
+      <x:c r="AX136" s="22"/>
+      <x:c r="AY136" s="22"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="12"/>
@@ -6205,6 +7932,18 @@
       <x:c r="AK137" s="12"/>
       <x:c r="AL137" s="12"/>
       <x:c r="AM137" s="12"/>
+      <x:c r="AN137" s="23"/>
+      <x:c r="AO137" s="22"/>
+      <x:c r="AP137" s="22"/>
+      <x:c r="AQ137" s="24"/>
+      <x:c r="AR137" s="24"/>
+      <x:c r="AS137" s="22"/>
+      <x:c r="AT137" s="25"/>
+      <x:c r="AU137" s="25"/>
+      <x:c r="AV137" s="22"/>
+      <x:c r="AW137" s="22"/>
+      <x:c r="AX137" s="22"/>
+      <x:c r="AY137" s="22"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="12"/>
@@ -6246,6 +7985,18 @@
       <x:c r="AK138" s="12"/>
       <x:c r="AL138" s="12"/>
       <x:c r="AM138" s="12"/>
+      <x:c r="AN138" s="23"/>
+      <x:c r="AO138" s="22"/>
+      <x:c r="AP138" s="22"/>
+      <x:c r="AQ138" s="24"/>
+      <x:c r="AR138" s="24"/>
+      <x:c r="AS138" s="22"/>
+      <x:c r="AT138" s="25"/>
+      <x:c r="AU138" s="25"/>
+      <x:c r="AV138" s="22"/>
+      <x:c r="AW138" s="22"/>
+      <x:c r="AX138" s="22"/>
+      <x:c r="AY138" s="22"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="12"/>
@@ -6287,6 +8038,18 @@
       <x:c r="AK139" s="12"/>
       <x:c r="AL139" s="12"/>
       <x:c r="AM139" s="12"/>
+      <x:c r="AN139" s="23"/>
+      <x:c r="AO139" s="22"/>
+      <x:c r="AP139" s="22"/>
+      <x:c r="AQ139" s="24"/>
+      <x:c r="AR139" s="24"/>
+      <x:c r="AS139" s="22"/>
+      <x:c r="AT139" s="25"/>
+      <x:c r="AU139" s="25"/>
+      <x:c r="AV139" s="22"/>
+      <x:c r="AW139" s="22"/>
+      <x:c r="AX139" s="22"/>
+      <x:c r="AY139" s="22"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="12"/>
@@ -6328,6 +8091,18 @@
       <x:c r="AK140" s="12"/>
       <x:c r="AL140" s="12"/>
       <x:c r="AM140" s="12"/>
+      <x:c r="AN140" s="23"/>
+      <x:c r="AO140" s="22"/>
+      <x:c r="AP140" s="22"/>
+      <x:c r="AQ140" s="24"/>
+      <x:c r="AR140" s="24"/>
+      <x:c r="AS140" s="22"/>
+      <x:c r="AT140" s="25"/>
+      <x:c r="AU140" s="25"/>
+      <x:c r="AV140" s="22"/>
+      <x:c r="AW140" s="22"/>
+      <x:c r="AX140" s="22"/>
+      <x:c r="AY140" s="22"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="12"/>
@@ -6369,6 +8144,18 @@
       <x:c r="AK141" s="12"/>
       <x:c r="AL141" s="12"/>
       <x:c r="AM141" s="12"/>
+      <x:c r="AN141" s="23"/>
+      <x:c r="AO141" s="22"/>
+      <x:c r="AP141" s="22"/>
+      <x:c r="AQ141" s="24"/>
+      <x:c r="AR141" s="24"/>
+      <x:c r="AS141" s="22"/>
+      <x:c r="AT141" s="25"/>
+      <x:c r="AU141" s="25"/>
+      <x:c r="AV141" s="22"/>
+      <x:c r="AW141" s="22"/>
+      <x:c r="AX141" s="22"/>
+      <x:c r="AY141" s="22"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="12"/>
@@ -6410,6 +8197,18 @@
       <x:c r="AK142" s="12"/>
       <x:c r="AL142" s="12"/>
       <x:c r="AM142" s="12"/>
+      <x:c r="AN142" s="23"/>
+      <x:c r="AO142" s="22"/>
+      <x:c r="AP142" s="22"/>
+      <x:c r="AQ142" s="24"/>
+      <x:c r="AR142" s="24"/>
+      <x:c r="AS142" s="22"/>
+      <x:c r="AT142" s="25"/>
+      <x:c r="AU142" s="25"/>
+      <x:c r="AV142" s="22"/>
+      <x:c r="AW142" s="22"/>
+      <x:c r="AX142" s="22"/>
+      <x:c r="AY142" s="22"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="12"/>
@@ -6451,6 +8250,18 @@
       <x:c r="AK143" s="12"/>
       <x:c r="AL143" s="12"/>
       <x:c r="AM143" s="12"/>
+      <x:c r="AN143" s="23"/>
+      <x:c r="AO143" s="22"/>
+      <x:c r="AP143" s="22"/>
+      <x:c r="AQ143" s="24"/>
+      <x:c r="AR143" s="24"/>
+      <x:c r="AS143" s="22"/>
+      <x:c r="AT143" s="25"/>
+      <x:c r="AU143" s="25"/>
+      <x:c r="AV143" s="22"/>
+      <x:c r="AW143" s="22"/>
+      <x:c r="AX143" s="22"/>
+      <x:c r="AY143" s="22"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="12"/>
@@ -6492,6 +8303,18 @@
       <x:c r="AK144" s="12"/>
       <x:c r="AL144" s="12"/>
       <x:c r="AM144" s="12"/>
+      <x:c r="AN144" s="23"/>
+      <x:c r="AO144" s="22"/>
+      <x:c r="AP144" s="22"/>
+      <x:c r="AQ144" s="24"/>
+      <x:c r="AR144" s="24"/>
+      <x:c r="AS144" s="22"/>
+      <x:c r="AT144" s="25"/>
+      <x:c r="AU144" s="25"/>
+      <x:c r="AV144" s="22"/>
+      <x:c r="AW144" s="22"/>
+      <x:c r="AX144" s="22"/>
+      <x:c r="AY144" s="22"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="12"/>
@@ -6533,6 +8356,18 @@
       <x:c r="AK145" s="12"/>
       <x:c r="AL145" s="12"/>
       <x:c r="AM145" s="12"/>
+      <x:c r="AN145" s="23"/>
+      <x:c r="AO145" s="22"/>
+      <x:c r="AP145" s="22"/>
+      <x:c r="AQ145" s="24"/>
+      <x:c r="AR145" s="24"/>
+      <x:c r="AS145" s="22"/>
+      <x:c r="AT145" s="25"/>
+      <x:c r="AU145" s="25"/>
+      <x:c r="AV145" s="22"/>
+      <x:c r="AW145" s="22"/>
+      <x:c r="AX145" s="22"/>
+      <x:c r="AY145" s="22"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="12"/>
@@ -6574,6 +8409,18 @@
       <x:c r="AK146" s="12"/>
       <x:c r="AL146" s="12"/>
       <x:c r="AM146" s="12"/>
+      <x:c r="AN146" s="23"/>
+      <x:c r="AO146" s="22"/>
+      <x:c r="AP146" s="22"/>
+      <x:c r="AQ146" s="24"/>
+      <x:c r="AR146" s="24"/>
+      <x:c r="AS146" s="22"/>
+      <x:c r="AT146" s="25"/>
+      <x:c r="AU146" s="25"/>
+      <x:c r="AV146" s="22"/>
+      <x:c r="AW146" s="22"/>
+      <x:c r="AX146" s="22"/>
+      <x:c r="AY146" s="22"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="12"/>
@@ -6615,6 +8462,18 @@
       <x:c r="AK147" s="12"/>
       <x:c r="AL147" s="12"/>
       <x:c r="AM147" s="12"/>
+      <x:c r="AN147" s="23"/>
+      <x:c r="AO147" s="22"/>
+      <x:c r="AP147" s="22"/>
+      <x:c r="AQ147" s="24"/>
+      <x:c r="AR147" s="24"/>
+      <x:c r="AS147" s="22"/>
+      <x:c r="AT147" s="25"/>
+      <x:c r="AU147" s="25"/>
+      <x:c r="AV147" s="22"/>
+      <x:c r="AW147" s="22"/>
+      <x:c r="AX147" s="22"/>
+      <x:c r="AY147" s="22"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="12"/>
@@ -6656,6 +8515,18 @@
       <x:c r="AK148" s="12"/>
       <x:c r="AL148" s="12"/>
       <x:c r="AM148" s="12"/>
+      <x:c r="AN148" s="23"/>
+      <x:c r="AO148" s="22"/>
+      <x:c r="AP148" s="22"/>
+      <x:c r="AQ148" s="24"/>
+      <x:c r="AR148" s="24"/>
+      <x:c r="AS148" s="22"/>
+      <x:c r="AT148" s="25"/>
+      <x:c r="AU148" s="25"/>
+      <x:c r="AV148" s="22"/>
+      <x:c r="AW148" s="22"/>
+      <x:c r="AX148" s="22"/>
+      <x:c r="AY148" s="22"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="12"/>
@@ -6697,6 +8568,18 @@
       <x:c r="AK149" s="12"/>
       <x:c r="AL149" s="12"/>
       <x:c r="AM149" s="12"/>
+      <x:c r="AN149" s="23"/>
+      <x:c r="AO149" s="22"/>
+      <x:c r="AP149" s="22"/>
+      <x:c r="AQ149" s="24"/>
+      <x:c r="AR149" s="24"/>
+      <x:c r="AS149" s="22"/>
+      <x:c r="AT149" s="25"/>
+      <x:c r="AU149" s="25"/>
+      <x:c r="AV149" s="22"/>
+      <x:c r="AW149" s="22"/>
+      <x:c r="AX149" s="22"/>
+      <x:c r="AY149" s="22"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="12"/>
@@ -6738,6 +8621,18 @@
       <x:c r="AK150" s="12"/>
       <x:c r="AL150" s="12"/>
       <x:c r="AM150" s="12"/>
+      <x:c r="AN150" s="23"/>
+      <x:c r="AO150" s="22"/>
+      <x:c r="AP150" s="22"/>
+      <x:c r="AQ150" s="24"/>
+      <x:c r="AR150" s="24"/>
+      <x:c r="AS150" s="22"/>
+      <x:c r="AT150" s="25"/>
+      <x:c r="AU150" s="25"/>
+      <x:c r="AV150" s="22"/>
+      <x:c r="AW150" s="22"/>
+      <x:c r="AX150" s="22"/>
+      <x:c r="AY150" s="22"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="12"/>
@@ -6779,6 +8674,18 @@
       <x:c r="AK151" s="12"/>
       <x:c r="AL151" s="12"/>
       <x:c r="AM151" s="12"/>
+      <x:c r="AN151" s="23"/>
+      <x:c r="AO151" s="22"/>
+      <x:c r="AP151" s="22"/>
+      <x:c r="AQ151" s="24"/>
+      <x:c r="AR151" s="24"/>
+      <x:c r="AS151" s="22"/>
+      <x:c r="AT151" s="25"/>
+      <x:c r="AU151" s="25"/>
+      <x:c r="AV151" s="22"/>
+      <x:c r="AW151" s="22"/>
+      <x:c r="AX151" s="22"/>
+      <x:c r="AY151" s="22"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="12"/>
@@ -6820,6 +8727,18 @@
       <x:c r="AK152" s="12"/>
       <x:c r="AL152" s="12"/>
       <x:c r="AM152" s="12"/>
+      <x:c r="AN152" s="23"/>
+      <x:c r="AO152" s="22"/>
+      <x:c r="AP152" s="22"/>
+      <x:c r="AQ152" s="24"/>
+      <x:c r="AR152" s="24"/>
+      <x:c r="AS152" s="22"/>
+      <x:c r="AT152" s="25"/>
+      <x:c r="AU152" s="25"/>
+      <x:c r="AV152" s="22"/>
+      <x:c r="AW152" s="22"/>
+      <x:c r="AX152" s="22"/>
+      <x:c r="AY152" s="22"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="12"/>
@@ -6861,6 +8780,18 @@
       <x:c r="AK153" s="12"/>
       <x:c r="AL153" s="12"/>
       <x:c r="AM153" s="12"/>
+      <x:c r="AN153" s="23"/>
+      <x:c r="AO153" s="22"/>
+      <x:c r="AP153" s="22"/>
+      <x:c r="AQ153" s="24"/>
+      <x:c r="AR153" s="24"/>
+      <x:c r="AS153" s="22"/>
+      <x:c r="AT153" s="25"/>
+      <x:c r="AU153" s="25"/>
+      <x:c r="AV153" s="22"/>
+      <x:c r="AW153" s="22"/>
+      <x:c r="AX153" s="22"/>
+      <x:c r="AY153" s="22"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="12"/>
@@ -6902,6 +8833,18 @@
       <x:c r="AK154" s="12"/>
       <x:c r="AL154" s="12"/>
       <x:c r="AM154" s="12"/>
+      <x:c r="AN154" s="23"/>
+      <x:c r="AO154" s="22"/>
+      <x:c r="AP154" s="22"/>
+      <x:c r="AQ154" s="24"/>
+      <x:c r="AR154" s="24"/>
+      <x:c r="AS154" s="22"/>
+      <x:c r="AT154" s="25"/>
+      <x:c r="AU154" s="25"/>
+      <x:c r="AV154" s="22"/>
+      <x:c r="AW154" s="22"/>
+      <x:c r="AX154" s="22"/>
+      <x:c r="AY154" s="22"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="12"/>
@@ -6943,6 +8886,18 @@
       <x:c r="AK155" s="12"/>
       <x:c r="AL155" s="12"/>
       <x:c r="AM155" s="12"/>
+      <x:c r="AN155" s="23"/>
+      <x:c r="AO155" s="22"/>
+      <x:c r="AP155" s="22"/>
+      <x:c r="AQ155" s="24"/>
+      <x:c r="AR155" s="24"/>
+      <x:c r="AS155" s="22"/>
+      <x:c r="AT155" s="25"/>
+      <x:c r="AU155" s="25"/>
+      <x:c r="AV155" s="22"/>
+      <x:c r="AW155" s="22"/>
+      <x:c r="AX155" s="22"/>
+      <x:c r="AY155" s="22"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="12"/>
@@ -6984,6 +8939,18 @@
       <x:c r="AK156" s="12"/>
       <x:c r="AL156" s="12"/>
       <x:c r="AM156" s="12"/>
+      <x:c r="AN156" s="23"/>
+      <x:c r="AO156" s="22"/>
+      <x:c r="AP156" s="22"/>
+      <x:c r="AQ156" s="24"/>
+      <x:c r="AR156" s="24"/>
+      <x:c r="AS156" s="22"/>
+      <x:c r="AT156" s="25"/>
+      <x:c r="AU156" s="25"/>
+      <x:c r="AV156" s="22"/>
+      <x:c r="AW156" s="22"/>
+      <x:c r="AX156" s="22"/>
+      <x:c r="AY156" s="22"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="12"/>
@@ -7025,6 +8992,18 @@
       <x:c r="AK157" s="12"/>
       <x:c r="AL157" s="12"/>
       <x:c r="AM157" s="12"/>
+      <x:c r="AN157" s="23"/>
+      <x:c r="AO157" s="22"/>
+      <x:c r="AP157" s="22"/>
+      <x:c r="AQ157" s="24"/>
+      <x:c r="AR157" s="24"/>
+      <x:c r="AS157" s="22"/>
+      <x:c r="AT157" s="25"/>
+      <x:c r="AU157" s="25"/>
+      <x:c r="AV157" s="22"/>
+      <x:c r="AW157" s="22"/>
+      <x:c r="AX157" s="22"/>
+      <x:c r="AY157" s="22"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="12"/>
@@ -7066,6 +9045,18 @@
       <x:c r="AK158" s="12"/>
       <x:c r="AL158" s="12"/>
       <x:c r="AM158" s="12"/>
+      <x:c r="AN158" s="23"/>
+      <x:c r="AO158" s="22"/>
+      <x:c r="AP158" s="22"/>
+      <x:c r="AQ158" s="24"/>
+      <x:c r="AR158" s="24"/>
+      <x:c r="AS158" s="22"/>
+      <x:c r="AT158" s="25"/>
+      <x:c r="AU158" s="25"/>
+      <x:c r="AV158" s="22"/>
+      <x:c r="AW158" s="22"/>
+      <x:c r="AX158" s="22"/>
+      <x:c r="AY158" s="22"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="12"/>
@@ -7107,6 +9098,18 @@
       <x:c r="AK159" s="12"/>
       <x:c r="AL159" s="12"/>
       <x:c r="AM159" s="12"/>
+      <x:c r="AN159" s="23"/>
+      <x:c r="AO159" s="22"/>
+      <x:c r="AP159" s="22"/>
+      <x:c r="AQ159" s="24"/>
+      <x:c r="AR159" s="24"/>
+      <x:c r="AS159" s="22"/>
+      <x:c r="AT159" s="25"/>
+      <x:c r="AU159" s="25"/>
+      <x:c r="AV159" s="22"/>
+      <x:c r="AW159" s="22"/>
+      <x:c r="AX159" s="22"/>
+      <x:c r="AY159" s="22"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="12"/>
@@ -7148,6 +9151,18 @@
       <x:c r="AK160" s="12"/>
       <x:c r="AL160" s="12"/>
       <x:c r="AM160" s="12"/>
+      <x:c r="AN160" s="23"/>
+      <x:c r="AO160" s="22"/>
+      <x:c r="AP160" s="22"/>
+      <x:c r="AQ160" s="24"/>
+      <x:c r="AR160" s="24"/>
+      <x:c r="AS160" s="22"/>
+      <x:c r="AT160" s="25"/>
+      <x:c r="AU160" s="25"/>
+      <x:c r="AV160" s="22"/>
+      <x:c r="AW160" s="22"/>
+      <x:c r="AX160" s="22"/>
+      <x:c r="AY160" s="22"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="12"/>
@@ -7189,6 +9204,18 @@
       <x:c r="AK161" s="12"/>
       <x:c r="AL161" s="12"/>
       <x:c r="AM161" s="12"/>
+      <x:c r="AN161" s="23"/>
+      <x:c r="AO161" s="22"/>
+      <x:c r="AP161" s="22"/>
+      <x:c r="AQ161" s="24"/>
+      <x:c r="AR161" s="24"/>
+      <x:c r="AS161" s="22"/>
+      <x:c r="AT161" s="25"/>
+      <x:c r="AU161" s="25"/>
+      <x:c r="AV161" s="22"/>
+      <x:c r="AW161" s="22"/>
+      <x:c r="AX161" s="22"/>
+      <x:c r="AY161" s="22"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="12"/>
@@ -7230,6 +9257,18 @@
       <x:c r="AK162" s="12"/>
       <x:c r="AL162" s="12"/>
       <x:c r="AM162" s="12"/>
+      <x:c r="AN162" s="23"/>
+      <x:c r="AO162" s="22"/>
+      <x:c r="AP162" s="22"/>
+      <x:c r="AQ162" s="24"/>
+      <x:c r="AR162" s="24"/>
+      <x:c r="AS162" s="22"/>
+      <x:c r="AT162" s="25"/>
+      <x:c r="AU162" s="25"/>
+      <x:c r="AV162" s="22"/>
+      <x:c r="AW162" s="22"/>
+      <x:c r="AX162" s="22"/>
+      <x:c r="AY162" s="22"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="12"/>
@@ -7271,6 +9310,18 @@
       <x:c r="AK163" s="12"/>
       <x:c r="AL163" s="12"/>
       <x:c r="AM163" s="12"/>
+      <x:c r="AN163" s="23"/>
+      <x:c r="AO163" s="22"/>
+      <x:c r="AP163" s="22"/>
+      <x:c r="AQ163" s="24"/>
+      <x:c r="AR163" s="24"/>
+      <x:c r="AS163" s="22"/>
+      <x:c r="AT163" s="25"/>
+      <x:c r="AU163" s="25"/>
+      <x:c r="AV163" s="22"/>
+      <x:c r="AW163" s="22"/>
+      <x:c r="AX163" s="22"/>
+      <x:c r="AY163" s="22"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="12"/>
@@ -7312,6 +9363,18 @@
       <x:c r="AK164" s="12"/>
       <x:c r="AL164" s="12"/>
       <x:c r="AM164" s="12"/>
+      <x:c r="AN164" s="23"/>
+      <x:c r="AO164" s="22"/>
+      <x:c r="AP164" s="22"/>
+      <x:c r="AQ164" s="24"/>
+      <x:c r="AR164" s="24"/>
+      <x:c r="AS164" s="22"/>
+      <x:c r="AT164" s="25"/>
+      <x:c r="AU164" s="25"/>
+      <x:c r="AV164" s="22"/>
+      <x:c r="AW164" s="22"/>
+      <x:c r="AX164" s="22"/>
+      <x:c r="AY164" s="22"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="12"/>
@@ -7353,6 +9416,18 @@
       <x:c r="AK165" s="12"/>
       <x:c r="AL165" s="12"/>
       <x:c r="AM165" s="12"/>
+      <x:c r="AN165" s="23"/>
+      <x:c r="AO165" s="22"/>
+      <x:c r="AP165" s="22"/>
+      <x:c r="AQ165" s="24"/>
+      <x:c r="AR165" s="24"/>
+      <x:c r="AS165" s="22"/>
+      <x:c r="AT165" s="25"/>
+      <x:c r="AU165" s="25"/>
+      <x:c r="AV165" s="22"/>
+      <x:c r="AW165" s="22"/>
+      <x:c r="AX165" s="22"/>
+      <x:c r="AY165" s="22"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="12"/>
@@ -7394,6 +9469,18 @@
       <x:c r="AK166" s="12"/>
       <x:c r="AL166" s="12"/>
       <x:c r="AM166" s="12"/>
+      <x:c r="AN166" s="23"/>
+      <x:c r="AO166" s="22"/>
+      <x:c r="AP166" s="22"/>
+      <x:c r="AQ166" s="24"/>
+      <x:c r="AR166" s="24"/>
+      <x:c r="AS166" s="22"/>
+      <x:c r="AT166" s="25"/>
+      <x:c r="AU166" s="25"/>
+      <x:c r="AV166" s="22"/>
+      <x:c r="AW166" s="22"/>
+      <x:c r="AX166" s="22"/>
+      <x:c r="AY166" s="22"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="12"/>
@@ -7435,6 +9522,18 @@
       <x:c r="AK167" s="12"/>
       <x:c r="AL167" s="12"/>
       <x:c r="AM167" s="12"/>
+      <x:c r="AN167" s="23"/>
+      <x:c r="AO167" s="22"/>
+      <x:c r="AP167" s="22"/>
+      <x:c r="AQ167" s="24"/>
+      <x:c r="AR167" s="24"/>
+      <x:c r="AS167" s="22"/>
+      <x:c r="AT167" s="25"/>
+      <x:c r="AU167" s="25"/>
+      <x:c r="AV167" s="22"/>
+      <x:c r="AW167" s="22"/>
+      <x:c r="AX167" s="22"/>
+      <x:c r="AY167" s="22"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="12"/>
@@ -7476,6 +9575,18 @@
       <x:c r="AK168" s="12"/>
       <x:c r="AL168" s="12"/>
       <x:c r="AM168" s="12"/>
+      <x:c r="AN168" s="23"/>
+      <x:c r="AO168" s="22"/>
+      <x:c r="AP168" s="22"/>
+      <x:c r="AQ168" s="24"/>
+      <x:c r="AR168" s="24"/>
+      <x:c r="AS168" s="22"/>
+      <x:c r="AT168" s="25"/>
+      <x:c r="AU168" s="25"/>
+      <x:c r="AV168" s="22"/>
+      <x:c r="AW168" s="22"/>
+      <x:c r="AX168" s="22"/>
+      <x:c r="AY168" s="22"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="12"/>
@@ -7517,6 +9628,18 @@
       <x:c r="AK169" s="12"/>
       <x:c r="AL169" s="12"/>
       <x:c r="AM169" s="12"/>
+      <x:c r="AN169" s="23"/>
+      <x:c r="AO169" s="22"/>
+      <x:c r="AP169" s="22"/>
+      <x:c r="AQ169" s="24"/>
+      <x:c r="AR169" s="24"/>
+      <x:c r="AS169" s="22"/>
+      <x:c r="AT169" s="25"/>
+      <x:c r="AU169" s="25"/>
+      <x:c r="AV169" s="22"/>
+      <x:c r="AW169" s="22"/>
+      <x:c r="AX169" s="22"/>
+      <x:c r="AY169" s="22"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="12"/>
@@ -7558,6 +9681,18 @@
       <x:c r="AK170" s="12"/>
       <x:c r="AL170" s="12"/>
       <x:c r="AM170" s="12"/>
+      <x:c r="AN170" s="23"/>
+      <x:c r="AO170" s="22"/>
+      <x:c r="AP170" s="22"/>
+      <x:c r="AQ170" s="24"/>
+      <x:c r="AR170" s="24"/>
+      <x:c r="AS170" s="22"/>
+      <x:c r="AT170" s="25"/>
+      <x:c r="AU170" s="25"/>
+      <x:c r="AV170" s="22"/>
+      <x:c r="AW170" s="22"/>
+      <x:c r="AX170" s="22"/>
+      <x:c r="AY170" s="22"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="12"/>
@@ -7599,6 +9734,18 @@
       <x:c r="AK171" s="12"/>
       <x:c r="AL171" s="12"/>
       <x:c r="AM171" s="12"/>
+      <x:c r="AN171" s="23"/>
+      <x:c r="AO171" s="22"/>
+      <x:c r="AP171" s="22"/>
+      <x:c r="AQ171" s="24"/>
+      <x:c r="AR171" s="24"/>
+      <x:c r="AS171" s="22"/>
+      <x:c r="AT171" s="25"/>
+      <x:c r="AU171" s="25"/>
+      <x:c r="AV171" s="22"/>
+      <x:c r="AW171" s="22"/>
+      <x:c r="AX171" s="22"/>
+      <x:c r="AY171" s="22"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="12"/>
@@ -7640,6 +9787,18 @@
       <x:c r="AK172" s="12"/>
       <x:c r="AL172" s="12"/>
       <x:c r="AM172" s="12"/>
+      <x:c r="AN172" s="23"/>
+      <x:c r="AO172" s="22"/>
+      <x:c r="AP172" s="22"/>
+      <x:c r="AQ172" s="24"/>
+      <x:c r="AR172" s="24"/>
+      <x:c r="AS172" s="22"/>
+      <x:c r="AT172" s="25"/>
+      <x:c r="AU172" s="25"/>
+      <x:c r="AV172" s="22"/>
+      <x:c r="AW172" s="22"/>
+      <x:c r="AX172" s="22"/>
+      <x:c r="AY172" s="22"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="12"/>
@@ -7681,6 +9840,18 @@
       <x:c r="AK173" s="12"/>
       <x:c r="AL173" s="12"/>
       <x:c r="AM173" s="12"/>
+      <x:c r="AN173" s="23"/>
+      <x:c r="AO173" s="22"/>
+      <x:c r="AP173" s="22"/>
+      <x:c r="AQ173" s="24"/>
+      <x:c r="AR173" s="24"/>
+      <x:c r="AS173" s="22"/>
+      <x:c r="AT173" s="25"/>
+      <x:c r="AU173" s="25"/>
+      <x:c r="AV173" s="22"/>
+      <x:c r="AW173" s="22"/>
+      <x:c r="AX173" s="22"/>
+      <x:c r="AY173" s="22"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="12"/>
@@ -7722,6 +9893,18 @@
       <x:c r="AK174" s="12"/>
       <x:c r="AL174" s="12"/>
       <x:c r="AM174" s="12"/>
+      <x:c r="AN174" s="23"/>
+      <x:c r="AO174" s="22"/>
+      <x:c r="AP174" s="22"/>
+      <x:c r="AQ174" s="24"/>
+      <x:c r="AR174" s="24"/>
+      <x:c r="AS174" s="22"/>
+      <x:c r="AT174" s="25"/>
+      <x:c r="AU174" s="25"/>
+      <x:c r="AV174" s="22"/>
+      <x:c r="AW174" s="22"/>
+      <x:c r="AX174" s="22"/>
+      <x:c r="AY174" s="22"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="12"/>
@@ -7763,6 +9946,18 @@
       <x:c r="AK175" s="12"/>
       <x:c r="AL175" s="12"/>
       <x:c r="AM175" s="12"/>
+      <x:c r="AN175" s="23"/>
+      <x:c r="AO175" s="22"/>
+      <x:c r="AP175" s="22"/>
+      <x:c r="AQ175" s="24"/>
+      <x:c r="AR175" s="24"/>
+      <x:c r="AS175" s="22"/>
+      <x:c r="AT175" s="25"/>
+      <x:c r="AU175" s="25"/>
+      <x:c r="AV175" s="22"/>
+      <x:c r="AW175" s="22"/>
+      <x:c r="AX175" s="22"/>
+      <x:c r="AY175" s="22"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="12"/>
@@ -7804,6 +9999,18 @@
       <x:c r="AK176" s="12"/>
       <x:c r="AL176" s="12"/>
       <x:c r="AM176" s="12"/>
+      <x:c r="AN176" s="23"/>
+      <x:c r="AO176" s="22"/>
+      <x:c r="AP176" s="22"/>
+      <x:c r="AQ176" s="24"/>
+      <x:c r="AR176" s="24"/>
+      <x:c r="AS176" s="22"/>
+      <x:c r="AT176" s="25"/>
+      <x:c r="AU176" s="25"/>
+      <x:c r="AV176" s="22"/>
+      <x:c r="AW176" s="22"/>
+      <x:c r="AX176" s="22"/>
+      <x:c r="AY176" s="22"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="12"/>
@@ -7845,6 +10052,18 @@
       <x:c r="AK177" s="12"/>
       <x:c r="AL177" s="12"/>
       <x:c r="AM177" s="12"/>
+      <x:c r="AN177" s="23"/>
+      <x:c r="AO177" s="22"/>
+      <x:c r="AP177" s="22"/>
+      <x:c r="AQ177" s="24"/>
+      <x:c r="AR177" s="24"/>
+      <x:c r="AS177" s="22"/>
+      <x:c r="AT177" s="25"/>
+      <x:c r="AU177" s="25"/>
+      <x:c r="AV177" s="22"/>
+      <x:c r="AW177" s="22"/>
+      <x:c r="AX177" s="22"/>
+      <x:c r="AY177" s="22"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="12"/>
@@ -7886,6 +10105,18 @@
       <x:c r="AK178" s="12"/>
       <x:c r="AL178" s="12"/>
       <x:c r="AM178" s="12"/>
+      <x:c r="AN178" s="23"/>
+      <x:c r="AO178" s="22"/>
+      <x:c r="AP178" s="22"/>
+      <x:c r="AQ178" s="24"/>
+      <x:c r="AR178" s="24"/>
+      <x:c r="AS178" s="22"/>
+      <x:c r="AT178" s="25"/>
+      <x:c r="AU178" s="25"/>
+      <x:c r="AV178" s="22"/>
+      <x:c r="AW178" s="22"/>
+      <x:c r="AX178" s="22"/>
+      <x:c r="AY178" s="22"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="12"/>
@@ -7927,6 +10158,18 @@
       <x:c r="AK179" s="12"/>
       <x:c r="AL179" s="12"/>
       <x:c r="AM179" s="12"/>
+      <x:c r="AN179" s="23"/>
+      <x:c r="AO179" s="22"/>
+      <x:c r="AP179" s="22"/>
+      <x:c r="AQ179" s="24"/>
+      <x:c r="AR179" s="24"/>
+      <x:c r="AS179" s="22"/>
+      <x:c r="AT179" s="25"/>
+      <x:c r="AU179" s="25"/>
+      <x:c r="AV179" s="22"/>
+      <x:c r="AW179" s="22"/>
+      <x:c r="AX179" s="22"/>
+      <x:c r="AY179" s="22"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="12"/>
@@ -7968,6 +10211,18 @@
       <x:c r="AK180" s="12"/>
       <x:c r="AL180" s="12"/>
       <x:c r="AM180" s="12"/>
+      <x:c r="AN180" s="23"/>
+      <x:c r="AO180" s="22"/>
+      <x:c r="AP180" s="22"/>
+      <x:c r="AQ180" s="24"/>
+      <x:c r="AR180" s="24"/>
+      <x:c r="AS180" s="22"/>
+      <x:c r="AT180" s="25"/>
+      <x:c r="AU180" s="25"/>
+      <x:c r="AV180" s="22"/>
+      <x:c r="AW180" s="22"/>
+      <x:c r="AX180" s="22"/>
+      <x:c r="AY180" s="22"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="12"/>
@@ -8009,6 +10264,18 @@
       <x:c r="AK181" s="12"/>
       <x:c r="AL181" s="12"/>
       <x:c r="AM181" s="12"/>
+      <x:c r="AN181" s="23"/>
+      <x:c r="AO181" s="22"/>
+      <x:c r="AP181" s="22"/>
+      <x:c r="AQ181" s="24"/>
+      <x:c r="AR181" s="24"/>
+      <x:c r="AS181" s="22"/>
+      <x:c r="AT181" s="25"/>
+      <x:c r="AU181" s="25"/>
+      <x:c r="AV181" s="22"/>
+      <x:c r="AW181" s="22"/>
+      <x:c r="AX181" s="22"/>
+      <x:c r="AY181" s="22"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="12"/>
@@ -8050,6 +10317,18 @@
       <x:c r="AK182" s="12"/>
       <x:c r="AL182" s="12"/>
       <x:c r="AM182" s="12"/>
+      <x:c r="AN182" s="23"/>
+      <x:c r="AO182" s="22"/>
+      <x:c r="AP182" s="22"/>
+      <x:c r="AQ182" s="24"/>
+      <x:c r="AR182" s="24"/>
+      <x:c r="AS182" s="22"/>
+      <x:c r="AT182" s="25"/>
+      <x:c r="AU182" s="25"/>
+      <x:c r="AV182" s="22"/>
+      <x:c r="AW182" s="22"/>
+      <x:c r="AX182" s="22"/>
+      <x:c r="AY182" s="22"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="12"/>
@@ -8091,6 +10370,18 @@
       <x:c r="AK183" s="12"/>
       <x:c r="AL183" s="12"/>
       <x:c r="AM183" s="12"/>
+      <x:c r="AN183" s="23"/>
+      <x:c r="AO183" s="22"/>
+      <x:c r="AP183" s="22"/>
+      <x:c r="AQ183" s="24"/>
+      <x:c r="AR183" s="24"/>
+      <x:c r="AS183" s="22"/>
+      <x:c r="AT183" s="25"/>
+      <x:c r="AU183" s="25"/>
+      <x:c r="AV183" s="22"/>
+      <x:c r="AW183" s="22"/>
+      <x:c r="AX183" s="22"/>
+      <x:c r="AY183" s="22"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="12"/>
@@ -8132,6 +10423,18 @@
       <x:c r="AK184" s="12"/>
       <x:c r="AL184" s="12"/>
       <x:c r="AM184" s="12"/>
+      <x:c r="AN184" s="23"/>
+      <x:c r="AO184" s="22"/>
+      <x:c r="AP184" s="22"/>
+      <x:c r="AQ184" s="24"/>
+      <x:c r="AR184" s="24"/>
+      <x:c r="AS184" s="22"/>
+      <x:c r="AT184" s="25"/>
+      <x:c r="AU184" s="25"/>
+      <x:c r="AV184" s="22"/>
+      <x:c r="AW184" s="22"/>
+      <x:c r="AX184" s="22"/>
+      <x:c r="AY184" s="22"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="12"/>
@@ -8173,6 +10476,18 @@
       <x:c r="AK185" s="12"/>
       <x:c r="AL185" s="12"/>
       <x:c r="AM185" s="12"/>
+      <x:c r="AN185" s="23"/>
+      <x:c r="AO185" s="22"/>
+      <x:c r="AP185" s="22"/>
+      <x:c r="AQ185" s="24"/>
+      <x:c r="AR185" s="24"/>
+      <x:c r="AS185" s="22"/>
+      <x:c r="AT185" s="25"/>
+      <x:c r="AU185" s="25"/>
+      <x:c r="AV185" s="22"/>
+      <x:c r="AW185" s="22"/>
+      <x:c r="AX185" s="22"/>
+      <x:c r="AY185" s="22"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="12"/>
@@ -8214,6 +10529,18 @@
       <x:c r="AK186" s="12"/>
       <x:c r="AL186" s="12"/>
       <x:c r="AM186" s="12"/>
+      <x:c r="AN186" s="23"/>
+      <x:c r="AO186" s="22"/>
+      <x:c r="AP186" s="22"/>
+      <x:c r="AQ186" s="24"/>
+      <x:c r="AR186" s="24"/>
+      <x:c r="AS186" s="22"/>
+      <x:c r="AT186" s="25"/>
+      <x:c r="AU186" s="25"/>
+      <x:c r="AV186" s="22"/>
+      <x:c r="AW186" s="22"/>
+      <x:c r="AX186" s="22"/>
+      <x:c r="AY186" s="22"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="12"/>
@@ -8255,6 +10582,18 @@
       <x:c r="AK187" s="12"/>
       <x:c r="AL187" s="12"/>
       <x:c r="AM187" s="12"/>
+      <x:c r="AN187" s="23"/>
+      <x:c r="AO187" s="22"/>
+      <x:c r="AP187" s="22"/>
+      <x:c r="AQ187" s="24"/>
+      <x:c r="AR187" s="24"/>
+      <x:c r="AS187" s="22"/>
+      <x:c r="AT187" s="25"/>
+      <x:c r="AU187" s="25"/>
+      <x:c r="AV187" s="22"/>
+      <x:c r="AW187" s="22"/>
+      <x:c r="AX187" s="22"/>
+      <x:c r="AY187" s="22"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="12"/>
@@ -8296,6 +10635,18 @@
       <x:c r="AK188" s="12"/>
       <x:c r="AL188" s="12"/>
       <x:c r="AM188" s="12"/>
+      <x:c r="AN188" s="23"/>
+      <x:c r="AO188" s="22"/>
+      <x:c r="AP188" s="22"/>
+      <x:c r="AQ188" s="24"/>
+      <x:c r="AR188" s="24"/>
+      <x:c r="AS188" s="22"/>
+      <x:c r="AT188" s="25"/>
+      <x:c r="AU188" s="25"/>
+      <x:c r="AV188" s="22"/>
+      <x:c r="AW188" s="22"/>
+      <x:c r="AX188" s="22"/>
+      <x:c r="AY188" s="22"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="12"/>
@@ -8337,6 +10688,18 @@
       <x:c r="AK189" s="12"/>
       <x:c r="AL189" s="12"/>
       <x:c r="AM189" s="12"/>
+      <x:c r="AN189" s="23"/>
+      <x:c r="AO189" s="22"/>
+      <x:c r="AP189" s="22"/>
+      <x:c r="AQ189" s="24"/>
+      <x:c r="AR189" s="24"/>
+      <x:c r="AS189" s="22"/>
+      <x:c r="AT189" s="25"/>
+      <x:c r="AU189" s="25"/>
+      <x:c r="AV189" s="22"/>
+      <x:c r="AW189" s="22"/>
+      <x:c r="AX189" s="22"/>
+      <x:c r="AY189" s="22"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="12"/>
@@ -8378,6 +10741,18 @@
       <x:c r="AK190" s="12"/>
       <x:c r="AL190" s="12"/>
       <x:c r="AM190" s="12"/>
+      <x:c r="AN190" s="23"/>
+      <x:c r="AO190" s="22"/>
+      <x:c r="AP190" s="22"/>
+      <x:c r="AQ190" s="24"/>
+      <x:c r="AR190" s="24"/>
+      <x:c r="AS190" s="22"/>
+      <x:c r="AT190" s="25"/>
+      <x:c r="AU190" s="25"/>
+      <x:c r="AV190" s="22"/>
+      <x:c r="AW190" s="22"/>
+      <x:c r="AX190" s="22"/>
+      <x:c r="AY190" s="22"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="12"/>
@@ -8419,6 +10794,18 @@
       <x:c r="AK191" s="12"/>
       <x:c r="AL191" s="12"/>
       <x:c r="AM191" s="12"/>
+      <x:c r="AN191" s="23"/>
+      <x:c r="AO191" s="22"/>
+      <x:c r="AP191" s="22"/>
+      <x:c r="AQ191" s="24"/>
+      <x:c r="AR191" s="24"/>
+      <x:c r="AS191" s="22"/>
+      <x:c r="AT191" s="25"/>
+      <x:c r="AU191" s="25"/>
+      <x:c r="AV191" s="22"/>
+      <x:c r="AW191" s="22"/>
+      <x:c r="AX191" s="22"/>
+      <x:c r="AY191" s="22"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="12"/>
@@ -8460,6 +10847,18 @@
       <x:c r="AK192" s="12"/>
       <x:c r="AL192" s="12"/>
       <x:c r="AM192" s="12"/>
+      <x:c r="AN192" s="23"/>
+      <x:c r="AO192" s="22"/>
+      <x:c r="AP192" s="22"/>
+      <x:c r="AQ192" s="24"/>
+      <x:c r="AR192" s="24"/>
+      <x:c r="AS192" s="22"/>
+      <x:c r="AT192" s="25"/>
+      <x:c r="AU192" s="25"/>
+      <x:c r="AV192" s="22"/>
+      <x:c r="AW192" s="22"/>
+      <x:c r="AX192" s="22"/>
+      <x:c r="AY192" s="22"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="12"/>
@@ -8501,6 +10900,18 @@
       <x:c r="AK193" s="12"/>
       <x:c r="AL193" s="12"/>
       <x:c r="AM193" s="12"/>
+      <x:c r="AN193" s="23"/>
+      <x:c r="AO193" s="22"/>
+      <x:c r="AP193" s="22"/>
+      <x:c r="AQ193" s="24"/>
+      <x:c r="AR193" s="24"/>
+      <x:c r="AS193" s="22"/>
+      <x:c r="AT193" s="25"/>
+      <x:c r="AU193" s="25"/>
+      <x:c r="AV193" s="22"/>
+      <x:c r="AW193" s="22"/>
+      <x:c r="AX193" s="22"/>
+      <x:c r="AY193" s="22"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="12"/>
@@ -8542,6 +10953,18 @@
       <x:c r="AK194" s="12"/>
       <x:c r="AL194" s="12"/>
       <x:c r="AM194" s="12"/>
+      <x:c r="AN194" s="23"/>
+      <x:c r="AO194" s="22"/>
+      <x:c r="AP194" s="22"/>
+      <x:c r="AQ194" s="24"/>
+      <x:c r="AR194" s="24"/>
+      <x:c r="AS194" s="22"/>
+      <x:c r="AT194" s="25"/>
+      <x:c r="AU194" s="25"/>
+      <x:c r="AV194" s="22"/>
+      <x:c r="AW194" s="22"/>
+      <x:c r="AX194" s="22"/>
+      <x:c r="AY194" s="22"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="12"/>
@@ -8583,6 +11006,18 @@
       <x:c r="AK195" s="12"/>
       <x:c r="AL195" s="12"/>
       <x:c r="AM195" s="12"/>
+      <x:c r="AN195" s="23"/>
+      <x:c r="AO195" s="22"/>
+      <x:c r="AP195" s="22"/>
+      <x:c r="AQ195" s="24"/>
+      <x:c r="AR195" s="24"/>
+      <x:c r="AS195" s="22"/>
+      <x:c r="AT195" s="25"/>
+      <x:c r="AU195" s="25"/>
+      <x:c r="AV195" s="22"/>
+      <x:c r="AW195" s="22"/>
+      <x:c r="AX195" s="22"/>
+      <x:c r="AY195" s="22"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="12"/>
@@ -8624,6 +11059,18 @@
       <x:c r="AK196" s="12"/>
       <x:c r="AL196" s="12"/>
       <x:c r="AM196" s="12"/>
+      <x:c r="AN196" s="23"/>
+      <x:c r="AO196" s="22"/>
+      <x:c r="AP196" s="22"/>
+      <x:c r="AQ196" s="24"/>
+      <x:c r="AR196" s="24"/>
+      <x:c r="AS196" s="22"/>
+      <x:c r="AT196" s="25"/>
+      <x:c r="AU196" s="25"/>
+      <x:c r="AV196" s="22"/>
+      <x:c r="AW196" s="22"/>
+      <x:c r="AX196" s="22"/>
+      <x:c r="AY196" s="22"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="12"/>
@@ -8665,6 +11112,18 @@
       <x:c r="AK197" s="12"/>
       <x:c r="AL197" s="12"/>
       <x:c r="AM197" s="12"/>
+      <x:c r="AN197" s="23"/>
+      <x:c r="AO197" s="22"/>
+      <x:c r="AP197" s="22"/>
+      <x:c r="AQ197" s="24"/>
+      <x:c r="AR197" s="24"/>
+      <x:c r="AS197" s="22"/>
+      <x:c r="AT197" s="25"/>
+      <x:c r="AU197" s="25"/>
+      <x:c r="AV197" s="22"/>
+      <x:c r="AW197" s="22"/>
+      <x:c r="AX197" s="22"/>
+      <x:c r="AY197" s="22"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="12"/>
@@ -8706,6 +11165,18 @@
       <x:c r="AK198" s="12"/>
       <x:c r="AL198" s="12"/>
       <x:c r="AM198" s="12"/>
+      <x:c r="AN198" s="23"/>
+      <x:c r="AO198" s="22"/>
+      <x:c r="AP198" s="22"/>
+      <x:c r="AQ198" s="24"/>
+      <x:c r="AR198" s="24"/>
+      <x:c r="AS198" s="22"/>
+      <x:c r="AT198" s="25"/>
+      <x:c r="AU198" s="25"/>
+      <x:c r="AV198" s="22"/>
+      <x:c r="AW198" s="22"/>
+      <x:c r="AX198" s="22"/>
+      <x:c r="AY198" s="22"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="12"/>
@@ -8747,6 +11218,18 @@
       <x:c r="AK199" s="12"/>
       <x:c r="AL199" s="12"/>
       <x:c r="AM199" s="12"/>
+      <x:c r="AN199" s="23"/>
+      <x:c r="AO199" s="22"/>
+      <x:c r="AP199" s="22"/>
+      <x:c r="AQ199" s="24"/>
+      <x:c r="AR199" s="24"/>
+      <x:c r="AS199" s="22"/>
+      <x:c r="AT199" s="25"/>
+      <x:c r="AU199" s="25"/>
+      <x:c r="AV199" s="22"/>
+      <x:c r="AW199" s="22"/>
+      <x:c r="AX199" s="22"/>
+      <x:c r="AY199" s="22"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="12"/>
@@ -8788,9 +11271,4221 @@
       <x:c r="AK200" s="12"/>
       <x:c r="AL200" s="12"/>
       <x:c r="AM200" s="12"/>
+      <x:c r="AN200" s="23"/>
+      <x:c r="AO200" s="22"/>
+      <x:c r="AP200" s="22"/>
+      <x:c r="AQ200" s="24"/>
+      <x:c r="AR200" s="24"/>
+      <x:c r="AS200" s="22"/>
+      <x:c r="AT200" s="25"/>
+      <x:c r="AU200" s="25"/>
+      <x:c r="AV200" s="22"/>
+      <x:c r="AW200" s="22"/>
+      <x:c r="AX200" s="22"/>
+      <x:c r="AY200" s="22"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="AN201" s="23"/>
+      <x:c r="AO201" s="22"/>
+      <x:c r="AP201" s="22"/>
+      <x:c r="AQ201" s="24"/>
+      <x:c r="AR201" s="24"/>
+      <x:c r="AS201" s="22"/>
+      <x:c r="AT201" s="25"/>
+      <x:c r="AU201" s="25"/>
+      <x:c r="AV201" s="22"/>
+      <x:c r="AW201" s="22"/>
+      <x:c r="AX201" s="22"/>
+      <x:c r="AY201" s="22"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="AN202" s="23"/>
+      <x:c r="AO202" s="22"/>
+      <x:c r="AP202" s="22"/>
+      <x:c r="AQ202" s="24"/>
+      <x:c r="AR202" s="24"/>
+      <x:c r="AS202" s="22"/>
+      <x:c r="AT202" s="25"/>
+      <x:c r="AU202" s="25"/>
+      <x:c r="AV202" s="22"/>
+      <x:c r="AW202" s="22"/>
+      <x:c r="AX202" s="22"/>
+      <x:c r="AY202" s="22"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="AN203" s="23"/>
+      <x:c r="AO203" s="22"/>
+      <x:c r="AP203" s="22"/>
+      <x:c r="AQ203" s="24"/>
+      <x:c r="AR203" s="24"/>
+      <x:c r="AS203" s="22"/>
+      <x:c r="AT203" s="25"/>
+      <x:c r="AU203" s="25"/>
+      <x:c r="AV203" s="22"/>
+      <x:c r="AW203" s="22"/>
+      <x:c r="AX203" s="22"/>
+      <x:c r="AY203" s="22"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="AN204" s="23"/>
+      <x:c r="AO204" s="22"/>
+      <x:c r="AP204" s="22"/>
+      <x:c r="AQ204" s="24"/>
+      <x:c r="AR204" s="24"/>
+      <x:c r="AS204" s="22"/>
+      <x:c r="AT204" s="25"/>
+      <x:c r="AU204" s="25"/>
+      <x:c r="AV204" s="22"/>
+      <x:c r="AW204" s="22"/>
+      <x:c r="AX204" s="22"/>
+      <x:c r="AY204" s="22"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="AN205" s="23"/>
+      <x:c r="AO205" s="22"/>
+      <x:c r="AP205" s="22"/>
+      <x:c r="AQ205" s="24"/>
+      <x:c r="AR205" s="24"/>
+      <x:c r="AS205" s="22"/>
+      <x:c r="AT205" s="25"/>
+      <x:c r="AU205" s="25"/>
+      <x:c r="AV205" s="22"/>
+      <x:c r="AW205" s="22"/>
+      <x:c r="AX205" s="22"/>
+      <x:c r="AY205" s="22"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="AN206" s="23"/>
+      <x:c r="AO206" s="22"/>
+      <x:c r="AP206" s="22"/>
+      <x:c r="AQ206" s="24"/>
+      <x:c r="AR206" s="24"/>
+      <x:c r="AS206" s="22"/>
+      <x:c r="AT206" s="25"/>
+      <x:c r="AU206" s="25"/>
+      <x:c r="AV206" s="22"/>
+      <x:c r="AW206" s="22"/>
+      <x:c r="AX206" s="22"/>
+      <x:c r="AY206" s="22"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="AN207" s="23"/>
+      <x:c r="AO207" s="22"/>
+      <x:c r="AP207" s="22"/>
+      <x:c r="AQ207" s="24"/>
+      <x:c r="AR207" s="24"/>
+      <x:c r="AS207" s="22"/>
+      <x:c r="AT207" s="25"/>
+      <x:c r="AU207" s="25"/>
+      <x:c r="AV207" s="22"/>
+      <x:c r="AW207" s="22"/>
+      <x:c r="AX207" s="22"/>
+      <x:c r="AY207" s="22"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="AN208" s="23"/>
+      <x:c r="AO208" s="22"/>
+      <x:c r="AP208" s="22"/>
+      <x:c r="AQ208" s="24"/>
+      <x:c r="AR208" s="24"/>
+      <x:c r="AS208" s="22"/>
+      <x:c r="AT208" s="25"/>
+      <x:c r="AU208" s="25"/>
+      <x:c r="AV208" s="22"/>
+      <x:c r="AW208" s="22"/>
+      <x:c r="AX208" s="22"/>
+      <x:c r="AY208" s="22"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="AN209" s="23"/>
+      <x:c r="AO209" s="22"/>
+      <x:c r="AP209" s="22"/>
+      <x:c r="AQ209" s="24"/>
+      <x:c r="AR209" s="24"/>
+      <x:c r="AS209" s="22"/>
+      <x:c r="AT209" s="25"/>
+      <x:c r="AU209" s="25"/>
+      <x:c r="AV209" s="22"/>
+      <x:c r="AW209" s="22"/>
+      <x:c r="AX209" s="22"/>
+      <x:c r="AY209" s="22"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="AN210" s="23"/>
+      <x:c r="AO210" s="22"/>
+      <x:c r="AP210" s="22"/>
+      <x:c r="AQ210" s="24"/>
+      <x:c r="AR210" s="24"/>
+      <x:c r="AS210" s="22"/>
+      <x:c r="AT210" s="25"/>
+      <x:c r="AU210" s="25"/>
+      <x:c r="AV210" s="22"/>
+      <x:c r="AW210" s="22"/>
+      <x:c r="AX210" s="22"/>
+      <x:c r="AY210" s="22"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="AN211" s="23"/>
+      <x:c r="AO211" s="22"/>
+      <x:c r="AP211" s="22"/>
+      <x:c r="AQ211" s="24"/>
+      <x:c r="AR211" s="24"/>
+      <x:c r="AS211" s="22"/>
+      <x:c r="AT211" s="25"/>
+      <x:c r="AU211" s="25"/>
+      <x:c r="AV211" s="22"/>
+      <x:c r="AW211" s="22"/>
+      <x:c r="AX211" s="22"/>
+      <x:c r="AY211" s="22"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="AN212" s="23"/>
+      <x:c r="AO212" s="22"/>
+      <x:c r="AP212" s="22"/>
+      <x:c r="AQ212" s="24"/>
+      <x:c r="AR212" s="24"/>
+      <x:c r="AS212" s="22"/>
+      <x:c r="AT212" s="25"/>
+      <x:c r="AU212" s="25"/>
+      <x:c r="AV212" s="22"/>
+      <x:c r="AW212" s="22"/>
+      <x:c r="AX212" s="22"/>
+      <x:c r="AY212" s="22"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="AN213" s="23"/>
+      <x:c r="AO213" s="22"/>
+      <x:c r="AP213" s="22"/>
+      <x:c r="AQ213" s="24"/>
+      <x:c r="AR213" s="24"/>
+      <x:c r="AS213" s="22"/>
+      <x:c r="AT213" s="25"/>
+      <x:c r="AU213" s="25"/>
+      <x:c r="AV213" s="22"/>
+      <x:c r="AW213" s="22"/>
+      <x:c r="AX213" s="22"/>
+      <x:c r="AY213" s="22"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="AN214" s="23"/>
+      <x:c r="AO214" s="22"/>
+      <x:c r="AP214" s="22"/>
+      <x:c r="AQ214" s="24"/>
+      <x:c r="AR214" s="24"/>
+      <x:c r="AS214" s="22"/>
+      <x:c r="AT214" s="25"/>
+      <x:c r="AU214" s="25"/>
+      <x:c r="AV214" s="22"/>
+      <x:c r="AW214" s="22"/>
+      <x:c r="AX214" s="22"/>
+      <x:c r="AY214" s="22"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="AN215" s="23"/>
+      <x:c r="AO215" s="22"/>
+      <x:c r="AP215" s="22"/>
+      <x:c r="AQ215" s="24"/>
+      <x:c r="AR215" s="24"/>
+      <x:c r="AS215" s="22"/>
+      <x:c r="AT215" s="25"/>
+      <x:c r="AU215" s="25"/>
+      <x:c r="AV215" s="22"/>
+      <x:c r="AW215" s="22"/>
+      <x:c r="AX215" s="22"/>
+      <x:c r="AY215" s="22"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="AN216" s="23"/>
+      <x:c r="AO216" s="22"/>
+      <x:c r="AP216" s="22"/>
+      <x:c r="AQ216" s="24"/>
+      <x:c r="AR216" s="24"/>
+      <x:c r="AS216" s="22"/>
+      <x:c r="AT216" s="25"/>
+      <x:c r="AU216" s="25"/>
+      <x:c r="AV216" s="22"/>
+      <x:c r="AW216" s="22"/>
+      <x:c r="AX216" s="22"/>
+      <x:c r="AY216" s="22"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="AN217" s="23"/>
+      <x:c r="AO217" s="22"/>
+      <x:c r="AP217" s="22"/>
+      <x:c r="AQ217" s="24"/>
+      <x:c r="AR217" s="24"/>
+      <x:c r="AS217" s="22"/>
+      <x:c r="AT217" s="25"/>
+      <x:c r="AU217" s="25"/>
+      <x:c r="AV217" s="22"/>
+      <x:c r="AW217" s="22"/>
+      <x:c r="AX217" s="22"/>
+      <x:c r="AY217" s="22"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="AN218" s="23"/>
+      <x:c r="AO218" s="22"/>
+      <x:c r="AP218" s="22"/>
+      <x:c r="AQ218" s="24"/>
+      <x:c r="AR218" s="24"/>
+      <x:c r="AS218" s="22"/>
+      <x:c r="AT218" s="25"/>
+      <x:c r="AU218" s="25"/>
+      <x:c r="AV218" s="22"/>
+      <x:c r="AW218" s="22"/>
+      <x:c r="AX218" s="22"/>
+      <x:c r="AY218" s="22"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="AN219" s="23"/>
+      <x:c r="AO219" s="22"/>
+      <x:c r="AP219" s="22"/>
+      <x:c r="AQ219" s="24"/>
+      <x:c r="AR219" s="24"/>
+      <x:c r="AS219" s="22"/>
+      <x:c r="AT219" s="25"/>
+      <x:c r="AU219" s="25"/>
+      <x:c r="AV219" s="22"/>
+      <x:c r="AW219" s="22"/>
+      <x:c r="AX219" s="22"/>
+      <x:c r="AY219" s="22"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="AN220" s="23"/>
+      <x:c r="AO220" s="22"/>
+      <x:c r="AP220" s="22"/>
+      <x:c r="AQ220" s="24"/>
+      <x:c r="AR220" s="24"/>
+      <x:c r="AS220" s="22"/>
+      <x:c r="AT220" s="25"/>
+      <x:c r="AU220" s="25"/>
+      <x:c r="AV220" s="22"/>
+      <x:c r="AW220" s="22"/>
+      <x:c r="AX220" s="22"/>
+      <x:c r="AY220" s="22"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="AN221" s="23"/>
+      <x:c r="AO221" s="22"/>
+      <x:c r="AP221" s="22"/>
+      <x:c r="AQ221" s="24"/>
+      <x:c r="AR221" s="24"/>
+      <x:c r="AS221" s="22"/>
+      <x:c r="AT221" s="25"/>
+      <x:c r="AU221" s="25"/>
+      <x:c r="AV221" s="22"/>
+      <x:c r="AW221" s="22"/>
+      <x:c r="AX221" s="22"/>
+      <x:c r="AY221" s="22"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="AN222" s="23"/>
+      <x:c r="AO222" s="22"/>
+      <x:c r="AP222" s="22"/>
+      <x:c r="AQ222" s="24"/>
+      <x:c r="AR222" s="24"/>
+      <x:c r="AS222" s="22"/>
+      <x:c r="AT222" s="25"/>
+      <x:c r="AU222" s="25"/>
+      <x:c r="AV222" s="22"/>
+      <x:c r="AW222" s="22"/>
+      <x:c r="AX222" s="22"/>
+      <x:c r="AY222" s="22"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="AN223" s="23"/>
+      <x:c r="AO223" s="22"/>
+      <x:c r="AP223" s="22"/>
+      <x:c r="AQ223" s="24"/>
+      <x:c r="AR223" s="24"/>
+      <x:c r="AS223" s="22"/>
+      <x:c r="AT223" s="25"/>
+      <x:c r="AU223" s="25"/>
+      <x:c r="AV223" s="22"/>
+      <x:c r="AW223" s="22"/>
+      <x:c r="AX223" s="22"/>
+      <x:c r="AY223" s="22"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="AN224" s="23"/>
+      <x:c r="AO224" s="22"/>
+      <x:c r="AP224" s="22"/>
+      <x:c r="AQ224" s="24"/>
+      <x:c r="AR224" s="24"/>
+      <x:c r="AS224" s="22"/>
+      <x:c r="AT224" s="25"/>
+      <x:c r="AU224" s="25"/>
+      <x:c r="AV224" s="22"/>
+      <x:c r="AW224" s="22"/>
+      <x:c r="AX224" s="22"/>
+      <x:c r="AY224" s="22"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="AN225" s="23"/>
+      <x:c r="AO225" s="22"/>
+      <x:c r="AP225" s="22"/>
+      <x:c r="AQ225" s="24"/>
+      <x:c r="AR225" s="24"/>
+      <x:c r="AS225" s="22"/>
+      <x:c r="AT225" s="25"/>
+      <x:c r="AU225" s="25"/>
+      <x:c r="AV225" s="22"/>
+      <x:c r="AW225" s="22"/>
+      <x:c r="AX225" s="22"/>
+      <x:c r="AY225" s="22"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="AN226" s="23"/>
+      <x:c r="AO226" s="22"/>
+      <x:c r="AP226" s="22"/>
+      <x:c r="AQ226" s="24"/>
+      <x:c r="AR226" s="24"/>
+      <x:c r="AS226" s="22"/>
+      <x:c r="AT226" s="25"/>
+      <x:c r="AU226" s="25"/>
+      <x:c r="AV226" s="22"/>
+      <x:c r="AW226" s="22"/>
+      <x:c r="AX226" s="22"/>
+      <x:c r="AY226" s="22"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="AN227" s="23"/>
+      <x:c r="AO227" s="22"/>
+      <x:c r="AP227" s="22"/>
+      <x:c r="AQ227" s="24"/>
+      <x:c r="AR227" s="24"/>
+      <x:c r="AS227" s="22"/>
+      <x:c r="AT227" s="25"/>
+      <x:c r="AU227" s="25"/>
+      <x:c r="AV227" s="22"/>
+      <x:c r="AW227" s="22"/>
+      <x:c r="AX227" s="22"/>
+      <x:c r="AY227" s="22"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="AN228" s="23"/>
+      <x:c r="AO228" s="22"/>
+      <x:c r="AP228" s="22"/>
+      <x:c r="AQ228" s="24"/>
+      <x:c r="AR228" s="24"/>
+      <x:c r="AS228" s="22"/>
+      <x:c r="AT228" s="25"/>
+      <x:c r="AU228" s="25"/>
+      <x:c r="AV228" s="22"/>
+      <x:c r="AW228" s="22"/>
+      <x:c r="AX228" s="22"/>
+      <x:c r="AY228" s="22"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="AN229" s="23"/>
+      <x:c r="AO229" s="22"/>
+      <x:c r="AP229" s="22"/>
+      <x:c r="AQ229" s="24"/>
+      <x:c r="AR229" s="24"/>
+      <x:c r="AS229" s="22"/>
+      <x:c r="AT229" s="25"/>
+      <x:c r="AU229" s="25"/>
+      <x:c r="AV229" s="22"/>
+      <x:c r="AW229" s="22"/>
+      <x:c r="AX229" s="22"/>
+      <x:c r="AY229" s="22"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="AN230" s="23"/>
+      <x:c r="AO230" s="22"/>
+      <x:c r="AP230" s="22"/>
+      <x:c r="AQ230" s="24"/>
+      <x:c r="AR230" s="24"/>
+      <x:c r="AS230" s="22"/>
+      <x:c r="AT230" s="25"/>
+      <x:c r="AU230" s="25"/>
+      <x:c r="AV230" s="22"/>
+      <x:c r="AW230" s="22"/>
+      <x:c r="AX230" s="22"/>
+      <x:c r="AY230" s="22"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="AN231" s="23"/>
+      <x:c r="AO231" s="22"/>
+      <x:c r="AP231" s="22"/>
+      <x:c r="AQ231" s="24"/>
+      <x:c r="AR231" s="24"/>
+      <x:c r="AS231" s="22"/>
+      <x:c r="AT231" s="25"/>
+      <x:c r="AU231" s="25"/>
+      <x:c r="AV231" s="22"/>
+      <x:c r="AW231" s="22"/>
+      <x:c r="AX231" s="22"/>
+      <x:c r="AY231" s="22"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="AN232" s="23"/>
+      <x:c r="AO232" s="22"/>
+      <x:c r="AP232" s="22"/>
+      <x:c r="AQ232" s="24"/>
+      <x:c r="AR232" s="24"/>
+      <x:c r="AS232" s="22"/>
+      <x:c r="AT232" s="25"/>
+      <x:c r="AU232" s="25"/>
+      <x:c r="AV232" s="22"/>
+      <x:c r="AW232" s="22"/>
+      <x:c r="AX232" s="22"/>
+      <x:c r="AY232" s="22"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="AN233" s="23"/>
+      <x:c r="AO233" s="22"/>
+      <x:c r="AP233" s="22"/>
+      <x:c r="AQ233" s="24"/>
+      <x:c r="AR233" s="24"/>
+      <x:c r="AS233" s="22"/>
+      <x:c r="AT233" s="25"/>
+      <x:c r="AU233" s="25"/>
+      <x:c r="AV233" s="22"/>
+      <x:c r="AW233" s="22"/>
+      <x:c r="AX233" s="22"/>
+      <x:c r="AY233" s="22"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="AN234" s="23"/>
+      <x:c r="AO234" s="22"/>
+      <x:c r="AP234" s="22"/>
+      <x:c r="AQ234" s="24"/>
+      <x:c r="AR234" s="24"/>
+      <x:c r="AS234" s="22"/>
+      <x:c r="AT234" s="25"/>
+      <x:c r="AU234" s="25"/>
+      <x:c r="AV234" s="22"/>
+      <x:c r="AW234" s="22"/>
+      <x:c r="AX234" s="22"/>
+      <x:c r="AY234" s="22"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="AN235" s="23"/>
+      <x:c r="AO235" s="22"/>
+      <x:c r="AP235" s="22"/>
+      <x:c r="AQ235" s="24"/>
+      <x:c r="AR235" s="24"/>
+      <x:c r="AS235" s="22"/>
+      <x:c r="AT235" s="25"/>
+      <x:c r="AU235" s="25"/>
+      <x:c r="AV235" s="22"/>
+      <x:c r="AW235" s="22"/>
+      <x:c r="AX235" s="22"/>
+      <x:c r="AY235" s="22"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="AN236" s="23"/>
+      <x:c r="AO236" s="22"/>
+      <x:c r="AP236" s="22"/>
+      <x:c r="AQ236" s="24"/>
+      <x:c r="AR236" s="24"/>
+      <x:c r="AS236" s="22"/>
+      <x:c r="AT236" s="25"/>
+      <x:c r="AU236" s="25"/>
+      <x:c r="AV236" s="22"/>
+      <x:c r="AW236" s="22"/>
+      <x:c r="AX236" s="22"/>
+      <x:c r="AY236" s="22"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="AN237" s="23"/>
+      <x:c r="AO237" s="22"/>
+      <x:c r="AP237" s="22"/>
+      <x:c r="AQ237" s="24"/>
+      <x:c r="AR237" s="24"/>
+      <x:c r="AS237" s="22"/>
+      <x:c r="AT237" s="25"/>
+      <x:c r="AU237" s="25"/>
+      <x:c r="AV237" s="22"/>
+      <x:c r="AW237" s="22"/>
+      <x:c r="AX237" s="22"/>
+      <x:c r="AY237" s="22"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="AN238" s="23"/>
+      <x:c r="AO238" s="22"/>
+      <x:c r="AP238" s="22"/>
+      <x:c r="AQ238" s="24"/>
+      <x:c r="AR238" s="24"/>
+      <x:c r="AS238" s="22"/>
+      <x:c r="AT238" s="25"/>
+      <x:c r="AU238" s="25"/>
+      <x:c r="AV238" s="22"/>
+      <x:c r="AW238" s="22"/>
+      <x:c r="AX238" s="22"/>
+      <x:c r="AY238" s="22"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="AN239" s="23"/>
+      <x:c r="AO239" s="22"/>
+      <x:c r="AP239" s="22"/>
+      <x:c r="AQ239" s="24"/>
+      <x:c r="AR239" s="24"/>
+      <x:c r="AS239" s="22"/>
+      <x:c r="AT239" s="25"/>
+      <x:c r="AU239" s="25"/>
+      <x:c r="AV239" s="22"/>
+      <x:c r="AW239" s="22"/>
+      <x:c r="AX239" s="22"/>
+      <x:c r="AY239" s="22"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="AN240" s="23"/>
+      <x:c r="AO240" s="22"/>
+      <x:c r="AP240" s="22"/>
+      <x:c r="AQ240" s="24"/>
+      <x:c r="AR240" s="24"/>
+      <x:c r="AS240" s="22"/>
+      <x:c r="AT240" s="25"/>
+      <x:c r="AU240" s="25"/>
+      <x:c r="AV240" s="22"/>
+      <x:c r="AW240" s="22"/>
+      <x:c r="AX240" s="22"/>
+      <x:c r="AY240" s="22"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="AN241" s="23"/>
+      <x:c r="AO241" s="22"/>
+      <x:c r="AP241" s="22"/>
+      <x:c r="AQ241" s="24"/>
+      <x:c r="AR241" s="24"/>
+      <x:c r="AS241" s="22"/>
+      <x:c r="AT241" s="25"/>
+      <x:c r="AU241" s="25"/>
+      <x:c r="AV241" s="22"/>
+      <x:c r="AW241" s="22"/>
+      <x:c r="AX241" s="22"/>
+      <x:c r="AY241" s="22"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="AN242" s="23"/>
+      <x:c r="AO242" s="22"/>
+      <x:c r="AP242" s="22"/>
+      <x:c r="AQ242" s="24"/>
+      <x:c r="AR242" s="24"/>
+      <x:c r="AS242" s="22"/>
+      <x:c r="AT242" s="25"/>
+      <x:c r="AU242" s="25"/>
+      <x:c r="AV242" s="22"/>
+      <x:c r="AW242" s="22"/>
+      <x:c r="AX242" s="22"/>
+      <x:c r="AY242" s="22"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="AN243" s="23"/>
+      <x:c r="AO243" s="22"/>
+      <x:c r="AP243" s="22"/>
+      <x:c r="AQ243" s="24"/>
+      <x:c r="AR243" s="24"/>
+      <x:c r="AS243" s="22"/>
+      <x:c r="AT243" s="25"/>
+      <x:c r="AU243" s="25"/>
+      <x:c r="AV243" s="22"/>
+      <x:c r="AW243" s="22"/>
+      <x:c r="AX243" s="22"/>
+      <x:c r="AY243" s="22"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="AN244" s="23"/>
+      <x:c r="AO244" s="22"/>
+      <x:c r="AP244" s="22"/>
+      <x:c r="AQ244" s="24"/>
+      <x:c r="AR244" s="24"/>
+      <x:c r="AS244" s="22"/>
+      <x:c r="AT244" s="25"/>
+      <x:c r="AU244" s="25"/>
+      <x:c r="AV244" s="22"/>
+      <x:c r="AW244" s="22"/>
+      <x:c r="AX244" s="22"/>
+      <x:c r="AY244" s="22"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="AN245" s="23"/>
+      <x:c r="AO245" s="22"/>
+      <x:c r="AP245" s="22"/>
+      <x:c r="AQ245" s="24"/>
+      <x:c r="AR245" s="24"/>
+      <x:c r="AS245" s="22"/>
+      <x:c r="AT245" s="25"/>
+      <x:c r="AU245" s="25"/>
+      <x:c r="AV245" s="22"/>
+      <x:c r="AW245" s="22"/>
+      <x:c r="AX245" s="22"/>
+      <x:c r="AY245" s="22"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="AN246" s="23"/>
+      <x:c r="AO246" s="22"/>
+      <x:c r="AP246" s="22"/>
+      <x:c r="AQ246" s="24"/>
+      <x:c r="AR246" s="24"/>
+      <x:c r="AS246" s="22"/>
+      <x:c r="AT246" s="25"/>
+      <x:c r="AU246" s="25"/>
+      <x:c r="AV246" s="22"/>
+      <x:c r="AW246" s="22"/>
+      <x:c r="AX246" s="22"/>
+      <x:c r="AY246" s="22"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="AN247" s="23"/>
+      <x:c r="AO247" s="22"/>
+      <x:c r="AP247" s="22"/>
+      <x:c r="AQ247" s="24"/>
+      <x:c r="AR247" s="24"/>
+      <x:c r="AS247" s="22"/>
+      <x:c r="AT247" s="25"/>
+      <x:c r="AU247" s="25"/>
+      <x:c r="AV247" s="22"/>
+      <x:c r="AW247" s="22"/>
+      <x:c r="AX247" s="22"/>
+      <x:c r="AY247" s="22"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="AN248" s="23"/>
+      <x:c r="AO248" s="22"/>
+      <x:c r="AP248" s="22"/>
+      <x:c r="AQ248" s="24"/>
+      <x:c r="AR248" s="24"/>
+      <x:c r="AS248" s="22"/>
+      <x:c r="AT248" s="25"/>
+      <x:c r="AU248" s="25"/>
+      <x:c r="AV248" s="22"/>
+      <x:c r="AW248" s="22"/>
+      <x:c r="AX248" s="22"/>
+      <x:c r="AY248" s="22"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="AN249" s="23"/>
+      <x:c r="AO249" s="22"/>
+      <x:c r="AP249" s="22"/>
+      <x:c r="AQ249" s="24"/>
+      <x:c r="AR249" s="24"/>
+      <x:c r="AS249" s="22"/>
+      <x:c r="AT249" s="25"/>
+      <x:c r="AU249" s="25"/>
+      <x:c r="AV249" s="22"/>
+      <x:c r="AW249" s="22"/>
+      <x:c r="AX249" s="22"/>
+      <x:c r="AY249" s="22"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="AN250" s="23"/>
+      <x:c r="AO250" s="22"/>
+      <x:c r="AP250" s="22"/>
+      <x:c r="AQ250" s="24"/>
+      <x:c r="AR250" s="24"/>
+      <x:c r="AS250" s="22"/>
+      <x:c r="AT250" s="25"/>
+      <x:c r="AU250" s="25"/>
+      <x:c r="AV250" s="22"/>
+      <x:c r="AW250" s="22"/>
+      <x:c r="AX250" s="22"/>
+      <x:c r="AY250" s="22"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="AN251" s="23"/>
+      <x:c r="AO251" s="22"/>
+      <x:c r="AP251" s="22"/>
+      <x:c r="AQ251" s="24"/>
+      <x:c r="AR251" s="24"/>
+      <x:c r="AS251" s="22"/>
+      <x:c r="AT251" s="25"/>
+      <x:c r="AU251" s="25"/>
+      <x:c r="AV251" s="22"/>
+      <x:c r="AW251" s="22"/>
+      <x:c r="AX251" s="22"/>
+      <x:c r="AY251" s="22"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="AN252" s="23"/>
+      <x:c r="AO252" s="22"/>
+      <x:c r="AP252" s="22"/>
+      <x:c r="AQ252" s="24"/>
+      <x:c r="AR252" s="24"/>
+      <x:c r="AS252" s="22"/>
+      <x:c r="AT252" s="25"/>
+      <x:c r="AU252" s="25"/>
+      <x:c r="AV252" s="22"/>
+      <x:c r="AW252" s="22"/>
+      <x:c r="AX252" s="22"/>
+      <x:c r="AY252" s="22"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="AN253" s="23"/>
+      <x:c r="AO253" s="22"/>
+      <x:c r="AP253" s="22"/>
+      <x:c r="AQ253" s="24"/>
+      <x:c r="AR253" s="24"/>
+      <x:c r="AS253" s="22"/>
+      <x:c r="AT253" s="25"/>
+      <x:c r="AU253" s="25"/>
+      <x:c r="AV253" s="22"/>
+      <x:c r="AW253" s="22"/>
+      <x:c r="AX253" s="22"/>
+      <x:c r="AY253" s="22"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="AN254" s="23"/>
+      <x:c r="AO254" s="22"/>
+      <x:c r="AP254" s="22"/>
+      <x:c r="AQ254" s="24"/>
+      <x:c r="AR254" s="24"/>
+      <x:c r="AS254" s="22"/>
+      <x:c r="AT254" s="25"/>
+      <x:c r="AU254" s="25"/>
+      <x:c r="AV254" s="22"/>
+      <x:c r="AW254" s="22"/>
+      <x:c r="AX254" s="22"/>
+      <x:c r="AY254" s="22"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="AN255" s="23"/>
+      <x:c r="AO255" s="22"/>
+      <x:c r="AP255" s="22"/>
+      <x:c r="AQ255" s="24"/>
+      <x:c r="AR255" s="24"/>
+      <x:c r="AS255" s="22"/>
+      <x:c r="AT255" s="25"/>
+      <x:c r="AU255" s="25"/>
+      <x:c r="AV255" s="22"/>
+      <x:c r="AW255" s="22"/>
+      <x:c r="AX255" s="22"/>
+      <x:c r="AY255" s="22"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="AN256" s="23"/>
+      <x:c r="AO256" s="22"/>
+      <x:c r="AP256" s="22"/>
+      <x:c r="AQ256" s="24"/>
+      <x:c r="AR256" s="24"/>
+      <x:c r="AS256" s="22"/>
+      <x:c r="AT256" s="25"/>
+      <x:c r="AU256" s="25"/>
+      <x:c r="AV256" s="22"/>
+      <x:c r="AW256" s="22"/>
+      <x:c r="AX256" s="22"/>
+      <x:c r="AY256" s="22"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="AN257" s="23"/>
+      <x:c r="AO257" s="22"/>
+      <x:c r="AP257" s="22"/>
+      <x:c r="AQ257" s="24"/>
+      <x:c r="AR257" s="24"/>
+      <x:c r="AS257" s="22"/>
+      <x:c r="AT257" s="25"/>
+      <x:c r="AU257" s="25"/>
+      <x:c r="AV257" s="22"/>
+      <x:c r="AW257" s="22"/>
+      <x:c r="AX257" s="22"/>
+      <x:c r="AY257" s="22"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="AN258" s="23"/>
+      <x:c r="AO258" s="22"/>
+      <x:c r="AP258" s="22"/>
+      <x:c r="AQ258" s="24"/>
+      <x:c r="AR258" s="24"/>
+      <x:c r="AS258" s="22"/>
+      <x:c r="AT258" s="25"/>
+      <x:c r="AU258" s="25"/>
+      <x:c r="AV258" s="22"/>
+      <x:c r="AW258" s="22"/>
+      <x:c r="AX258" s="22"/>
+      <x:c r="AY258" s="22"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="AN259" s="23"/>
+      <x:c r="AO259" s="22"/>
+      <x:c r="AP259" s="22"/>
+      <x:c r="AQ259" s="24"/>
+      <x:c r="AR259" s="24"/>
+      <x:c r="AS259" s="22"/>
+      <x:c r="AT259" s="25"/>
+      <x:c r="AU259" s="25"/>
+      <x:c r="AV259" s="22"/>
+      <x:c r="AW259" s="22"/>
+      <x:c r="AX259" s="22"/>
+      <x:c r="AY259" s="22"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="AN260" s="23"/>
+      <x:c r="AO260" s="22"/>
+      <x:c r="AP260" s="22"/>
+      <x:c r="AQ260" s="24"/>
+      <x:c r="AR260" s="24"/>
+      <x:c r="AS260" s="22"/>
+      <x:c r="AT260" s="25"/>
+      <x:c r="AU260" s="25"/>
+      <x:c r="AV260" s="22"/>
+      <x:c r="AW260" s="22"/>
+      <x:c r="AX260" s="22"/>
+      <x:c r="AY260" s="22"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="AN261" s="23"/>
+      <x:c r="AO261" s="22"/>
+      <x:c r="AP261" s="22"/>
+      <x:c r="AQ261" s="24"/>
+      <x:c r="AR261" s="24"/>
+      <x:c r="AS261" s="22"/>
+      <x:c r="AT261" s="25"/>
+      <x:c r="AU261" s="25"/>
+      <x:c r="AV261" s="22"/>
+      <x:c r="AW261" s="22"/>
+      <x:c r="AX261" s="22"/>
+      <x:c r="AY261" s="22"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="AN262" s="23"/>
+      <x:c r="AO262" s="22"/>
+      <x:c r="AP262" s="22"/>
+      <x:c r="AQ262" s="24"/>
+      <x:c r="AR262" s="24"/>
+      <x:c r="AS262" s="22"/>
+      <x:c r="AT262" s="25"/>
+      <x:c r="AU262" s="25"/>
+      <x:c r="AV262" s="22"/>
+      <x:c r="AW262" s="22"/>
+      <x:c r="AX262" s="22"/>
+      <x:c r="AY262" s="22"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="AN263" s="23"/>
+      <x:c r="AO263" s="22"/>
+      <x:c r="AP263" s="22"/>
+      <x:c r="AQ263" s="24"/>
+      <x:c r="AR263" s="24"/>
+      <x:c r="AS263" s="22"/>
+      <x:c r="AT263" s="25"/>
+      <x:c r="AU263" s="25"/>
+      <x:c r="AV263" s="22"/>
+      <x:c r="AW263" s="22"/>
+      <x:c r="AX263" s="22"/>
+      <x:c r="AY263" s="22"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="AN264" s="23"/>
+      <x:c r="AO264" s="22"/>
+      <x:c r="AP264" s="22"/>
+      <x:c r="AQ264" s="24"/>
+      <x:c r="AR264" s="24"/>
+      <x:c r="AS264" s="22"/>
+      <x:c r="AT264" s="25"/>
+      <x:c r="AU264" s="25"/>
+      <x:c r="AV264" s="22"/>
+      <x:c r="AW264" s="22"/>
+      <x:c r="AX264" s="22"/>
+      <x:c r="AY264" s="22"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="AN265" s="23"/>
+      <x:c r="AO265" s="22"/>
+      <x:c r="AP265" s="22"/>
+      <x:c r="AQ265" s="24"/>
+      <x:c r="AR265" s="24"/>
+      <x:c r="AS265" s="22"/>
+      <x:c r="AT265" s="25"/>
+      <x:c r="AU265" s="25"/>
+      <x:c r="AV265" s="22"/>
+      <x:c r="AW265" s="22"/>
+      <x:c r="AX265" s="22"/>
+      <x:c r="AY265" s="22"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="AN266" s="23"/>
+      <x:c r="AO266" s="22"/>
+      <x:c r="AP266" s="22"/>
+      <x:c r="AQ266" s="24"/>
+      <x:c r="AR266" s="24"/>
+      <x:c r="AS266" s="22"/>
+      <x:c r="AT266" s="25"/>
+      <x:c r="AU266" s="25"/>
+      <x:c r="AV266" s="22"/>
+      <x:c r="AW266" s="22"/>
+      <x:c r="AX266" s="22"/>
+      <x:c r="AY266" s="22"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="AN267" s="23"/>
+      <x:c r="AO267" s="22"/>
+      <x:c r="AP267" s="22"/>
+      <x:c r="AQ267" s="24"/>
+      <x:c r="AR267" s="24"/>
+      <x:c r="AS267" s="22"/>
+      <x:c r="AT267" s="25"/>
+      <x:c r="AU267" s="25"/>
+      <x:c r="AV267" s="22"/>
+      <x:c r="AW267" s="22"/>
+      <x:c r="AX267" s="22"/>
+      <x:c r="AY267" s="22"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="AN268" s="23"/>
+      <x:c r="AO268" s="22"/>
+      <x:c r="AP268" s="22"/>
+      <x:c r="AQ268" s="24"/>
+      <x:c r="AR268" s="24"/>
+      <x:c r="AS268" s="22"/>
+      <x:c r="AT268" s="25"/>
+      <x:c r="AU268" s="25"/>
+      <x:c r="AV268" s="22"/>
+      <x:c r="AW268" s="22"/>
+      <x:c r="AX268" s="22"/>
+      <x:c r="AY268" s="22"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="AN269" s="23"/>
+      <x:c r="AO269" s="22"/>
+      <x:c r="AP269" s="22"/>
+      <x:c r="AQ269" s="24"/>
+      <x:c r="AR269" s="24"/>
+      <x:c r="AS269" s="22"/>
+      <x:c r="AT269" s="25"/>
+      <x:c r="AU269" s="25"/>
+      <x:c r="AV269" s="22"/>
+      <x:c r="AW269" s="22"/>
+      <x:c r="AX269" s="22"/>
+      <x:c r="AY269" s="22"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="AN270" s="23"/>
+      <x:c r="AO270" s="22"/>
+      <x:c r="AP270" s="22"/>
+      <x:c r="AQ270" s="24"/>
+      <x:c r="AR270" s="24"/>
+      <x:c r="AS270" s="22"/>
+      <x:c r="AT270" s="25"/>
+      <x:c r="AU270" s="25"/>
+      <x:c r="AV270" s="22"/>
+      <x:c r="AW270" s="22"/>
+      <x:c r="AX270" s="22"/>
+      <x:c r="AY270" s="22"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="AN271" s="23"/>
+      <x:c r="AO271" s="22"/>
+      <x:c r="AP271" s="22"/>
+      <x:c r="AQ271" s="24"/>
+      <x:c r="AR271" s="24"/>
+      <x:c r="AS271" s="22"/>
+      <x:c r="AT271" s="25"/>
+      <x:c r="AU271" s="25"/>
+      <x:c r="AV271" s="22"/>
+      <x:c r="AW271" s="22"/>
+      <x:c r="AX271" s="22"/>
+      <x:c r="AY271" s="22"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="AN272" s="23"/>
+      <x:c r="AO272" s="22"/>
+      <x:c r="AP272" s="22"/>
+      <x:c r="AQ272" s="24"/>
+      <x:c r="AR272" s="24"/>
+      <x:c r="AS272" s="22"/>
+      <x:c r="AT272" s="25"/>
+      <x:c r="AU272" s="25"/>
+      <x:c r="AV272" s="22"/>
+      <x:c r="AW272" s="22"/>
+      <x:c r="AX272" s="22"/>
+      <x:c r="AY272" s="22"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="AN273" s="23"/>
+      <x:c r="AO273" s="22"/>
+      <x:c r="AP273" s="22"/>
+      <x:c r="AQ273" s="24"/>
+      <x:c r="AR273" s="24"/>
+      <x:c r="AS273" s="22"/>
+      <x:c r="AT273" s="25"/>
+      <x:c r="AU273" s="25"/>
+      <x:c r="AV273" s="22"/>
+      <x:c r="AW273" s="22"/>
+      <x:c r="AX273" s="22"/>
+      <x:c r="AY273" s="22"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="AN274" s="23"/>
+      <x:c r="AO274" s="22"/>
+      <x:c r="AP274" s="22"/>
+      <x:c r="AQ274" s="24"/>
+      <x:c r="AR274" s="24"/>
+      <x:c r="AS274" s="22"/>
+      <x:c r="AT274" s="25"/>
+      <x:c r="AU274" s="25"/>
+      <x:c r="AV274" s="22"/>
+      <x:c r="AW274" s="22"/>
+      <x:c r="AX274" s="22"/>
+      <x:c r="AY274" s="22"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="AN275" s="23"/>
+      <x:c r="AO275" s="22"/>
+      <x:c r="AP275" s="22"/>
+      <x:c r="AQ275" s="24"/>
+      <x:c r="AR275" s="24"/>
+      <x:c r="AS275" s="22"/>
+      <x:c r="AT275" s="25"/>
+      <x:c r="AU275" s="25"/>
+      <x:c r="AV275" s="22"/>
+      <x:c r="AW275" s="22"/>
+      <x:c r="AX275" s="22"/>
+      <x:c r="AY275" s="22"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="AN276" s="23"/>
+      <x:c r="AO276" s="22"/>
+      <x:c r="AP276" s="22"/>
+      <x:c r="AQ276" s="24"/>
+      <x:c r="AR276" s="24"/>
+      <x:c r="AS276" s="22"/>
+      <x:c r="AT276" s="25"/>
+      <x:c r="AU276" s="25"/>
+      <x:c r="AV276" s="22"/>
+      <x:c r="AW276" s="22"/>
+      <x:c r="AX276" s="22"/>
+      <x:c r="AY276" s="22"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="AN277" s="23"/>
+      <x:c r="AO277" s="22"/>
+      <x:c r="AP277" s="22"/>
+      <x:c r="AQ277" s="24"/>
+      <x:c r="AR277" s="24"/>
+      <x:c r="AS277" s="22"/>
+      <x:c r="AT277" s="25"/>
+      <x:c r="AU277" s="25"/>
+      <x:c r="AV277" s="22"/>
+      <x:c r="AW277" s="22"/>
+      <x:c r="AX277" s="22"/>
+      <x:c r="AY277" s="22"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="AN278" s="23"/>
+      <x:c r="AO278" s="22"/>
+      <x:c r="AP278" s="22"/>
+      <x:c r="AQ278" s="24"/>
+      <x:c r="AR278" s="24"/>
+      <x:c r="AS278" s="22"/>
+      <x:c r="AT278" s="25"/>
+      <x:c r="AU278" s="25"/>
+      <x:c r="AV278" s="22"/>
+      <x:c r="AW278" s="22"/>
+      <x:c r="AX278" s="22"/>
+      <x:c r="AY278" s="22"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="AN279" s="23"/>
+      <x:c r="AO279" s="22"/>
+      <x:c r="AP279" s="22"/>
+      <x:c r="AQ279" s="24"/>
+      <x:c r="AR279" s="24"/>
+      <x:c r="AS279" s="22"/>
+      <x:c r="AT279" s="25"/>
+      <x:c r="AU279" s="25"/>
+      <x:c r="AV279" s="22"/>
+      <x:c r="AW279" s="22"/>
+      <x:c r="AX279" s="22"/>
+      <x:c r="AY279" s="22"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="AN280" s="23"/>
+      <x:c r="AO280" s="22"/>
+      <x:c r="AP280" s="22"/>
+      <x:c r="AQ280" s="24"/>
+      <x:c r="AR280" s="24"/>
+      <x:c r="AS280" s="22"/>
+      <x:c r="AT280" s="25"/>
+      <x:c r="AU280" s="25"/>
+      <x:c r="AV280" s="22"/>
+      <x:c r="AW280" s="22"/>
+      <x:c r="AX280" s="22"/>
+      <x:c r="AY280" s="22"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="AN281" s="23"/>
+      <x:c r="AO281" s="22"/>
+      <x:c r="AP281" s="22"/>
+      <x:c r="AQ281" s="24"/>
+      <x:c r="AR281" s="24"/>
+      <x:c r="AS281" s="22"/>
+      <x:c r="AT281" s="25"/>
+      <x:c r="AU281" s="25"/>
+      <x:c r="AV281" s="22"/>
+      <x:c r="AW281" s="22"/>
+      <x:c r="AX281" s="22"/>
+      <x:c r="AY281" s="22"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="AN282" s="23"/>
+      <x:c r="AO282" s="22"/>
+      <x:c r="AP282" s="22"/>
+      <x:c r="AQ282" s="24"/>
+      <x:c r="AR282" s="24"/>
+      <x:c r="AS282" s="22"/>
+      <x:c r="AT282" s="25"/>
+      <x:c r="AU282" s="25"/>
+      <x:c r="AV282" s="22"/>
+      <x:c r="AW282" s="22"/>
+      <x:c r="AX282" s="22"/>
+      <x:c r="AY282" s="22"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="AN283" s="23"/>
+      <x:c r="AO283" s="22"/>
+      <x:c r="AP283" s="22"/>
+      <x:c r="AQ283" s="24"/>
+      <x:c r="AR283" s="24"/>
+      <x:c r="AS283" s="22"/>
+      <x:c r="AT283" s="25"/>
+      <x:c r="AU283" s="25"/>
+      <x:c r="AV283" s="22"/>
+      <x:c r="AW283" s="22"/>
+      <x:c r="AX283" s="22"/>
+      <x:c r="AY283" s="22"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="AN284" s="23"/>
+      <x:c r="AO284" s="22"/>
+      <x:c r="AP284" s="22"/>
+      <x:c r="AQ284" s="24"/>
+      <x:c r="AR284" s="24"/>
+      <x:c r="AS284" s="22"/>
+      <x:c r="AT284" s="25"/>
+      <x:c r="AU284" s="25"/>
+      <x:c r="AV284" s="22"/>
+      <x:c r="AW284" s="22"/>
+      <x:c r="AX284" s="22"/>
+      <x:c r="AY284" s="22"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="AN285" s="23"/>
+      <x:c r="AO285" s="22"/>
+      <x:c r="AP285" s="22"/>
+      <x:c r="AQ285" s="24"/>
+      <x:c r="AR285" s="24"/>
+      <x:c r="AS285" s="22"/>
+      <x:c r="AT285" s="25"/>
+      <x:c r="AU285" s="25"/>
+      <x:c r="AV285" s="22"/>
+      <x:c r="AW285" s="22"/>
+      <x:c r="AX285" s="22"/>
+      <x:c r="AY285" s="22"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="AN286" s="23"/>
+      <x:c r="AO286" s="22"/>
+      <x:c r="AP286" s="22"/>
+      <x:c r="AQ286" s="24"/>
+      <x:c r="AR286" s="24"/>
+      <x:c r="AS286" s="22"/>
+      <x:c r="AT286" s="25"/>
+      <x:c r="AU286" s="25"/>
+      <x:c r="AV286" s="22"/>
+      <x:c r="AW286" s="22"/>
+      <x:c r="AX286" s="22"/>
+      <x:c r="AY286" s="22"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="AN287" s="23"/>
+      <x:c r="AO287" s="22"/>
+      <x:c r="AP287" s="22"/>
+      <x:c r="AQ287" s="24"/>
+      <x:c r="AR287" s="24"/>
+      <x:c r="AS287" s="22"/>
+      <x:c r="AT287" s="25"/>
+      <x:c r="AU287" s="25"/>
+      <x:c r="AV287" s="22"/>
+      <x:c r="AW287" s="22"/>
+      <x:c r="AX287" s="22"/>
+      <x:c r="AY287" s="22"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="AN288" s="23"/>
+      <x:c r="AO288" s="22"/>
+      <x:c r="AP288" s="22"/>
+      <x:c r="AQ288" s="24"/>
+      <x:c r="AR288" s="24"/>
+      <x:c r="AS288" s="22"/>
+      <x:c r="AT288" s="25"/>
+      <x:c r="AU288" s="25"/>
+      <x:c r="AV288" s="22"/>
+      <x:c r="AW288" s="22"/>
+      <x:c r="AX288" s="22"/>
+      <x:c r="AY288" s="22"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="AN289" s="23"/>
+      <x:c r="AO289" s="22"/>
+      <x:c r="AP289" s="22"/>
+      <x:c r="AQ289" s="24"/>
+      <x:c r="AR289" s="24"/>
+      <x:c r="AS289" s="22"/>
+      <x:c r="AT289" s="25"/>
+      <x:c r="AU289" s="25"/>
+      <x:c r="AV289" s="22"/>
+      <x:c r="AW289" s="22"/>
+      <x:c r="AX289" s="22"/>
+      <x:c r="AY289" s="22"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="AN290" s="23"/>
+      <x:c r="AO290" s="22"/>
+      <x:c r="AP290" s="22"/>
+      <x:c r="AQ290" s="24"/>
+      <x:c r="AR290" s="24"/>
+      <x:c r="AS290" s="22"/>
+      <x:c r="AT290" s="25"/>
+      <x:c r="AU290" s="25"/>
+      <x:c r="AV290" s="22"/>
+      <x:c r="AW290" s="22"/>
+      <x:c r="AX290" s="22"/>
+      <x:c r="AY290" s="22"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="AN291" s="23"/>
+      <x:c r="AO291" s="22"/>
+      <x:c r="AP291" s="22"/>
+      <x:c r="AQ291" s="24"/>
+      <x:c r="AR291" s="24"/>
+      <x:c r="AS291" s="22"/>
+      <x:c r="AT291" s="25"/>
+      <x:c r="AU291" s="25"/>
+      <x:c r="AV291" s="22"/>
+      <x:c r="AW291" s="22"/>
+      <x:c r="AX291" s="22"/>
+      <x:c r="AY291" s="22"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="AN292" s="23"/>
+      <x:c r="AO292" s="22"/>
+      <x:c r="AP292" s="22"/>
+      <x:c r="AQ292" s="24"/>
+      <x:c r="AR292" s="24"/>
+      <x:c r="AS292" s="22"/>
+      <x:c r="AT292" s="25"/>
+      <x:c r="AU292" s="25"/>
+      <x:c r="AV292" s="22"/>
+      <x:c r="AW292" s="22"/>
+      <x:c r="AX292" s="22"/>
+      <x:c r="AY292" s="22"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="AN293" s="23"/>
+      <x:c r="AO293" s="22"/>
+      <x:c r="AP293" s="22"/>
+      <x:c r="AQ293" s="24"/>
+      <x:c r="AR293" s="24"/>
+      <x:c r="AS293" s="22"/>
+      <x:c r="AT293" s="25"/>
+      <x:c r="AU293" s="25"/>
+      <x:c r="AV293" s="22"/>
+      <x:c r="AW293" s="22"/>
+      <x:c r="AX293" s="22"/>
+      <x:c r="AY293" s="22"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="AN294" s="23"/>
+      <x:c r="AO294" s="22"/>
+      <x:c r="AP294" s="22"/>
+      <x:c r="AQ294" s="24"/>
+      <x:c r="AR294" s="24"/>
+      <x:c r="AS294" s="22"/>
+      <x:c r="AT294" s="25"/>
+      <x:c r="AU294" s="25"/>
+      <x:c r="AV294" s="22"/>
+      <x:c r="AW294" s="22"/>
+      <x:c r="AX294" s="22"/>
+      <x:c r="AY294" s="22"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="AN295" s="23"/>
+      <x:c r="AO295" s="22"/>
+      <x:c r="AP295" s="22"/>
+      <x:c r="AQ295" s="24"/>
+      <x:c r="AR295" s="24"/>
+      <x:c r="AS295" s="22"/>
+      <x:c r="AT295" s="25"/>
+      <x:c r="AU295" s="25"/>
+      <x:c r="AV295" s="22"/>
+      <x:c r="AW295" s="22"/>
+      <x:c r="AX295" s="22"/>
+      <x:c r="AY295" s="22"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="AN296" s="23"/>
+      <x:c r="AO296" s="22"/>
+      <x:c r="AP296" s="22"/>
+      <x:c r="AQ296" s="24"/>
+      <x:c r="AR296" s="24"/>
+      <x:c r="AS296" s="22"/>
+      <x:c r="AT296" s="25"/>
+      <x:c r="AU296" s="25"/>
+      <x:c r="AV296" s="22"/>
+      <x:c r="AW296" s="22"/>
+      <x:c r="AX296" s="22"/>
+      <x:c r="AY296" s="22"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="AN297" s="23"/>
+      <x:c r="AO297" s="22"/>
+      <x:c r="AP297" s="22"/>
+      <x:c r="AQ297" s="24"/>
+      <x:c r="AR297" s="24"/>
+      <x:c r="AS297" s="22"/>
+      <x:c r="AT297" s="25"/>
+      <x:c r="AU297" s="25"/>
+      <x:c r="AV297" s="22"/>
+      <x:c r="AW297" s="22"/>
+      <x:c r="AX297" s="22"/>
+      <x:c r="AY297" s="22"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="AN298" s="23"/>
+      <x:c r="AO298" s="22"/>
+      <x:c r="AP298" s="22"/>
+      <x:c r="AQ298" s="24"/>
+      <x:c r="AR298" s="24"/>
+      <x:c r="AS298" s="22"/>
+      <x:c r="AT298" s="25"/>
+      <x:c r="AU298" s="25"/>
+      <x:c r="AV298" s="22"/>
+      <x:c r="AW298" s="22"/>
+      <x:c r="AX298" s="22"/>
+      <x:c r="AY298" s="22"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="AN299" s="23"/>
+      <x:c r="AO299" s="22"/>
+      <x:c r="AP299" s="22"/>
+      <x:c r="AQ299" s="24"/>
+      <x:c r="AR299" s="24"/>
+      <x:c r="AS299" s="22"/>
+      <x:c r="AT299" s="25"/>
+      <x:c r="AU299" s="25"/>
+      <x:c r="AV299" s="22"/>
+      <x:c r="AW299" s="22"/>
+      <x:c r="AX299" s="22"/>
+      <x:c r="AY299" s="22"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="AN300" s="23"/>
+      <x:c r="AO300" s="22"/>
+      <x:c r="AP300" s="22"/>
+      <x:c r="AQ300" s="24"/>
+      <x:c r="AR300" s="24"/>
+      <x:c r="AS300" s="22"/>
+      <x:c r="AT300" s="25"/>
+      <x:c r="AU300" s="25"/>
+      <x:c r="AV300" s="22"/>
+      <x:c r="AW300" s="22"/>
+      <x:c r="AX300" s="22"/>
+      <x:c r="AY300" s="22"/>
+    </x:row>
+    <x:row r="301">
+      <x:c r="AN301" s="23"/>
+      <x:c r="AO301" s="22"/>
+      <x:c r="AP301" s="22"/>
+      <x:c r="AQ301" s="24"/>
+      <x:c r="AR301" s="24"/>
+      <x:c r="AS301" s="22"/>
+      <x:c r="AT301" s="25"/>
+      <x:c r="AU301" s="25"/>
+      <x:c r="AV301" s="22"/>
+      <x:c r="AW301" s="22"/>
+      <x:c r="AX301" s="22"/>
+      <x:c r="AY301" s="22"/>
+    </x:row>
+    <x:row r="302">
+      <x:c r="AN302" s="23"/>
+      <x:c r="AO302" s="22"/>
+      <x:c r="AP302" s="22"/>
+      <x:c r="AQ302" s="24"/>
+      <x:c r="AR302" s="24"/>
+      <x:c r="AS302" s="22"/>
+      <x:c r="AT302" s="25"/>
+      <x:c r="AU302" s="25"/>
+      <x:c r="AV302" s="22"/>
+      <x:c r="AW302" s="22"/>
+      <x:c r="AX302" s="22"/>
+      <x:c r="AY302" s="22"/>
+    </x:row>
+    <x:row r="303">
+      <x:c r="AN303" s="23"/>
+      <x:c r="AO303" s="22"/>
+      <x:c r="AP303" s="22"/>
+      <x:c r="AQ303" s="24"/>
+      <x:c r="AR303" s="24"/>
+      <x:c r="AS303" s="22"/>
+      <x:c r="AT303" s="25"/>
+      <x:c r="AU303" s="25"/>
+      <x:c r="AV303" s="22"/>
+      <x:c r="AW303" s="22"/>
+      <x:c r="AX303" s="22"/>
+      <x:c r="AY303" s="22"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="AN304" s="23"/>
+      <x:c r="AO304" s="22"/>
+      <x:c r="AP304" s="22"/>
+      <x:c r="AQ304" s="24"/>
+      <x:c r="AR304" s="24"/>
+      <x:c r="AS304" s="22"/>
+      <x:c r="AT304" s="25"/>
+      <x:c r="AU304" s="25"/>
+      <x:c r="AV304" s="22"/>
+      <x:c r="AW304" s="22"/>
+      <x:c r="AX304" s="22"/>
+      <x:c r="AY304" s="22"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="AN305" s="23"/>
+      <x:c r="AO305" s="22"/>
+      <x:c r="AP305" s="22"/>
+      <x:c r="AQ305" s="24"/>
+      <x:c r="AR305" s="24"/>
+      <x:c r="AS305" s="22"/>
+      <x:c r="AT305" s="25"/>
+      <x:c r="AU305" s="25"/>
+      <x:c r="AV305" s="22"/>
+      <x:c r="AW305" s="22"/>
+      <x:c r="AX305" s="22"/>
+      <x:c r="AY305" s="22"/>
+    </x:row>
+    <x:row r="306">
+      <x:c r="AN306" s="23"/>
+      <x:c r="AO306" s="22"/>
+      <x:c r="AP306" s="22"/>
+      <x:c r="AQ306" s="24"/>
+      <x:c r="AR306" s="24"/>
+      <x:c r="AS306" s="22"/>
+      <x:c r="AT306" s="25"/>
+      <x:c r="AU306" s="25"/>
+      <x:c r="AV306" s="22"/>
+      <x:c r="AW306" s="22"/>
+      <x:c r="AX306" s="22"/>
+      <x:c r="AY306" s="22"/>
+    </x:row>
+    <x:row r="307">
+      <x:c r="AN307" s="23"/>
+      <x:c r="AO307" s="22"/>
+      <x:c r="AP307" s="22"/>
+      <x:c r="AQ307" s="24"/>
+      <x:c r="AR307" s="24"/>
+      <x:c r="AS307" s="22"/>
+      <x:c r="AT307" s="25"/>
+      <x:c r="AU307" s="25"/>
+      <x:c r="AV307" s="22"/>
+      <x:c r="AW307" s="22"/>
+      <x:c r="AX307" s="22"/>
+      <x:c r="AY307" s="22"/>
+    </x:row>
+    <x:row r="308">
+      <x:c r="AN308" s="23"/>
+      <x:c r="AO308" s="22"/>
+      <x:c r="AP308" s="22"/>
+      <x:c r="AQ308" s="24"/>
+      <x:c r="AR308" s="24"/>
+      <x:c r="AS308" s="22"/>
+      <x:c r="AT308" s="25"/>
+      <x:c r="AU308" s="25"/>
+      <x:c r="AV308" s="22"/>
+      <x:c r="AW308" s="22"/>
+      <x:c r="AX308" s="22"/>
+      <x:c r="AY308" s="22"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="AN309" s="23"/>
+      <x:c r="AO309" s="22"/>
+      <x:c r="AP309" s="22"/>
+      <x:c r="AQ309" s="24"/>
+      <x:c r="AR309" s="24"/>
+      <x:c r="AS309" s="22"/>
+      <x:c r="AT309" s="25"/>
+      <x:c r="AU309" s="25"/>
+      <x:c r="AV309" s="22"/>
+      <x:c r="AW309" s="22"/>
+      <x:c r="AX309" s="22"/>
+      <x:c r="AY309" s="22"/>
+    </x:row>
+    <x:row r="310">
+      <x:c r="AN310" s="23"/>
+      <x:c r="AO310" s="22"/>
+      <x:c r="AP310" s="22"/>
+      <x:c r="AQ310" s="24"/>
+      <x:c r="AR310" s="24"/>
+      <x:c r="AS310" s="22"/>
+      <x:c r="AT310" s="25"/>
+      <x:c r="AU310" s="25"/>
+      <x:c r="AV310" s="22"/>
+      <x:c r="AW310" s="22"/>
+      <x:c r="AX310" s="22"/>
+      <x:c r="AY310" s="22"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="AN311" s="23"/>
+      <x:c r="AO311" s="22"/>
+      <x:c r="AP311" s="22"/>
+      <x:c r="AQ311" s="24"/>
+      <x:c r="AR311" s="24"/>
+      <x:c r="AS311" s="22"/>
+      <x:c r="AT311" s="25"/>
+      <x:c r="AU311" s="25"/>
+      <x:c r="AV311" s="22"/>
+      <x:c r="AW311" s="22"/>
+      <x:c r="AX311" s="22"/>
+      <x:c r="AY311" s="22"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="AN312" s="23"/>
+      <x:c r="AO312" s="22"/>
+      <x:c r="AP312" s="22"/>
+      <x:c r="AQ312" s="24"/>
+      <x:c r="AR312" s="24"/>
+      <x:c r="AS312" s="22"/>
+      <x:c r="AT312" s="25"/>
+      <x:c r="AU312" s="25"/>
+      <x:c r="AV312" s="22"/>
+      <x:c r="AW312" s="22"/>
+      <x:c r="AX312" s="22"/>
+      <x:c r="AY312" s="22"/>
+    </x:row>
+    <x:row r="313">
+      <x:c r="AN313" s="23"/>
+      <x:c r="AO313" s="22"/>
+      <x:c r="AP313" s="22"/>
+      <x:c r="AQ313" s="24"/>
+      <x:c r="AR313" s="24"/>
+      <x:c r="AS313" s="22"/>
+      <x:c r="AT313" s="25"/>
+      <x:c r="AU313" s="25"/>
+      <x:c r="AV313" s="22"/>
+      <x:c r="AW313" s="22"/>
+      <x:c r="AX313" s="22"/>
+      <x:c r="AY313" s="22"/>
+    </x:row>
+    <x:row r="314">
+      <x:c r="AN314" s="23"/>
+      <x:c r="AO314" s="22"/>
+      <x:c r="AP314" s="22"/>
+      <x:c r="AQ314" s="24"/>
+      <x:c r="AR314" s="24"/>
+      <x:c r="AS314" s="22"/>
+      <x:c r="AT314" s="25"/>
+      <x:c r="AU314" s="25"/>
+      <x:c r="AV314" s="22"/>
+      <x:c r="AW314" s="22"/>
+      <x:c r="AX314" s="22"/>
+      <x:c r="AY314" s="22"/>
+    </x:row>
+    <x:row r="315">
+      <x:c r="AN315" s="23"/>
+      <x:c r="AO315" s="22"/>
+      <x:c r="AP315" s="22"/>
+      <x:c r="AQ315" s="24"/>
+      <x:c r="AR315" s="24"/>
+      <x:c r="AS315" s="22"/>
+      <x:c r="AT315" s="25"/>
+      <x:c r="AU315" s="25"/>
+      <x:c r="AV315" s="22"/>
+      <x:c r="AW315" s="22"/>
+      <x:c r="AX315" s="22"/>
+      <x:c r="AY315" s="22"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="AN316" s="23"/>
+      <x:c r="AO316" s="22"/>
+      <x:c r="AP316" s="22"/>
+      <x:c r="AQ316" s="24"/>
+      <x:c r="AR316" s="24"/>
+      <x:c r="AS316" s="22"/>
+      <x:c r="AT316" s="25"/>
+      <x:c r="AU316" s="25"/>
+      <x:c r="AV316" s="22"/>
+      <x:c r="AW316" s="22"/>
+      <x:c r="AX316" s="22"/>
+      <x:c r="AY316" s="22"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="AN317" s="23"/>
+      <x:c r="AO317" s="22"/>
+      <x:c r="AP317" s="22"/>
+      <x:c r="AQ317" s="24"/>
+      <x:c r="AR317" s="24"/>
+      <x:c r="AS317" s="22"/>
+      <x:c r="AT317" s="25"/>
+      <x:c r="AU317" s="25"/>
+      <x:c r="AV317" s="22"/>
+      <x:c r="AW317" s="22"/>
+      <x:c r="AX317" s="22"/>
+      <x:c r="AY317" s="22"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="AN318" s="23"/>
+      <x:c r="AO318" s="22"/>
+      <x:c r="AP318" s="22"/>
+      <x:c r="AQ318" s="24"/>
+      <x:c r="AR318" s="24"/>
+      <x:c r="AS318" s="22"/>
+      <x:c r="AT318" s="25"/>
+      <x:c r="AU318" s="25"/>
+      <x:c r="AV318" s="22"/>
+      <x:c r="AW318" s="22"/>
+      <x:c r="AX318" s="22"/>
+      <x:c r="AY318" s="22"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="AN319" s="23"/>
+      <x:c r="AO319" s="22"/>
+      <x:c r="AP319" s="22"/>
+      <x:c r="AQ319" s="24"/>
+      <x:c r="AR319" s="24"/>
+      <x:c r="AS319" s="22"/>
+      <x:c r="AT319" s="25"/>
+      <x:c r="AU319" s="25"/>
+      <x:c r="AV319" s="22"/>
+      <x:c r="AW319" s="22"/>
+      <x:c r="AX319" s="22"/>
+      <x:c r="AY319" s="22"/>
+    </x:row>
+    <x:row r="320">
+      <x:c r="AN320" s="23"/>
+      <x:c r="AO320" s="22"/>
+      <x:c r="AP320" s="22"/>
+      <x:c r="AQ320" s="24"/>
+      <x:c r="AR320" s="24"/>
+      <x:c r="AS320" s="22"/>
+      <x:c r="AT320" s="25"/>
+      <x:c r="AU320" s="25"/>
+      <x:c r="AV320" s="22"/>
+      <x:c r="AW320" s="22"/>
+      <x:c r="AX320" s="22"/>
+      <x:c r="AY320" s="22"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="AN321" s="23"/>
+      <x:c r="AO321" s="22"/>
+      <x:c r="AP321" s="22"/>
+      <x:c r="AQ321" s="24"/>
+      <x:c r="AR321" s="24"/>
+      <x:c r="AS321" s="22"/>
+      <x:c r="AT321" s="25"/>
+      <x:c r="AU321" s="25"/>
+      <x:c r="AV321" s="22"/>
+      <x:c r="AW321" s="22"/>
+      <x:c r="AX321" s="22"/>
+      <x:c r="AY321" s="22"/>
+    </x:row>
+    <x:row r="322">
+      <x:c r="AN322" s="23"/>
+      <x:c r="AO322" s="22"/>
+      <x:c r="AP322" s="22"/>
+      <x:c r="AQ322" s="24"/>
+      <x:c r="AR322" s="24"/>
+      <x:c r="AS322" s="22"/>
+      <x:c r="AT322" s="25"/>
+      <x:c r="AU322" s="25"/>
+      <x:c r="AV322" s="22"/>
+      <x:c r="AW322" s="22"/>
+      <x:c r="AX322" s="22"/>
+      <x:c r="AY322" s="22"/>
+    </x:row>
+    <x:row r="323">
+      <x:c r="AN323" s="23"/>
+      <x:c r="AO323" s="22"/>
+      <x:c r="AP323" s="22"/>
+      <x:c r="AQ323" s="24"/>
+      <x:c r="AR323" s="24"/>
+      <x:c r="AS323" s="22"/>
+      <x:c r="AT323" s="25"/>
+      <x:c r="AU323" s="25"/>
+      <x:c r="AV323" s="22"/>
+      <x:c r="AW323" s="22"/>
+      <x:c r="AX323" s="22"/>
+      <x:c r="AY323" s="22"/>
+    </x:row>
+    <x:row r="324">
+      <x:c r="AN324" s="23"/>
+      <x:c r="AO324" s="22"/>
+      <x:c r="AP324" s="22"/>
+      <x:c r="AQ324" s="24"/>
+      <x:c r="AR324" s="24"/>
+      <x:c r="AS324" s="22"/>
+      <x:c r="AT324" s="25"/>
+      <x:c r="AU324" s="25"/>
+      <x:c r="AV324" s="22"/>
+      <x:c r="AW324" s="22"/>
+      <x:c r="AX324" s="22"/>
+      <x:c r="AY324" s="22"/>
+    </x:row>
+    <x:row r="325">
+      <x:c r="AN325" s="23"/>
+      <x:c r="AO325" s="22"/>
+      <x:c r="AP325" s="22"/>
+      <x:c r="AQ325" s="24"/>
+      <x:c r="AR325" s="24"/>
+      <x:c r="AS325" s="22"/>
+      <x:c r="AT325" s="25"/>
+      <x:c r="AU325" s="25"/>
+      <x:c r="AV325" s="22"/>
+      <x:c r="AW325" s="22"/>
+      <x:c r="AX325" s="22"/>
+      <x:c r="AY325" s="22"/>
+    </x:row>
+    <x:row r="326">
+      <x:c r="AN326" s="23"/>
+      <x:c r="AO326" s="22"/>
+      <x:c r="AP326" s="22"/>
+      <x:c r="AQ326" s="24"/>
+      <x:c r="AR326" s="24"/>
+      <x:c r="AS326" s="22"/>
+      <x:c r="AT326" s="25"/>
+      <x:c r="AU326" s="25"/>
+      <x:c r="AV326" s="22"/>
+      <x:c r="AW326" s="22"/>
+      <x:c r="AX326" s="22"/>
+      <x:c r="AY326" s="22"/>
+    </x:row>
+    <x:row r="327">
+      <x:c r="AN327" s="23"/>
+      <x:c r="AO327" s="22"/>
+      <x:c r="AP327" s="22"/>
+      <x:c r="AQ327" s="24"/>
+      <x:c r="AR327" s="24"/>
+      <x:c r="AS327" s="22"/>
+      <x:c r="AT327" s="25"/>
+      <x:c r="AU327" s="25"/>
+      <x:c r="AV327" s="22"/>
+      <x:c r="AW327" s="22"/>
+      <x:c r="AX327" s="22"/>
+      <x:c r="AY327" s="22"/>
+    </x:row>
+    <x:row r="328">
+      <x:c r="AN328" s="23"/>
+      <x:c r="AO328" s="22"/>
+      <x:c r="AP328" s="22"/>
+      <x:c r="AQ328" s="24"/>
+      <x:c r="AR328" s="24"/>
+      <x:c r="AS328" s="22"/>
+      <x:c r="AT328" s="25"/>
+      <x:c r="AU328" s="25"/>
+      <x:c r="AV328" s="22"/>
+      <x:c r="AW328" s="22"/>
+      <x:c r="AX328" s="22"/>
+      <x:c r="AY328" s="22"/>
+    </x:row>
+    <x:row r="329">
+      <x:c r="AN329" s="23"/>
+      <x:c r="AO329" s="22"/>
+      <x:c r="AP329" s="22"/>
+      <x:c r="AQ329" s="24"/>
+      <x:c r="AR329" s="24"/>
+      <x:c r="AS329" s="22"/>
+      <x:c r="AT329" s="25"/>
+      <x:c r="AU329" s="25"/>
+      <x:c r="AV329" s="22"/>
+      <x:c r="AW329" s="22"/>
+      <x:c r="AX329" s="22"/>
+      <x:c r="AY329" s="22"/>
+    </x:row>
+    <x:row r="330">
+      <x:c r="AN330" s="23"/>
+      <x:c r="AO330" s="22"/>
+      <x:c r="AP330" s="22"/>
+      <x:c r="AQ330" s="24"/>
+      <x:c r="AR330" s="24"/>
+      <x:c r="AS330" s="22"/>
+      <x:c r="AT330" s="25"/>
+      <x:c r="AU330" s="25"/>
+      <x:c r="AV330" s="22"/>
+      <x:c r="AW330" s="22"/>
+      <x:c r="AX330" s="22"/>
+      <x:c r="AY330" s="22"/>
+    </x:row>
+    <x:row r="331">
+      <x:c r="AN331" s="23"/>
+      <x:c r="AO331" s="22"/>
+      <x:c r="AP331" s="22"/>
+      <x:c r="AQ331" s="24"/>
+      <x:c r="AR331" s="24"/>
+      <x:c r="AS331" s="22"/>
+      <x:c r="AT331" s="25"/>
+      <x:c r="AU331" s="25"/>
+      <x:c r="AV331" s="22"/>
+      <x:c r="AW331" s="22"/>
+      <x:c r="AX331" s="22"/>
+      <x:c r="AY331" s="22"/>
+    </x:row>
+    <x:row r="332">
+      <x:c r="AN332" s="23"/>
+      <x:c r="AO332" s="22"/>
+      <x:c r="AP332" s="22"/>
+      <x:c r="AQ332" s="24"/>
+      <x:c r="AR332" s="24"/>
+      <x:c r="AS332" s="22"/>
+      <x:c r="AT332" s="25"/>
+      <x:c r="AU332" s="25"/>
+      <x:c r="AV332" s="22"/>
+      <x:c r="AW332" s="22"/>
+      <x:c r="AX332" s="22"/>
+      <x:c r="AY332" s="22"/>
+    </x:row>
+    <x:row r="333">
+      <x:c r="AN333" s="23"/>
+      <x:c r="AO333" s="22"/>
+      <x:c r="AP333" s="22"/>
+      <x:c r="AQ333" s="24"/>
+      <x:c r="AR333" s="24"/>
+      <x:c r="AS333" s="22"/>
+      <x:c r="AT333" s="25"/>
+      <x:c r="AU333" s="25"/>
+      <x:c r="AV333" s="22"/>
+      <x:c r="AW333" s="22"/>
+      <x:c r="AX333" s="22"/>
+      <x:c r="AY333" s="22"/>
+    </x:row>
+    <x:row r="334">
+      <x:c r="AN334" s="23"/>
+      <x:c r="AO334" s="22"/>
+      <x:c r="AP334" s="22"/>
+      <x:c r="AQ334" s="24"/>
+      <x:c r="AR334" s="24"/>
+      <x:c r="AS334" s="22"/>
+      <x:c r="AT334" s="25"/>
+      <x:c r="AU334" s="25"/>
+      <x:c r="AV334" s="22"/>
+      <x:c r="AW334" s="22"/>
+      <x:c r="AX334" s="22"/>
+      <x:c r="AY334" s="22"/>
+    </x:row>
+    <x:row r="335">
+      <x:c r="AN335" s="23"/>
+      <x:c r="AO335" s="22"/>
+      <x:c r="AP335" s="22"/>
+      <x:c r="AQ335" s="24"/>
+      <x:c r="AR335" s="24"/>
+      <x:c r="AS335" s="22"/>
+      <x:c r="AT335" s="25"/>
+      <x:c r="AU335" s="25"/>
+      <x:c r="AV335" s="22"/>
+      <x:c r="AW335" s="22"/>
+      <x:c r="AX335" s="22"/>
+      <x:c r="AY335" s="22"/>
+    </x:row>
+    <x:row r="336">
+      <x:c r="AN336" s="23"/>
+      <x:c r="AO336" s="22"/>
+      <x:c r="AP336" s="22"/>
+      <x:c r="AQ336" s="24"/>
+      <x:c r="AR336" s="24"/>
+      <x:c r="AS336" s="22"/>
+      <x:c r="AT336" s="25"/>
+      <x:c r="AU336" s="25"/>
+      <x:c r="AV336" s="22"/>
+      <x:c r="AW336" s="22"/>
+      <x:c r="AX336" s="22"/>
+      <x:c r="AY336" s="22"/>
+    </x:row>
+    <x:row r="337">
+      <x:c r="AN337" s="23"/>
+      <x:c r="AO337" s="22"/>
+      <x:c r="AP337" s="22"/>
+      <x:c r="AQ337" s="24"/>
+      <x:c r="AR337" s="24"/>
+      <x:c r="AS337" s="22"/>
+      <x:c r="AT337" s="25"/>
+      <x:c r="AU337" s="25"/>
+      <x:c r="AV337" s="22"/>
+      <x:c r="AW337" s="22"/>
+      <x:c r="AX337" s="22"/>
+      <x:c r="AY337" s="22"/>
+    </x:row>
+    <x:row r="338">
+      <x:c r="AN338" s="23"/>
+      <x:c r="AO338" s="22"/>
+      <x:c r="AP338" s="22"/>
+      <x:c r="AQ338" s="24"/>
+      <x:c r="AR338" s="24"/>
+      <x:c r="AS338" s="22"/>
+      <x:c r="AT338" s="25"/>
+      <x:c r="AU338" s="25"/>
+      <x:c r="AV338" s="22"/>
+      <x:c r="AW338" s="22"/>
+      <x:c r="AX338" s="22"/>
+      <x:c r="AY338" s="22"/>
+    </x:row>
+    <x:row r="339">
+      <x:c r="AN339" s="23"/>
+      <x:c r="AO339" s="22"/>
+      <x:c r="AP339" s="22"/>
+      <x:c r="AQ339" s="24"/>
+      <x:c r="AR339" s="24"/>
+      <x:c r="AS339" s="22"/>
+      <x:c r="AT339" s="25"/>
+      <x:c r="AU339" s="25"/>
+      <x:c r="AV339" s="22"/>
+      <x:c r="AW339" s="22"/>
+      <x:c r="AX339" s="22"/>
+      <x:c r="AY339" s="22"/>
+    </x:row>
+    <x:row r="340">
+      <x:c r="AN340" s="23"/>
+      <x:c r="AO340" s="22"/>
+      <x:c r="AP340" s="22"/>
+      <x:c r="AQ340" s="24"/>
+      <x:c r="AR340" s="24"/>
+      <x:c r="AS340" s="22"/>
+      <x:c r="AT340" s="25"/>
+      <x:c r="AU340" s="25"/>
+      <x:c r="AV340" s="22"/>
+      <x:c r="AW340" s="22"/>
+      <x:c r="AX340" s="22"/>
+      <x:c r="AY340" s="22"/>
+    </x:row>
+    <x:row r="341">
+      <x:c r="AN341" s="23"/>
+      <x:c r="AO341" s="22"/>
+      <x:c r="AP341" s="22"/>
+      <x:c r="AQ341" s="24"/>
+      <x:c r="AR341" s="24"/>
+      <x:c r="AS341" s="22"/>
+      <x:c r="AT341" s="25"/>
+      <x:c r="AU341" s="25"/>
+      <x:c r="AV341" s="22"/>
+      <x:c r="AW341" s="22"/>
+      <x:c r="AX341" s="22"/>
+      <x:c r="AY341" s="22"/>
+    </x:row>
+    <x:row r="342">
+      <x:c r="AN342" s="23"/>
+      <x:c r="AO342" s="22"/>
+      <x:c r="AP342" s="22"/>
+      <x:c r="AQ342" s="24"/>
+      <x:c r="AR342" s="24"/>
+      <x:c r="AS342" s="22"/>
+      <x:c r="AT342" s="25"/>
+      <x:c r="AU342" s="25"/>
+      <x:c r="AV342" s="22"/>
+      <x:c r="AW342" s="22"/>
+      <x:c r="AX342" s="22"/>
+      <x:c r="AY342" s="22"/>
+    </x:row>
+    <x:row r="343">
+      <x:c r="AN343" s="23"/>
+      <x:c r="AO343" s="22"/>
+      <x:c r="AP343" s="22"/>
+      <x:c r="AQ343" s="24"/>
+      <x:c r="AR343" s="24"/>
+      <x:c r="AS343" s="22"/>
+      <x:c r="AT343" s="25"/>
+      <x:c r="AU343" s="25"/>
+      <x:c r="AV343" s="22"/>
+      <x:c r="AW343" s="22"/>
+      <x:c r="AX343" s="22"/>
+      <x:c r="AY343" s="22"/>
+    </x:row>
+    <x:row r="344">
+      <x:c r="AN344" s="23"/>
+      <x:c r="AO344" s="22"/>
+      <x:c r="AP344" s="22"/>
+      <x:c r="AQ344" s="24"/>
+      <x:c r="AR344" s="24"/>
+      <x:c r="AS344" s="22"/>
+      <x:c r="AT344" s="25"/>
+      <x:c r="AU344" s="25"/>
+      <x:c r="AV344" s="22"/>
+      <x:c r="AW344" s="22"/>
+      <x:c r="AX344" s="22"/>
+      <x:c r="AY344" s="22"/>
+    </x:row>
+    <x:row r="345">
+      <x:c r="AN345" s="23"/>
+      <x:c r="AO345" s="22"/>
+      <x:c r="AP345" s="22"/>
+      <x:c r="AQ345" s="24"/>
+      <x:c r="AR345" s="24"/>
+      <x:c r="AS345" s="22"/>
+      <x:c r="AT345" s="25"/>
+      <x:c r="AU345" s="25"/>
+      <x:c r="AV345" s="22"/>
+      <x:c r="AW345" s="22"/>
+      <x:c r="AX345" s="22"/>
+      <x:c r="AY345" s="22"/>
+    </x:row>
+    <x:row r="346">
+      <x:c r="AN346" s="23"/>
+      <x:c r="AO346" s="22"/>
+      <x:c r="AP346" s="22"/>
+      <x:c r="AQ346" s="24"/>
+      <x:c r="AR346" s="24"/>
+      <x:c r="AS346" s="22"/>
+      <x:c r="AT346" s="25"/>
+      <x:c r="AU346" s="25"/>
+      <x:c r="AV346" s="22"/>
+      <x:c r="AW346" s="22"/>
+      <x:c r="AX346" s="22"/>
+      <x:c r="AY346" s="22"/>
+    </x:row>
+    <x:row r="347">
+      <x:c r="AN347" s="23"/>
+      <x:c r="AO347" s="22"/>
+      <x:c r="AP347" s="22"/>
+      <x:c r="AQ347" s="24"/>
+      <x:c r="AR347" s="24"/>
+      <x:c r="AS347" s="22"/>
+      <x:c r="AT347" s="25"/>
+      <x:c r="AU347" s="25"/>
+      <x:c r="AV347" s="22"/>
+      <x:c r="AW347" s="22"/>
+      <x:c r="AX347" s="22"/>
+      <x:c r="AY347" s="22"/>
+    </x:row>
+    <x:row r="348">
+      <x:c r="AN348" s="23"/>
+      <x:c r="AO348" s="22"/>
+      <x:c r="AP348" s="22"/>
+      <x:c r="AQ348" s="24"/>
+      <x:c r="AR348" s="24"/>
+      <x:c r="AS348" s="22"/>
+      <x:c r="AT348" s="25"/>
+      <x:c r="AU348" s="25"/>
+      <x:c r="AV348" s="22"/>
+      <x:c r="AW348" s="22"/>
+      <x:c r="AX348" s="22"/>
+      <x:c r="AY348" s="22"/>
+    </x:row>
+    <x:row r="349">
+      <x:c r="AN349" s="23"/>
+      <x:c r="AO349" s="22"/>
+      <x:c r="AP349" s="22"/>
+      <x:c r="AQ349" s="24"/>
+      <x:c r="AR349" s="24"/>
+      <x:c r="AS349" s="22"/>
+      <x:c r="AT349" s="25"/>
+      <x:c r="AU349" s="25"/>
+      <x:c r="AV349" s="22"/>
+      <x:c r="AW349" s="22"/>
+      <x:c r="AX349" s="22"/>
+      <x:c r="AY349" s="22"/>
+    </x:row>
+    <x:row r="350">
+      <x:c r="AN350" s="23"/>
+      <x:c r="AO350" s="22"/>
+      <x:c r="AP350" s="22"/>
+      <x:c r="AQ350" s="24"/>
+      <x:c r="AR350" s="24"/>
+      <x:c r="AS350" s="22"/>
+      <x:c r="AT350" s="25"/>
+      <x:c r="AU350" s="25"/>
+      <x:c r="AV350" s="22"/>
+      <x:c r="AW350" s="22"/>
+      <x:c r="AX350" s="22"/>
+      <x:c r="AY350" s="22"/>
+    </x:row>
+    <x:row r="351">
+      <x:c r="AN351" s="23"/>
+      <x:c r="AO351" s="22"/>
+      <x:c r="AP351" s="22"/>
+      <x:c r="AQ351" s="24"/>
+      <x:c r="AR351" s="24"/>
+      <x:c r="AS351" s="22"/>
+      <x:c r="AT351" s="25"/>
+      <x:c r="AU351" s="25"/>
+      <x:c r="AV351" s="22"/>
+      <x:c r="AW351" s="22"/>
+      <x:c r="AX351" s="22"/>
+      <x:c r="AY351" s="22"/>
+    </x:row>
+    <x:row r="352">
+      <x:c r="AN352" s="23"/>
+      <x:c r="AO352" s="22"/>
+      <x:c r="AP352" s="22"/>
+      <x:c r="AQ352" s="24"/>
+      <x:c r="AR352" s="24"/>
+      <x:c r="AS352" s="22"/>
+      <x:c r="AT352" s="25"/>
+      <x:c r="AU352" s="25"/>
+      <x:c r="AV352" s="22"/>
+      <x:c r="AW352" s="22"/>
+      <x:c r="AX352" s="22"/>
+      <x:c r="AY352" s="22"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="AN353" s="23"/>
+      <x:c r="AO353" s="22"/>
+      <x:c r="AP353" s="22"/>
+      <x:c r="AQ353" s="24"/>
+      <x:c r="AR353" s="24"/>
+      <x:c r="AS353" s="22"/>
+      <x:c r="AT353" s="25"/>
+      <x:c r="AU353" s="25"/>
+      <x:c r="AV353" s="22"/>
+      <x:c r="AW353" s="22"/>
+      <x:c r="AX353" s="22"/>
+      <x:c r="AY353" s="22"/>
+    </x:row>
+    <x:row r="354">
+      <x:c r="AN354" s="23"/>
+      <x:c r="AO354" s="22"/>
+      <x:c r="AP354" s="22"/>
+      <x:c r="AQ354" s="24"/>
+      <x:c r="AR354" s="24"/>
+      <x:c r="AS354" s="22"/>
+      <x:c r="AT354" s="25"/>
+      <x:c r="AU354" s="25"/>
+      <x:c r="AV354" s="22"/>
+      <x:c r="AW354" s="22"/>
+      <x:c r="AX354" s="22"/>
+      <x:c r="AY354" s="22"/>
+    </x:row>
+    <x:row r="355">
+      <x:c r="AN355" s="23"/>
+      <x:c r="AO355" s="22"/>
+      <x:c r="AP355" s="22"/>
+      <x:c r="AQ355" s="24"/>
+      <x:c r="AR355" s="24"/>
+      <x:c r="AS355" s="22"/>
+      <x:c r="AT355" s="25"/>
+      <x:c r="AU355" s="25"/>
+      <x:c r="AV355" s="22"/>
+      <x:c r="AW355" s="22"/>
+      <x:c r="AX355" s="22"/>
+      <x:c r="AY355" s="22"/>
+    </x:row>
+    <x:row r="356">
+      <x:c r="AN356" s="23"/>
+      <x:c r="AO356" s="22"/>
+      <x:c r="AP356" s="22"/>
+      <x:c r="AQ356" s="24"/>
+      <x:c r="AR356" s="24"/>
+      <x:c r="AS356" s="22"/>
+      <x:c r="AT356" s="25"/>
+      <x:c r="AU356" s="25"/>
+      <x:c r="AV356" s="22"/>
+      <x:c r="AW356" s="22"/>
+      <x:c r="AX356" s="22"/>
+      <x:c r="AY356" s="22"/>
+    </x:row>
+    <x:row r="357">
+      <x:c r="AN357" s="23"/>
+      <x:c r="AO357" s="22"/>
+      <x:c r="AP357" s="22"/>
+      <x:c r="AQ357" s="24"/>
+      <x:c r="AR357" s="24"/>
+      <x:c r="AS357" s="22"/>
+      <x:c r="AT357" s="25"/>
+      <x:c r="AU357" s="25"/>
+      <x:c r="AV357" s="22"/>
+      <x:c r="AW357" s="22"/>
+      <x:c r="AX357" s="22"/>
+      <x:c r="AY357" s="22"/>
+    </x:row>
+    <x:row r="358">
+      <x:c r="AN358" s="23"/>
+      <x:c r="AO358" s="22"/>
+      <x:c r="AP358" s="22"/>
+      <x:c r="AQ358" s="24"/>
+      <x:c r="AR358" s="24"/>
+      <x:c r="AS358" s="22"/>
+      <x:c r="AT358" s="25"/>
+      <x:c r="AU358" s="25"/>
+      <x:c r="AV358" s="22"/>
+      <x:c r="AW358" s="22"/>
+      <x:c r="AX358" s="22"/>
+      <x:c r="AY358" s="22"/>
+    </x:row>
+    <x:row r="359">
+      <x:c r="AN359" s="23"/>
+      <x:c r="AO359" s="22"/>
+      <x:c r="AP359" s="22"/>
+      <x:c r="AQ359" s="24"/>
+      <x:c r="AR359" s="24"/>
+      <x:c r="AS359" s="22"/>
+      <x:c r="AT359" s="25"/>
+      <x:c r="AU359" s="25"/>
+      <x:c r="AV359" s="22"/>
+      <x:c r="AW359" s="22"/>
+      <x:c r="AX359" s="22"/>
+      <x:c r="AY359" s="22"/>
+    </x:row>
+    <x:row r="360">
+      <x:c r="AN360" s="23"/>
+      <x:c r="AO360" s="22"/>
+      <x:c r="AP360" s="22"/>
+      <x:c r="AQ360" s="24"/>
+      <x:c r="AR360" s="24"/>
+      <x:c r="AS360" s="22"/>
+      <x:c r="AT360" s="25"/>
+      <x:c r="AU360" s="25"/>
+      <x:c r="AV360" s="22"/>
+      <x:c r="AW360" s="22"/>
+      <x:c r="AX360" s="22"/>
+      <x:c r="AY360" s="22"/>
+    </x:row>
+    <x:row r="361">
+      <x:c r="AN361" s="23"/>
+      <x:c r="AO361" s="22"/>
+      <x:c r="AP361" s="22"/>
+      <x:c r="AQ361" s="24"/>
+      <x:c r="AR361" s="24"/>
+      <x:c r="AS361" s="22"/>
+      <x:c r="AT361" s="25"/>
+      <x:c r="AU361" s="25"/>
+      <x:c r="AV361" s="22"/>
+      <x:c r="AW361" s="22"/>
+      <x:c r="AX361" s="22"/>
+      <x:c r="AY361" s="22"/>
+    </x:row>
+    <x:row r="362">
+      <x:c r="AN362" s="23"/>
+      <x:c r="AO362" s="22"/>
+      <x:c r="AP362" s="22"/>
+      <x:c r="AQ362" s="24"/>
+      <x:c r="AR362" s="24"/>
+      <x:c r="AS362" s="22"/>
+      <x:c r="AT362" s="25"/>
+      <x:c r="AU362" s="25"/>
+      <x:c r="AV362" s="22"/>
+      <x:c r="AW362" s="22"/>
+      <x:c r="AX362" s="22"/>
+      <x:c r="AY362" s="22"/>
+    </x:row>
+    <x:row r="363">
+      <x:c r="AN363" s="23"/>
+      <x:c r="AO363" s="22"/>
+      <x:c r="AP363" s="22"/>
+      <x:c r="AQ363" s="24"/>
+      <x:c r="AR363" s="24"/>
+      <x:c r="AS363" s="22"/>
+      <x:c r="AT363" s="25"/>
+      <x:c r="AU363" s="25"/>
+      <x:c r="AV363" s="22"/>
+      <x:c r="AW363" s="22"/>
+      <x:c r="AX363" s="22"/>
+      <x:c r="AY363" s="22"/>
+    </x:row>
+    <x:row r="364">
+      <x:c r="AN364" s="23"/>
+      <x:c r="AO364" s="22"/>
+      <x:c r="AP364" s="22"/>
+      <x:c r="AQ364" s="24"/>
+      <x:c r="AR364" s="24"/>
+      <x:c r="AS364" s="22"/>
+      <x:c r="AT364" s="25"/>
+      <x:c r="AU364" s="25"/>
+      <x:c r="AV364" s="22"/>
+      <x:c r="AW364" s="22"/>
+      <x:c r="AX364" s="22"/>
+      <x:c r="AY364" s="22"/>
+    </x:row>
+    <x:row r="365">
+      <x:c r="AN365" s="23"/>
+      <x:c r="AO365" s="22"/>
+      <x:c r="AP365" s="22"/>
+      <x:c r="AQ365" s="24"/>
+      <x:c r="AR365" s="24"/>
+      <x:c r="AS365" s="22"/>
+      <x:c r="AT365" s="25"/>
+      <x:c r="AU365" s="25"/>
+      <x:c r="AV365" s="22"/>
+      <x:c r="AW365" s="22"/>
+      <x:c r="AX365" s="22"/>
+      <x:c r="AY365" s="22"/>
+    </x:row>
+    <x:row r="366">
+      <x:c r="AN366" s="23"/>
+      <x:c r="AO366" s="22"/>
+      <x:c r="AP366" s="22"/>
+      <x:c r="AQ366" s="24"/>
+      <x:c r="AR366" s="24"/>
+      <x:c r="AS366" s="22"/>
+      <x:c r="AT366" s="25"/>
+      <x:c r="AU366" s="25"/>
+      <x:c r="AV366" s="22"/>
+      <x:c r="AW366" s="22"/>
+      <x:c r="AX366" s="22"/>
+      <x:c r="AY366" s="22"/>
+    </x:row>
+    <x:row r="367">
+      <x:c r="AN367" s="23"/>
+      <x:c r="AO367" s="22"/>
+      <x:c r="AP367" s="22"/>
+      <x:c r="AQ367" s="24"/>
+      <x:c r="AR367" s="24"/>
+      <x:c r="AS367" s="22"/>
+      <x:c r="AT367" s="25"/>
+      <x:c r="AU367" s="25"/>
+      <x:c r="AV367" s="22"/>
+      <x:c r="AW367" s="22"/>
+      <x:c r="AX367" s="22"/>
+      <x:c r="AY367" s="22"/>
+    </x:row>
+    <x:row r="368">
+      <x:c r="AN368" s="23"/>
+      <x:c r="AO368" s="22"/>
+      <x:c r="AP368" s="22"/>
+      <x:c r="AQ368" s="24"/>
+      <x:c r="AR368" s="24"/>
+      <x:c r="AS368" s="22"/>
+      <x:c r="AT368" s="25"/>
+      <x:c r="AU368" s="25"/>
+      <x:c r="AV368" s="22"/>
+      <x:c r="AW368" s="22"/>
+      <x:c r="AX368" s="22"/>
+      <x:c r="AY368" s="22"/>
+    </x:row>
+    <x:row r="369">
+      <x:c r="AN369" s="23"/>
+      <x:c r="AO369" s="22"/>
+      <x:c r="AP369" s="22"/>
+      <x:c r="AQ369" s="24"/>
+      <x:c r="AR369" s="24"/>
+      <x:c r="AS369" s="22"/>
+      <x:c r="AT369" s="25"/>
+      <x:c r="AU369" s="25"/>
+      <x:c r="AV369" s="22"/>
+      <x:c r="AW369" s="22"/>
+      <x:c r="AX369" s="22"/>
+      <x:c r="AY369" s="22"/>
+    </x:row>
+    <x:row r="370">
+      <x:c r="AN370" s="23"/>
+      <x:c r="AO370" s="22"/>
+      <x:c r="AP370" s="22"/>
+      <x:c r="AQ370" s="24"/>
+      <x:c r="AR370" s="24"/>
+      <x:c r="AS370" s="22"/>
+      <x:c r="AT370" s="25"/>
+      <x:c r="AU370" s="25"/>
+      <x:c r="AV370" s="22"/>
+      <x:c r="AW370" s="22"/>
+      <x:c r="AX370" s="22"/>
+      <x:c r="AY370" s="22"/>
+    </x:row>
+    <x:row r="371">
+      <x:c r="AN371" s="23"/>
+      <x:c r="AO371" s="22"/>
+      <x:c r="AP371" s="22"/>
+      <x:c r="AQ371" s="24"/>
+      <x:c r="AR371" s="24"/>
+      <x:c r="AS371" s="22"/>
+      <x:c r="AT371" s="25"/>
+      <x:c r="AU371" s="25"/>
+      <x:c r="AV371" s="22"/>
+      <x:c r="AW371" s="22"/>
+      <x:c r="AX371" s="22"/>
+      <x:c r="AY371" s="22"/>
+    </x:row>
+    <x:row r="372">
+      <x:c r="AN372" s="23"/>
+      <x:c r="AO372" s="22"/>
+      <x:c r="AP372" s="22"/>
+      <x:c r="AQ372" s="24"/>
+      <x:c r="AR372" s="24"/>
+      <x:c r="AS372" s="22"/>
+      <x:c r="AT372" s="25"/>
+      <x:c r="AU372" s="25"/>
+      <x:c r="AV372" s="22"/>
+      <x:c r="AW372" s="22"/>
+      <x:c r="AX372" s="22"/>
+      <x:c r="AY372" s="22"/>
+    </x:row>
+    <x:row r="373">
+      <x:c r="AN373" s="23"/>
+      <x:c r="AO373" s="22"/>
+      <x:c r="AP373" s="22"/>
+      <x:c r="AQ373" s="24"/>
+      <x:c r="AR373" s="24"/>
+      <x:c r="AS373" s="22"/>
+      <x:c r="AT373" s="25"/>
+      <x:c r="AU373" s="25"/>
+      <x:c r="AV373" s="22"/>
+      <x:c r="AW373" s="22"/>
+      <x:c r="AX373" s="22"/>
+      <x:c r="AY373" s="22"/>
+    </x:row>
+    <x:row r="374">
+      <x:c r="AN374" s="23"/>
+      <x:c r="AO374" s="22"/>
+      <x:c r="AP374" s="22"/>
+      <x:c r="AQ374" s="24"/>
+      <x:c r="AR374" s="24"/>
+      <x:c r="AS374" s="22"/>
+      <x:c r="AT374" s="25"/>
+      <x:c r="AU374" s="25"/>
+      <x:c r="AV374" s="22"/>
+      <x:c r="AW374" s="22"/>
+      <x:c r="AX374" s="22"/>
+      <x:c r="AY374" s="22"/>
+    </x:row>
+    <x:row r="375">
+      <x:c r="AN375" s="23"/>
+      <x:c r="AO375" s="22"/>
+      <x:c r="AP375" s="22"/>
+      <x:c r="AQ375" s="24"/>
+      <x:c r="AR375" s="24"/>
+      <x:c r="AS375" s="22"/>
+      <x:c r="AT375" s="25"/>
+      <x:c r="AU375" s="25"/>
+      <x:c r="AV375" s="22"/>
+      <x:c r="AW375" s="22"/>
+      <x:c r="AX375" s="22"/>
+      <x:c r="AY375" s="22"/>
+    </x:row>
+    <x:row r="376">
+      <x:c r="AN376" s="23"/>
+      <x:c r="AO376" s="22"/>
+      <x:c r="AP376" s="22"/>
+      <x:c r="AQ376" s="24"/>
+      <x:c r="AR376" s="24"/>
+      <x:c r="AS376" s="22"/>
+      <x:c r="AT376" s="25"/>
+      <x:c r="AU376" s="25"/>
+      <x:c r="AV376" s="22"/>
+      <x:c r="AW376" s="22"/>
+      <x:c r="AX376" s="22"/>
+      <x:c r="AY376" s="22"/>
+    </x:row>
+    <x:row r="377">
+      <x:c r="AN377" s="23"/>
+      <x:c r="AO377" s="22"/>
+      <x:c r="AP377" s="22"/>
+      <x:c r="AQ377" s="24"/>
+      <x:c r="AR377" s="24"/>
+      <x:c r="AS377" s="22"/>
+      <x:c r="AT377" s="25"/>
+      <x:c r="AU377" s="25"/>
+      <x:c r="AV377" s="22"/>
+      <x:c r="AW377" s="22"/>
+      <x:c r="AX377" s="22"/>
+      <x:c r="AY377" s="22"/>
+    </x:row>
+    <x:row r="378">
+      <x:c r="AN378" s="23"/>
+      <x:c r="AO378" s="22"/>
+      <x:c r="AP378" s="22"/>
+      <x:c r="AQ378" s="24"/>
+      <x:c r="AR378" s="24"/>
+      <x:c r="AS378" s="22"/>
+      <x:c r="AT378" s="25"/>
+      <x:c r="AU378" s="25"/>
+      <x:c r="AV378" s="22"/>
+      <x:c r="AW378" s="22"/>
+      <x:c r="AX378" s="22"/>
+      <x:c r="AY378" s="22"/>
+    </x:row>
+    <x:row r="379">
+      <x:c r="AN379" s="23"/>
+      <x:c r="AO379" s="22"/>
+      <x:c r="AP379" s="22"/>
+      <x:c r="AQ379" s="24"/>
+      <x:c r="AR379" s="24"/>
+      <x:c r="AS379" s="22"/>
+      <x:c r="AT379" s="25"/>
+      <x:c r="AU379" s="25"/>
+      <x:c r="AV379" s="22"/>
+      <x:c r="AW379" s="22"/>
+      <x:c r="AX379" s="22"/>
+      <x:c r="AY379" s="22"/>
+    </x:row>
+    <x:row r="380">
+      <x:c r="AN380" s="23"/>
+      <x:c r="AO380" s="22"/>
+      <x:c r="AP380" s="22"/>
+      <x:c r="AQ380" s="24"/>
+      <x:c r="AR380" s="24"/>
+      <x:c r="AS380" s="22"/>
+      <x:c r="AT380" s="25"/>
+      <x:c r="AU380" s="25"/>
+      <x:c r="AV380" s="22"/>
+      <x:c r="AW380" s="22"/>
+      <x:c r="AX380" s="22"/>
+      <x:c r="AY380" s="22"/>
+    </x:row>
+    <x:row r="381">
+      <x:c r="AN381" s="23"/>
+      <x:c r="AO381" s="22"/>
+      <x:c r="AP381" s="22"/>
+      <x:c r="AQ381" s="24"/>
+      <x:c r="AR381" s="24"/>
+      <x:c r="AS381" s="22"/>
+      <x:c r="AT381" s="25"/>
+      <x:c r="AU381" s="25"/>
+      <x:c r="AV381" s="22"/>
+      <x:c r="AW381" s="22"/>
+      <x:c r="AX381" s="22"/>
+      <x:c r="AY381" s="22"/>
+    </x:row>
+    <x:row r="382">
+      <x:c r="AN382" s="23"/>
+      <x:c r="AO382" s="22"/>
+      <x:c r="AP382" s="22"/>
+      <x:c r="AQ382" s="24"/>
+      <x:c r="AR382" s="24"/>
+      <x:c r="AS382" s="22"/>
+      <x:c r="AT382" s="25"/>
+      <x:c r="AU382" s="25"/>
+      <x:c r="AV382" s="22"/>
+      <x:c r="AW382" s="22"/>
+      <x:c r="AX382" s="22"/>
+      <x:c r="AY382" s="22"/>
+    </x:row>
+    <x:row r="383">
+      <x:c r="AN383" s="23"/>
+      <x:c r="AO383" s="22"/>
+      <x:c r="AP383" s="22"/>
+      <x:c r="AQ383" s="24"/>
+      <x:c r="AR383" s="24"/>
+      <x:c r="AS383" s="22"/>
+      <x:c r="AT383" s="25"/>
+      <x:c r="AU383" s="25"/>
+      <x:c r="AV383" s="22"/>
+      <x:c r="AW383" s="22"/>
+      <x:c r="AX383" s="22"/>
+      <x:c r="AY383" s="22"/>
+    </x:row>
+    <x:row r="384">
+      <x:c r="AN384" s="23"/>
+      <x:c r="AO384" s="22"/>
+      <x:c r="AP384" s="22"/>
+      <x:c r="AQ384" s="24"/>
+      <x:c r="AR384" s="24"/>
+      <x:c r="AS384" s="22"/>
+      <x:c r="AT384" s="25"/>
+      <x:c r="AU384" s="25"/>
+      <x:c r="AV384" s="22"/>
+      <x:c r="AW384" s="22"/>
+      <x:c r="AX384" s="22"/>
+      <x:c r="AY384" s="22"/>
+    </x:row>
+    <x:row r="385">
+      <x:c r="AN385" s="23"/>
+      <x:c r="AO385" s="22"/>
+      <x:c r="AP385" s="22"/>
+      <x:c r="AQ385" s="24"/>
+      <x:c r="AR385" s="24"/>
+      <x:c r="AS385" s="22"/>
+      <x:c r="AT385" s="25"/>
+      <x:c r="AU385" s="25"/>
+      <x:c r="AV385" s="22"/>
+      <x:c r="AW385" s="22"/>
+      <x:c r="AX385" s="22"/>
+      <x:c r="AY385" s="22"/>
+    </x:row>
+    <x:row r="386">
+      <x:c r="AN386" s="23"/>
+      <x:c r="AO386" s="22"/>
+      <x:c r="AP386" s="22"/>
+      <x:c r="AQ386" s="24"/>
+      <x:c r="AR386" s="24"/>
+      <x:c r="AS386" s="22"/>
+      <x:c r="AT386" s="25"/>
+      <x:c r="AU386" s="25"/>
+      <x:c r="AV386" s="22"/>
+      <x:c r="AW386" s="22"/>
+      <x:c r="AX386" s="22"/>
+      <x:c r="AY386" s="22"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="AN387" s="23"/>
+      <x:c r="AO387" s="22"/>
+      <x:c r="AP387" s="22"/>
+      <x:c r="AQ387" s="24"/>
+      <x:c r="AR387" s="24"/>
+      <x:c r="AS387" s="22"/>
+      <x:c r="AT387" s="25"/>
+      <x:c r="AU387" s="25"/>
+      <x:c r="AV387" s="22"/>
+      <x:c r="AW387" s="22"/>
+      <x:c r="AX387" s="22"/>
+      <x:c r="AY387" s="22"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="AN388" s="23"/>
+      <x:c r="AO388" s="22"/>
+      <x:c r="AP388" s="22"/>
+      <x:c r="AQ388" s="24"/>
+      <x:c r="AR388" s="24"/>
+      <x:c r="AS388" s="22"/>
+      <x:c r="AT388" s="25"/>
+      <x:c r="AU388" s="25"/>
+      <x:c r="AV388" s="22"/>
+      <x:c r="AW388" s="22"/>
+      <x:c r="AX388" s="22"/>
+      <x:c r="AY388" s="22"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="AN389" s="23"/>
+      <x:c r="AO389" s="22"/>
+      <x:c r="AP389" s="22"/>
+      <x:c r="AQ389" s="24"/>
+      <x:c r="AR389" s="24"/>
+      <x:c r="AS389" s="22"/>
+      <x:c r="AT389" s="25"/>
+      <x:c r="AU389" s="25"/>
+      <x:c r="AV389" s="22"/>
+      <x:c r="AW389" s="22"/>
+      <x:c r="AX389" s="22"/>
+      <x:c r="AY389" s="22"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="AN390" s="23"/>
+      <x:c r="AO390" s="22"/>
+      <x:c r="AP390" s="22"/>
+      <x:c r="AQ390" s="24"/>
+      <x:c r="AR390" s="24"/>
+      <x:c r="AS390" s="22"/>
+      <x:c r="AT390" s="25"/>
+      <x:c r="AU390" s="25"/>
+      <x:c r="AV390" s="22"/>
+      <x:c r="AW390" s="22"/>
+      <x:c r="AX390" s="22"/>
+      <x:c r="AY390" s="22"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="AN391" s="23"/>
+      <x:c r="AO391" s="22"/>
+      <x:c r="AP391" s="22"/>
+      <x:c r="AQ391" s="24"/>
+      <x:c r="AR391" s="24"/>
+      <x:c r="AS391" s="22"/>
+      <x:c r="AT391" s="25"/>
+      <x:c r="AU391" s="25"/>
+      <x:c r="AV391" s="22"/>
+      <x:c r="AW391" s="22"/>
+      <x:c r="AX391" s="22"/>
+      <x:c r="AY391" s="22"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="AN392" s="23"/>
+      <x:c r="AO392" s="22"/>
+      <x:c r="AP392" s="22"/>
+      <x:c r="AQ392" s="24"/>
+      <x:c r="AR392" s="24"/>
+      <x:c r="AS392" s="22"/>
+      <x:c r="AT392" s="25"/>
+      <x:c r="AU392" s="25"/>
+      <x:c r="AV392" s="22"/>
+      <x:c r="AW392" s="22"/>
+      <x:c r="AX392" s="22"/>
+      <x:c r="AY392" s="22"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="AN393" s="23"/>
+      <x:c r="AO393" s="22"/>
+      <x:c r="AP393" s="22"/>
+      <x:c r="AQ393" s="24"/>
+      <x:c r="AR393" s="24"/>
+      <x:c r="AS393" s="22"/>
+      <x:c r="AT393" s="25"/>
+      <x:c r="AU393" s="25"/>
+      <x:c r="AV393" s="22"/>
+      <x:c r="AW393" s="22"/>
+      <x:c r="AX393" s="22"/>
+      <x:c r="AY393" s="22"/>
+    </x:row>
+    <x:row r="394">
+      <x:c r="AN394" s="23"/>
+      <x:c r="AO394" s="22"/>
+      <x:c r="AP394" s="22"/>
+      <x:c r="AQ394" s="24"/>
+      <x:c r="AR394" s="24"/>
+      <x:c r="AS394" s="22"/>
+      <x:c r="AT394" s="25"/>
+      <x:c r="AU394" s="25"/>
+      <x:c r="AV394" s="22"/>
+      <x:c r="AW394" s="22"/>
+      <x:c r="AX394" s="22"/>
+      <x:c r="AY394" s="22"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="AN395" s="23"/>
+      <x:c r="AO395" s="22"/>
+      <x:c r="AP395" s="22"/>
+      <x:c r="AQ395" s="24"/>
+      <x:c r="AR395" s="24"/>
+      <x:c r="AS395" s="22"/>
+      <x:c r="AT395" s="25"/>
+      <x:c r="AU395" s="25"/>
+      <x:c r="AV395" s="22"/>
+      <x:c r="AW395" s="22"/>
+      <x:c r="AX395" s="22"/>
+      <x:c r="AY395" s="22"/>
+    </x:row>
+    <x:row r="396">
+      <x:c r="AN396" s="23"/>
+      <x:c r="AO396" s="22"/>
+      <x:c r="AP396" s="22"/>
+      <x:c r="AQ396" s="24"/>
+      <x:c r="AR396" s="24"/>
+      <x:c r="AS396" s="22"/>
+      <x:c r="AT396" s="25"/>
+      <x:c r="AU396" s="25"/>
+      <x:c r="AV396" s="22"/>
+      <x:c r="AW396" s="22"/>
+      <x:c r="AX396" s="22"/>
+      <x:c r="AY396" s="22"/>
+    </x:row>
+    <x:row r="397">
+      <x:c r="AN397" s="23"/>
+      <x:c r="AO397" s="22"/>
+      <x:c r="AP397" s="22"/>
+      <x:c r="AQ397" s="24"/>
+      <x:c r="AR397" s="24"/>
+      <x:c r="AS397" s="22"/>
+      <x:c r="AT397" s="25"/>
+      <x:c r="AU397" s="25"/>
+      <x:c r="AV397" s="22"/>
+      <x:c r="AW397" s="22"/>
+      <x:c r="AX397" s="22"/>
+      <x:c r="AY397" s="22"/>
+    </x:row>
+    <x:row r="398">
+      <x:c r="AN398" s="23"/>
+      <x:c r="AO398" s="22"/>
+      <x:c r="AP398" s="22"/>
+      <x:c r="AQ398" s="24"/>
+      <x:c r="AR398" s="24"/>
+      <x:c r="AS398" s="22"/>
+      <x:c r="AT398" s="25"/>
+      <x:c r="AU398" s="25"/>
+      <x:c r="AV398" s="22"/>
+      <x:c r="AW398" s="22"/>
+      <x:c r="AX398" s="22"/>
+      <x:c r="AY398" s="22"/>
+    </x:row>
+    <x:row r="399">
+      <x:c r="AN399" s="23"/>
+      <x:c r="AO399" s="22"/>
+      <x:c r="AP399" s="22"/>
+      <x:c r="AQ399" s="24"/>
+      <x:c r="AR399" s="24"/>
+      <x:c r="AS399" s="22"/>
+      <x:c r="AT399" s="25"/>
+      <x:c r="AU399" s="25"/>
+      <x:c r="AV399" s="22"/>
+      <x:c r="AW399" s="22"/>
+      <x:c r="AX399" s="22"/>
+      <x:c r="AY399" s="22"/>
+    </x:row>
+    <x:row r="400">
+      <x:c r="AN400" s="23"/>
+      <x:c r="AO400" s="22"/>
+      <x:c r="AP400" s="22"/>
+      <x:c r="AQ400" s="24"/>
+      <x:c r="AR400" s="24"/>
+      <x:c r="AS400" s="22"/>
+      <x:c r="AT400" s="25"/>
+      <x:c r="AU400" s="25"/>
+      <x:c r="AV400" s="22"/>
+      <x:c r="AW400" s="22"/>
+      <x:c r="AX400" s="22"/>
+      <x:c r="AY400" s="22"/>
+    </x:row>
+    <x:row r="401">
+      <x:c r="AN401" s="23"/>
+      <x:c r="AO401" s="22"/>
+      <x:c r="AP401" s="22"/>
+      <x:c r="AQ401" s="24"/>
+      <x:c r="AR401" s="24"/>
+      <x:c r="AS401" s="22"/>
+      <x:c r="AT401" s="25"/>
+      <x:c r="AU401" s="25"/>
+      <x:c r="AV401" s="22"/>
+      <x:c r="AW401" s="22"/>
+      <x:c r="AX401" s="22"/>
+      <x:c r="AY401" s="22"/>
+    </x:row>
+    <x:row r="402">
+      <x:c r="AN402" s="23"/>
+      <x:c r="AO402" s="22"/>
+      <x:c r="AP402" s="22"/>
+      <x:c r="AQ402" s="24"/>
+      <x:c r="AR402" s="24"/>
+      <x:c r="AS402" s="22"/>
+      <x:c r="AT402" s="25"/>
+      <x:c r="AU402" s="25"/>
+      <x:c r="AV402" s="22"/>
+      <x:c r="AW402" s="22"/>
+      <x:c r="AX402" s="22"/>
+      <x:c r="AY402" s="22"/>
+    </x:row>
+    <x:row r="403">
+      <x:c r="AN403" s="23"/>
+      <x:c r="AO403" s="22"/>
+      <x:c r="AP403" s="22"/>
+      <x:c r="AQ403" s="24"/>
+      <x:c r="AR403" s="24"/>
+      <x:c r="AS403" s="22"/>
+      <x:c r="AT403" s="25"/>
+      <x:c r="AU403" s="25"/>
+      <x:c r="AV403" s="22"/>
+      <x:c r="AW403" s="22"/>
+      <x:c r="AX403" s="22"/>
+      <x:c r="AY403" s="22"/>
+    </x:row>
+    <x:row r="404">
+      <x:c r="AN404" s="23"/>
+      <x:c r="AO404" s="22"/>
+      <x:c r="AP404" s="22"/>
+      <x:c r="AQ404" s="24"/>
+      <x:c r="AR404" s="24"/>
+      <x:c r="AS404" s="22"/>
+      <x:c r="AT404" s="25"/>
+      <x:c r="AU404" s="25"/>
+      <x:c r="AV404" s="22"/>
+      <x:c r="AW404" s="22"/>
+      <x:c r="AX404" s="22"/>
+      <x:c r="AY404" s="22"/>
+    </x:row>
+    <x:row r="405">
+      <x:c r="AN405" s="23"/>
+      <x:c r="AO405" s="22"/>
+      <x:c r="AP405" s="22"/>
+      <x:c r="AQ405" s="24"/>
+      <x:c r="AR405" s="24"/>
+      <x:c r="AS405" s="22"/>
+      <x:c r="AT405" s="25"/>
+      <x:c r="AU405" s="25"/>
+      <x:c r="AV405" s="22"/>
+      <x:c r="AW405" s="22"/>
+      <x:c r="AX405" s="22"/>
+      <x:c r="AY405" s="22"/>
+    </x:row>
+    <x:row r="406">
+      <x:c r="AN406" s="23"/>
+      <x:c r="AO406" s="22"/>
+      <x:c r="AP406" s="22"/>
+      <x:c r="AQ406" s="24"/>
+      <x:c r="AR406" s="24"/>
+      <x:c r="AS406" s="22"/>
+      <x:c r="AT406" s="25"/>
+      <x:c r="AU406" s="25"/>
+      <x:c r="AV406" s="22"/>
+      <x:c r="AW406" s="22"/>
+      <x:c r="AX406" s="22"/>
+      <x:c r="AY406" s="22"/>
+    </x:row>
+    <x:row r="407">
+      <x:c r="AN407" s="23"/>
+      <x:c r="AO407" s="22"/>
+      <x:c r="AP407" s="22"/>
+      <x:c r="AQ407" s="24"/>
+      <x:c r="AR407" s="24"/>
+      <x:c r="AS407" s="22"/>
+      <x:c r="AT407" s="25"/>
+      <x:c r="AU407" s="25"/>
+      <x:c r="AV407" s="22"/>
+      <x:c r="AW407" s="22"/>
+      <x:c r="AX407" s="22"/>
+      <x:c r="AY407" s="22"/>
+    </x:row>
+    <x:row r="408">
+      <x:c r="AN408" s="23"/>
+      <x:c r="AO408" s="22"/>
+      <x:c r="AP408" s="22"/>
+      <x:c r="AQ408" s="24"/>
+      <x:c r="AR408" s="24"/>
+      <x:c r="AS408" s="22"/>
+      <x:c r="AT408" s="25"/>
+      <x:c r="AU408" s="25"/>
+      <x:c r="AV408" s="22"/>
+      <x:c r="AW408" s="22"/>
+      <x:c r="AX408" s="22"/>
+      <x:c r="AY408" s="22"/>
+    </x:row>
+    <x:row r="409">
+      <x:c r="AN409" s="23"/>
+      <x:c r="AO409" s="22"/>
+      <x:c r="AP409" s="22"/>
+      <x:c r="AQ409" s="24"/>
+      <x:c r="AR409" s="24"/>
+      <x:c r="AS409" s="22"/>
+      <x:c r="AT409" s="25"/>
+      <x:c r="AU409" s="25"/>
+      <x:c r="AV409" s="22"/>
+      <x:c r="AW409" s="22"/>
+      <x:c r="AX409" s="22"/>
+      <x:c r="AY409" s="22"/>
+    </x:row>
+    <x:row r="410">
+      <x:c r="AN410" s="23"/>
+      <x:c r="AO410" s="22"/>
+      <x:c r="AP410" s="22"/>
+      <x:c r="AQ410" s="24"/>
+      <x:c r="AR410" s="24"/>
+      <x:c r="AS410" s="22"/>
+      <x:c r="AT410" s="25"/>
+      <x:c r="AU410" s="25"/>
+      <x:c r="AV410" s="22"/>
+      <x:c r="AW410" s="22"/>
+      <x:c r="AX410" s="22"/>
+      <x:c r="AY410" s="22"/>
+    </x:row>
+    <x:row r="411">
+      <x:c r="AN411" s="23"/>
+      <x:c r="AO411" s="22"/>
+      <x:c r="AP411" s="22"/>
+      <x:c r="AQ411" s="24"/>
+      <x:c r="AR411" s="24"/>
+      <x:c r="AS411" s="22"/>
+      <x:c r="AT411" s="25"/>
+      <x:c r="AU411" s="25"/>
+      <x:c r="AV411" s="22"/>
+      <x:c r="AW411" s="22"/>
+      <x:c r="AX411" s="22"/>
+      <x:c r="AY411" s="22"/>
+    </x:row>
+    <x:row r="412">
+      <x:c r="AN412" s="23"/>
+      <x:c r="AO412" s="22"/>
+      <x:c r="AP412" s="22"/>
+      <x:c r="AQ412" s="24"/>
+      <x:c r="AR412" s="24"/>
+      <x:c r="AS412" s="22"/>
+      <x:c r="AT412" s="25"/>
+      <x:c r="AU412" s="25"/>
+      <x:c r="AV412" s="22"/>
+      <x:c r="AW412" s="22"/>
+      <x:c r="AX412" s="22"/>
+      <x:c r="AY412" s="22"/>
+    </x:row>
+    <x:row r="413">
+      <x:c r="AN413" s="23"/>
+      <x:c r="AO413" s="22"/>
+      <x:c r="AP413" s="22"/>
+      <x:c r="AQ413" s="24"/>
+      <x:c r="AR413" s="24"/>
+      <x:c r="AS413" s="22"/>
+      <x:c r="AT413" s="25"/>
+      <x:c r="AU413" s="25"/>
+      <x:c r="AV413" s="22"/>
+      <x:c r="AW413" s="22"/>
+      <x:c r="AX413" s="22"/>
+      <x:c r="AY413" s="22"/>
+    </x:row>
+    <x:row r="414">
+      <x:c r="AN414" s="23"/>
+      <x:c r="AO414" s="22"/>
+      <x:c r="AP414" s="22"/>
+      <x:c r="AQ414" s="24"/>
+      <x:c r="AR414" s="24"/>
+      <x:c r="AS414" s="22"/>
+      <x:c r="AT414" s="25"/>
+      <x:c r="AU414" s="25"/>
+      <x:c r="AV414" s="22"/>
+      <x:c r="AW414" s="22"/>
+      <x:c r="AX414" s="22"/>
+      <x:c r="AY414" s="22"/>
+    </x:row>
+    <x:row r="415">
+      <x:c r="AN415" s="23"/>
+      <x:c r="AO415" s="22"/>
+      <x:c r="AP415" s="22"/>
+      <x:c r="AQ415" s="24"/>
+      <x:c r="AR415" s="24"/>
+      <x:c r="AS415" s="22"/>
+      <x:c r="AT415" s="25"/>
+      <x:c r="AU415" s="25"/>
+      <x:c r="AV415" s="22"/>
+      <x:c r="AW415" s="22"/>
+      <x:c r="AX415" s="22"/>
+      <x:c r="AY415" s="22"/>
+    </x:row>
+    <x:row r="416">
+      <x:c r="AN416" s="23"/>
+      <x:c r="AO416" s="22"/>
+      <x:c r="AP416" s="22"/>
+      <x:c r="AQ416" s="24"/>
+      <x:c r="AR416" s="24"/>
+      <x:c r="AS416" s="22"/>
+      <x:c r="AT416" s="25"/>
+      <x:c r="AU416" s="25"/>
+      <x:c r="AV416" s="22"/>
+      <x:c r="AW416" s="22"/>
+      <x:c r="AX416" s="22"/>
+      <x:c r="AY416" s="22"/>
+    </x:row>
+    <x:row r="417">
+      <x:c r="AN417" s="23"/>
+      <x:c r="AO417" s="22"/>
+      <x:c r="AP417" s="22"/>
+      <x:c r="AQ417" s="24"/>
+      <x:c r="AR417" s="24"/>
+      <x:c r="AS417" s="22"/>
+      <x:c r="AT417" s="25"/>
+      <x:c r="AU417" s="25"/>
+      <x:c r="AV417" s="22"/>
+      <x:c r="AW417" s="22"/>
+      <x:c r="AX417" s="22"/>
+      <x:c r="AY417" s="22"/>
+    </x:row>
+    <x:row r="418">
+      <x:c r="AN418" s="23"/>
+      <x:c r="AO418" s="22"/>
+      <x:c r="AP418" s="22"/>
+      <x:c r="AQ418" s="24"/>
+      <x:c r="AR418" s="24"/>
+      <x:c r="AS418" s="22"/>
+      <x:c r="AT418" s="25"/>
+      <x:c r="AU418" s="25"/>
+      <x:c r="AV418" s="22"/>
+      <x:c r="AW418" s="22"/>
+      <x:c r="AX418" s="22"/>
+      <x:c r="AY418" s="22"/>
+    </x:row>
+    <x:row r="419">
+      <x:c r="AN419" s="23"/>
+      <x:c r="AO419" s="22"/>
+      <x:c r="AP419" s="22"/>
+      <x:c r="AQ419" s="24"/>
+      <x:c r="AR419" s="24"/>
+      <x:c r="AS419" s="22"/>
+      <x:c r="AT419" s="25"/>
+      <x:c r="AU419" s="25"/>
+      <x:c r="AV419" s="22"/>
+      <x:c r="AW419" s="22"/>
+      <x:c r="AX419" s="22"/>
+      <x:c r="AY419" s="22"/>
+    </x:row>
+    <x:row r="420">
+      <x:c r="AN420" s="23"/>
+      <x:c r="AO420" s="22"/>
+      <x:c r="AP420" s="22"/>
+      <x:c r="AQ420" s="24"/>
+      <x:c r="AR420" s="24"/>
+      <x:c r="AS420" s="22"/>
+      <x:c r="AT420" s="25"/>
+      <x:c r="AU420" s="25"/>
+      <x:c r="AV420" s="22"/>
+      <x:c r="AW420" s="22"/>
+      <x:c r="AX420" s="22"/>
+      <x:c r="AY420" s="22"/>
+    </x:row>
+    <x:row r="421">
+      <x:c r="AN421" s="23"/>
+      <x:c r="AO421" s="22"/>
+      <x:c r="AP421" s="22"/>
+      <x:c r="AQ421" s="24"/>
+      <x:c r="AR421" s="24"/>
+      <x:c r="AS421" s="22"/>
+      <x:c r="AT421" s="25"/>
+      <x:c r="AU421" s="25"/>
+      <x:c r="AV421" s="22"/>
+      <x:c r="AW421" s="22"/>
+      <x:c r="AX421" s="22"/>
+      <x:c r="AY421" s="22"/>
+    </x:row>
+    <x:row r="422">
+      <x:c r="AN422" s="23"/>
+      <x:c r="AO422" s="22"/>
+      <x:c r="AP422" s="22"/>
+      <x:c r="AQ422" s="24"/>
+      <x:c r="AR422" s="24"/>
+      <x:c r="AS422" s="22"/>
+      <x:c r="AT422" s="25"/>
+      <x:c r="AU422" s="25"/>
+      <x:c r="AV422" s="22"/>
+      <x:c r="AW422" s="22"/>
+      <x:c r="AX422" s="22"/>
+      <x:c r="AY422" s="22"/>
+    </x:row>
+    <x:row r="423">
+      <x:c r="AN423" s="23"/>
+      <x:c r="AO423" s="22"/>
+      <x:c r="AP423" s="22"/>
+      <x:c r="AQ423" s="24"/>
+      <x:c r="AR423" s="24"/>
+      <x:c r="AS423" s="22"/>
+      <x:c r="AT423" s="25"/>
+      <x:c r="AU423" s="25"/>
+      <x:c r="AV423" s="22"/>
+      <x:c r="AW423" s="22"/>
+      <x:c r="AX423" s="22"/>
+      <x:c r="AY423" s="22"/>
+    </x:row>
+    <x:row r="424">
+      <x:c r="AN424" s="23"/>
+      <x:c r="AO424" s="22"/>
+      <x:c r="AP424" s="22"/>
+      <x:c r="AQ424" s="24"/>
+      <x:c r="AR424" s="24"/>
+      <x:c r="AS424" s="22"/>
+      <x:c r="AT424" s="25"/>
+      <x:c r="AU424" s="25"/>
+      <x:c r="AV424" s="22"/>
+      <x:c r="AW424" s="22"/>
+      <x:c r="AX424" s="22"/>
+      <x:c r="AY424" s="22"/>
+    </x:row>
+    <x:row r="425">
+      <x:c r="AN425" s="23"/>
+      <x:c r="AO425" s="22"/>
+      <x:c r="AP425" s="22"/>
+      <x:c r="AQ425" s="24"/>
+      <x:c r="AR425" s="24"/>
+      <x:c r="AS425" s="22"/>
+      <x:c r="AT425" s="25"/>
+      <x:c r="AU425" s="25"/>
+      <x:c r="AV425" s="22"/>
+      <x:c r="AW425" s="22"/>
+      <x:c r="AX425" s="22"/>
+      <x:c r="AY425" s="22"/>
+    </x:row>
+    <x:row r="426">
+      <x:c r="AN426" s="23"/>
+      <x:c r="AO426" s="22"/>
+      <x:c r="AP426" s="22"/>
+      <x:c r="AQ426" s="24"/>
+      <x:c r="AR426" s="24"/>
+      <x:c r="AS426" s="22"/>
+      <x:c r="AT426" s="25"/>
+      <x:c r="AU426" s="25"/>
+      <x:c r="AV426" s="22"/>
+      <x:c r="AW426" s="22"/>
+      <x:c r="AX426" s="22"/>
+      <x:c r="AY426" s="22"/>
+    </x:row>
+    <x:row r="427">
+      <x:c r="AN427" s="23"/>
+      <x:c r="AO427" s="22"/>
+      <x:c r="AP427" s="22"/>
+      <x:c r="AQ427" s="24"/>
+      <x:c r="AR427" s="24"/>
+      <x:c r="AS427" s="22"/>
+      <x:c r="AT427" s="25"/>
+      <x:c r="AU427" s="25"/>
+      <x:c r="AV427" s="22"/>
+      <x:c r="AW427" s="22"/>
+      <x:c r="AX427" s="22"/>
+      <x:c r="AY427" s="22"/>
+    </x:row>
+    <x:row r="428">
+      <x:c r="AN428" s="23"/>
+      <x:c r="AO428" s="22"/>
+      <x:c r="AP428" s="22"/>
+      <x:c r="AQ428" s="24"/>
+      <x:c r="AR428" s="24"/>
+      <x:c r="AS428" s="22"/>
+      <x:c r="AT428" s="25"/>
+      <x:c r="AU428" s="25"/>
+      <x:c r="AV428" s="22"/>
+      <x:c r="AW428" s="22"/>
+      <x:c r="AX428" s="22"/>
+      <x:c r="AY428" s="22"/>
+    </x:row>
+    <x:row r="429">
+      <x:c r="AN429" s="23"/>
+      <x:c r="AO429" s="22"/>
+      <x:c r="AP429" s="22"/>
+      <x:c r="AQ429" s="24"/>
+      <x:c r="AR429" s="24"/>
+      <x:c r="AS429" s="22"/>
+      <x:c r="AT429" s="25"/>
+      <x:c r="AU429" s="25"/>
+      <x:c r="AV429" s="22"/>
+      <x:c r="AW429" s="22"/>
+      <x:c r="AX429" s="22"/>
+      <x:c r="AY429" s="22"/>
+    </x:row>
+    <x:row r="430">
+      <x:c r="AN430" s="23"/>
+      <x:c r="AO430" s="22"/>
+      <x:c r="AP430" s="22"/>
+      <x:c r="AQ430" s="24"/>
+      <x:c r="AR430" s="24"/>
+      <x:c r="AS430" s="22"/>
+      <x:c r="AT430" s="25"/>
+      <x:c r="AU430" s="25"/>
+      <x:c r="AV430" s="22"/>
+      <x:c r="AW430" s="22"/>
+      <x:c r="AX430" s="22"/>
+      <x:c r="AY430" s="22"/>
+    </x:row>
+    <x:row r="431">
+      <x:c r="AN431" s="23"/>
+      <x:c r="AO431" s="22"/>
+      <x:c r="AP431" s="22"/>
+      <x:c r="AQ431" s="24"/>
+      <x:c r="AR431" s="24"/>
+      <x:c r="AS431" s="22"/>
+      <x:c r="AT431" s="25"/>
+      <x:c r="AU431" s="25"/>
+      <x:c r="AV431" s="22"/>
+      <x:c r="AW431" s="22"/>
+      <x:c r="AX431" s="22"/>
+      <x:c r="AY431" s="22"/>
+    </x:row>
+    <x:row r="432">
+      <x:c r="AN432" s="23"/>
+      <x:c r="AO432" s="22"/>
+      <x:c r="AP432" s="22"/>
+      <x:c r="AQ432" s="24"/>
+      <x:c r="AR432" s="24"/>
+      <x:c r="AS432" s="22"/>
+      <x:c r="AT432" s="25"/>
+      <x:c r="AU432" s="25"/>
+      <x:c r="AV432" s="22"/>
+      <x:c r="AW432" s="22"/>
+      <x:c r="AX432" s="22"/>
+      <x:c r="AY432" s="22"/>
+    </x:row>
+    <x:row r="433">
+      <x:c r="AN433" s="23"/>
+      <x:c r="AO433" s="22"/>
+      <x:c r="AP433" s="22"/>
+      <x:c r="AQ433" s="24"/>
+      <x:c r="AR433" s="24"/>
+      <x:c r="AS433" s="22"/>
+      <x:c r="AT433" s="25"/>
+      <x:c r="AU433" s="25"/>
+      <x:c r="AV433" s="22"/>
+      <x:c r="AW433" s="22"/>
+      <x:c r="AX433" s="22"/>
+      <x:c r="AY433" s="22"/>
+    </x:row>
+    <x:row r="434">
+      <x:c r="AN434" s="23"/>
+      <x:c r="AO434" s="22"/>
+      <x:c r="AP434" s="22"/>
+      <x:c r="AQ434" s="24"/>
+      <x:c r="AR434" s="24"/>
+      <x:c r="AS434" s="22"/>
+      <x:c r="AT434" s="25"/>
+      <x:c r="AU434" s="25"/>
+      <x:c r="AV434" s="22"/>
+      <x:c r="AW434" s="22"/>
+      <x:c r="AX434" s="22"/>
+      <x:c r="AY434" s="22"/>
+    </x:row>
+    <x:row r="435">
+      <x:c r="AN435" s="23"/>
+      <x:c r="AO435" s="22"/>
+      <x:c r="AP435" s="22"/>
+      <x:c r="AQ435" s="24"/>
+      <x:c r="AR435" s="24"/>
+      <x:c r="AS435" s="22"/>
+      <x:c r="AT435" s="25"/>
+      <x:c r="AU435" s="25"/>
+      <x:c r="AV435" s="22"/>
+      <x:c r="AW435" s="22"/>
+      <x:c r="AX435" s="22"/>
+      <x:c r="AY435" s="22"/>
+    </x:row>
+    <x:row r="436">
+      <x:c r="AN436" s="23"/>
+      <x:c r="AO436" s="22"/>
+      <x:c r="AP436" s="22"/>
+      <x:c r="AQ436" s="24"/>
+      <x:c r="AR436" s="24"/>
+      <x:c r="AS436" s="22"/>
+      <x:c r="AT436" s="25"/>
+      <x:c r="AU436" s="25"/>
+      <x:c r="AV436" s="22"/>
+      <x:c r="AW436" s="22"/>
+      <x:c r="AX436" s="22"/>
+      <x:c r="AY436" s="22"/>
+    </x:row>
+    <x:row r="437">
+      <x:c r="AN437" s="23"/>
+      <x:c r="AO437" s="22"/>
+      <x:c r="AP437" s="22"/>
+      <x:c r="AQ437" s="24"/>
+      <x:c r="AR437" s="24"/>
+      <x:c r="AS437" s="22"/>
+      <x:c r="AT437" s="25"/>
+      <x:c r="AU437" s="25"/>
+      <x:c r="AV437" s="22"/>
+      <x:c r="AW437" s="22"/>
+      <x:c r="AX437" s="22"/>
+      <x:c r="AY437" s="22"/>
+    </x:row>
+    <x:row r="438">
+      <x:c r="AN438" s="23"/>
+      <x:c r="AO438" s="22"/>
+      <x:c r="AP438" s="22"/>
+      <x:c r="AQ438" s="24"/>
+      <x:c r="AR438" s="24"/>
+      <x:c r="AS438" s="22"/>
+      <x:c r="AT438" s="25"/>
+      <x:c r="AU438" s="25"/>
+      <x:c r="AV438" s="22"/>
+      <x:c r="AW438" s="22"/>
+      <x:c r="AX438" s="22"/>
+      <x:c r="AY438" s="22"/>
+    </x:row>
+    <x:row r="439">
+      <x:c r="AN439" s="23"/>
+      <x:c r="AO439" s="22"/>
+      <x:c r="AP439" s="22"/>
+      <x:c r="AQ439" s="24"/>
+      <x:c r="AR439" s="24"/>
+      <x:c r="AS439" s="22"/>
+      <x:c r="AT439" s="25"/>
+      <x:c r="AU439" s="25"/>
+      <x:c r="AV439" s="22"/>
+      <x:c r="AW439" s="22"/>
+      <x:c r="AX439" s="22"/>
+      <x:c r="AY439" s="22"/>
+    </x:row>
+    <x:row r="440">
+      <x:c r="AN440" s="23"/>
+      <x:c r="AO440" s="22"/>
+      <x:c r="AP440" s="22"/>
+      <x:c r="AQ440" s="24"/>
+      <x:c r="AR440" s="24"/>
+      <x:c r="AS440" s="22"/>
+      <x:c r="AT440" s="25"/>
+      <x:c r="AU440" s="25"/>
+      <x:c r="AV440" s="22"/>
+      <x:c r="AW440" s="22"/>
+      <x:c r="AX440" s="22"/>
+      <x:c r="AY440" s="22"/>
+    </x:row>
+    <x:row r="441">
+      <x:c r="AN441" s="23"/>
+      <x:c r="AO441" s="22"/>
+      <x:c r="AP441" s="22"/>
+      <x:c r="AQ441" s="24"/>
+      <x:c r="AR441" s="24"/>
+      <x:c r="AS441" s="22"/>
+      <x:c r="AT441" s="25"/>
+      <x:c r="AU441" s="25"/>
+      <x:c r="AV441" s="22"/>
+      <x:c r="AW441" s="22"/>
+      <x:c r="AX441" s="22"/>
+      <x:c r="AY441" s="22"/>
+    </x:row>
+    <x:row r="442">
+      <x:c r="AN442" s="23"/>
+      <x:c r="AO442" s="22"/>
+      <x:c r="AP442" s="22"/>
+      <x:c r="AQ442" s="24"/>
+      <x:c r="AR442" s="24"/>
+      <x:c r="AS442" s="22"/>
+      <x:c r="AT442" s="25"/>
+      <x:c r="AU442" s="25"/>
+      <x:c r="AV442" s="22"/>
+      <x:c r="AW442" s="22"/>
+      <x:c r="AX442" s="22"/>
+      <x:c r="AY442" s="22"/>
+    </x:row>
+    <x:row r="443">
+      <x:c r="AN443" s="23"/>
+      <x:c r="AO443" s="22"/>
+      <x:c r="AP443" s="22"/>
+      <x:c r="AQ443" s="24"/>
+      <x:c r="AR443" s="24"/>
+      <x:c r="AS443" s="22"/>
+      <x:c r="AT443" s="25"/>
+      <x:c r="AU443" s="25"/>
+      <x:c r="AV443" s="22"/>
+      <x:c r="AW443" s="22"/>
+      <x:c r="AX443" s="22"/>
+      <x:c r="AY443" s="22"/>
+    </x:row>
+    <x:row r="444">
+      <x:c r="AN444" s="23"/>
+      <x:c r="AO444" s="22"/>
+      <x:c r="AP444" s="22"/>
+      <x:c r="AQ444" s="24"/>
+      <x:c r="AR444" s="24"/>
+      <x:c r="AS444" s="22"/>
+      <x:c r="AT444" s="25"/>
+      <x:c r="AU444" s="25"/>
+      <x:c r="AV444" s="22"/>
+      <x:c r="AW444" s="22"/>
+      <x:c r="AX444" s="22"/>
+      <x:c r="AY444" s="22"/>
+    </x:row>
+    <x:row r="445">
+      <x:c r="AN445" s="23"/>
+      <x:c r="AO445" s="22"/>
+      <x:c r="AP445" s="22"/>
+      <x:c r="AQ445" s="24"/>
+      <x:c r="AR445" s="24"/>
+      <x:c r="AS445" s="22"/>
+      <x:c r="AT445" s="25"/>
+      <x:c r="AU445" s="25"/>
+      <x:c r="AV445" s="22"/>
+      <x:c r="AW445" s="22"/>
+      <x:c r="AX445" s="22"/>
+      <x:c r="AY445" s="22"/>
+    </x:row>
+    <x:row r="446">
+      <x:c r="AN446" s="23"/>
+      <x:c r="AO446" s="22"/>
+      <x:c r="AP446" s="22"/>
+      <x:c r="AQ446" s="24"/>
+      <x:c r="AR446" s="24"/>
+      <x:c r="AS446" s="22"/>
+      <x:c r="AT446" s="25"/>
+      <x:c r="AU446" s="25"/>
+      <x:c r="AV446" s="22"/>
+      <x:c r="AW446" s="22"/>
+      <x:c r="AX446" s="22"/>
+      <x:c r="AY446" s="22"/>
+    </x:row>
+    <x:row r="447">
+      <x:c r="AN447" s="23"/>
+      <x:c r="AO447" s="22"/>
+      <x:c r="AP447" s="22"/>
+      <x:c r="AQ447" s="24"/>
+      <x:c r="AR447" s="24"/>
+      <x:c r="AS447" s="22"/>
+      <x:c r="AT447" s="25"/>
+      <x:c r="AU447" s="25"/>
+      <x:c r="AV447" s="22"/>
+      <x:c r="AW447" s="22"/>
+      <x:c r="AX447" s="22"/>
+      <x:c r="AY447" s="22"/>
+    </x:row>
+    <x:row r="448">
+      <x:c r="AN448" s="23"/>
+      <x:c r="AO448" s="22"/>
+      <x:c r="AP448" s="22"/>
+      <x:c r="AQ448" s="24"/>
+      <x:c r="AR448" s="24"/>
+      <x:c r="AS448" s="22"/>
+      <x:c r="AT448" s="25"/>
+      <x:c r="AU448" s="25"/>
+      <x:c r="AV448" s="22"/>
+      <x:c r="AW448" s="22"/>
+      <x:c r="AX448" s="22"/>
+      <x:c r="AY448" s="22"/>
+    </x:row>
+    <x:row r="449">
+      <x:c r="AN449" s="23"/>
+      <x:c r="AO449" s="22"/>
+      <x:c r="AP449" s="22"/>
+      <x:c r="AQ449" s="24"/>
+      <x:c r="AR449" s="24"/>
+      <x:c r="AS449" s="22"/>
+      <x:c r="AT449" s="25"/>
+      <x:c r="AU449" s="25"/>
+      <x:c r="AV449" s="22"/>
+      <x:c r="AW449" s="22"/>
+      <x:c r="AX449" s="22"/>
+      <x:c r="AY449" s="22"/>
+    </x:row>
+    <x:row r="450">
+      <x:c r="AN450" s="23"/>
+      <x:c r="AO450" s="22"/>
+      <x:c r="AP450" s="22"/>
+      <x:c r="AQ450" s="24"/>
+      <x:c r="AR450" s="24"/>
+      <x:c r="AS450" s="22"/>
+      <x:c r="AT450" s="25"/>
+      <x:c r="AU450" s="25"/>
+      <x:c r="AV450" s="22"/>
+      <x:c r="AW450" s="22"/>
+      <x:c r="AX450" s="22"/>
+      <x:c r="AY450" s="22"/>
+    </x:row>
+    <x:row r="451">
+      <x:c r="AN451" s="23"/>
+      <x:c r="AO451" s="22"/>
+      <x:c r="AP451" s="22"/>
+      <x:c r="AQ451" s="24"/>
+      <x:c r="AR451" s="24"/>
+      <x:c r="AS451" s="22"/>
+      <x:c r="AT451" s="25"/>
+      <x:c r="AU451" s="25"/>
+      <x:c r="AV451" s="22"/>
+      <x:c r="AW451" s="22"/>
+      <x:c r="AX451" s="22"/>
+      <x:c r="AY451" s="22"/>
+    </x:row>
+    <x:row r="452">
+      <x:c r="AN452" s="23"/>
+      <x:c r="AO452" s="22"/>
+      <x:c r="AP452" s="22"/>
+      <x:c r="AQ452" s="24"/>
+      <x:c r="AR452" s="24"/>
+      <x:c r="AS452" s="22"/>
+      <x:c r="AT452" s="25"/>
+      <x:c r="AU452" s="25"/>
+      <x:c r="AV452" s="22"/>
+      <x:c r="AW452" s="22"/>
+      <x:c r="AX452" s="22"/>
+      <x:c r="AY452" s="22"/>
+    </x:row>
+    <x:row r="453">
+      <x:c r="AN453" s="23"/>
+      <x:c r="AO453" s="22"/>
+      <x:c r="AP453" s="22"/>
+      <x:c r="AQ453" s="24"/>
+      <x:c r="AR453" s="24"/>
+      <x:c r="AS453" s="22"/>
+      <x:c r="AT453" s="25"/>
+      <x:c r="AU453" s="25"/>
+      <x:c r="AV453" s="22"/>
+      <x:c r="AW453" s="22"/>
+      <x:c r="AX453" s="22"/>
+      <x:c r="AY453" s="22"/>
+    </x:row>
+    <x:row r="454">
+      <x:c r="AN454" s="23"/>
+      <x:c r="AO454" s="22"/>
+      <x:c r="AP454" s="22"/>
+      <x:c r="AQ454" s="24"/>
+      <x:c r="AR454" s="24"/>
+      <x:c r="AS454" s="22"/>
+      <x:c r="AT454" s="25"/>
+      <x:c r="AU454" s="25"/>
+      <x:c r="AV454" s="22"/>
+      <x:c r="AW454" s="22"/>
+      <x:c r="AX454" s="22"/>
+      <x:c r="AY454" s="22"/>
+    </x:row>
+    <x:row r="455">
+      <x:c r="AN455" s="23"/>
+      <x:c r="AO455" s="22"/>
+      <x:c r="AP455" s="22"/>
+      <x:c r="AQ455" s="24"/>
+      <x:c r="AR455" s="24"/>
+      <x:c r="AS455" s="22"/>
+      <x:c r="AT455" s="25"/>
+      <x:c r="AU455" s="25"/>
+      <x:c r="AV455" s="22"/>
+      <x:c r="AW455" s="22"/>
+      <x:c r="AX455" s="22"/>
+      <x:c r="AY455" s="22"/>
+    </x:row>
+    <x:row r="456">
+      <x:c r="AN456" s="23"/>
+      <x:c r="AO456" s="22"/>
+      <x:c r="AP456" s="22"/>
+      <x:c r="AQ456" s="24"/>
+      <x:c r="AR456" s="24"/>
+      <x:c r="AS456" s="22"/>
+      <x:c r="AT456" s="25"/>
+      <x:c r="AU456" s="25"/>
+      <x:c r="AV456" s="22"/>
+      <x:c r="AW456" s="22"/>
+      <x:c r="AX456" s="22"/>
+      <x:c r="AY456" s="22"/>
+    </x:row>
+    <x:row r="457">
+      <x:c r="AN457" s="23"/>
+      <x:c r="AO457" s="22"/>
+      <x:c r="AP457" s="22"/>
+      <x:c r="AQ457" s="24"/>
+      <x:c r="AR457" s="24"/>
+      <x:c r="AS457" s="22"/>
+      <x:c r="AT457" s="25"/>
+      <x:c r="AU457" s="25"/>
+      <x:c r="AV457" s="22"/>
+      <x:c r="AW457" s="22"/>
+      <x:c r="AX457" s="22"/>
+      <x:c r="AY457" s="22"/>
+    </x:row>
+    <x:row r="458">
+      <x:c r="AN458" s="23"/>
+      <x:c r="AO458" s="22"/>
+      <x:c r="AP458" s="22"/>
+      <x:c r="AQ458" s="24"/>
+      <x:c r="AR458" s="24"/>
+      <x:c r="AS458" s="22"/>
+      <x:c r="AT458" s="25"/>
+      <x:c r="AU458" s="25"/>
+      <x:c r="AV458" s="22"/>
+      <x:c r="AW458" s="22"/>
+      <x:c r="AX458" s="22"/>
+      <x:c r="AY458" s="22"/>
+    </x:row>
+    <x:row r="459">
+      <x:c r="AN459" s="23"/>
+      <x:c r="AO459" s="22"/>
+      <x:c r="AP459" s="22"/>
+      <x:c r="AQ459" s="24"/>
+      <x:c r="AR459" s="24"/>
+      <x:c r="AS459" s="22"/>
+      <x:c r="AT459" s="25"/>
+      <x:c r="AU459" s="25"/>
+      <x:c r="AV459" s="22"/>
+      <x:c r="AW459" s="22"/>
+      <x:c r="AX459" s="22"/>
+      <x:c r="AY459" s="22"/>
+    </x:row>
+    <x:row r="460">
+      <x:c r="AN460" s="23"/>
+      <x:c r="AO460" s="22"/>
+      <x:c r="AP460" s="22"/>
+      <x:c r="AQ460" s="24"/>
+      <x:c r="AR460" s="24"/>
+      <x:c r="AS460" s="22"/>
+      <x:c r="AT460" s="25"/>
+      <x:c r="AU460" s="25"/>
+      <x:c r="AV460" s="22"/>
+      <x:c r="AW460" s="22"/>
+      <x:c r="AX460" s="22"/>
+      <x:c r="AY460" s="22"/>
+    </x:row>
+    <x:row r="461">
+      <x:c r="AN461" s="23"/>
+      <x:c r="AO461" s="22"/>
+      <x:c r="AP461" s="22"/>
+      <x:c r="AQ461" s="24"/>
+      <x:c r="AR461" s="24"/>
+      <x:c r="AS461" s="22"/>
+      <x:c r="AT461" s="25"/>
+      <x:c r="AU461" s="25"/>
+      <x:c r="AV461" s="22"/>
+      <x:c r="AW461" s="22"/>
+      <x:c r="AX461" s="22"/>
+      <x:c r="AY461" s="22"/>
+    </x:row>
+    <x:row r="462">
+      <x:c r="AN462" s="23"/>
+      <x:c r="AO462" s="22"/>
+      <x:c r="AP462" s="22"/>
+      <x:c r="AQ462" s="24"/>
+      <x:c r="AR462" s="24"/>
+      <x:c r="AS462" s="22"/>
+      <x:c r="AT462" s="25"/>
+      <x:c r="AU462" s="25"/>
+      <x:c r="AV462" s="22"/>
+      <x:c r="AW462" s="22"/>
+      <x:c r="AX462" s="22"/>
+      <x:c r="AY462" s="22"/>
+    </x:row>
+    <x:row r="463">
+      <x:c r="AN463" s="23"/>
+      <x:c r="AO463" s="22"/>
+      <x:c r="AP463" s="22"/>
+      <x:c r="AQ463" s="24"/>
+      <x:c r="AR463" s="24"/>
+      <x:c r="AS463" s="22"/>
+      <x:c r="AT463" s="25"/>
+      <x:c r="AU463" s="25"/>
+      <x:c r="AV463" s="22"/>
+      <x:c r="AW463" s="22"/>
+      <x:c r="AX463" s="22"/>
+      <x:c r="AY463" s="22"/>
+    </x:row>
+    <x:row r="464">
+      <x:c r="AN464" s="23"/>
+      <x:c r="AO464" s="22"/>
+      <x:c r="AP464" s="22"/>
+      <x:c r="AQ464" s="24"/>
+      <x:c r="AR464" s="24"/>
+      <x:c r="AS464" s="22"/>
+      <x:c r="AT464" s="25"/>
+      <x:c r="AU464" s="25"/>
+      <x:c r="AV464" s="22"/>
+      <x:c r="AW464" s="22"/>
+      <x:c r="AX464" s="22"/>
+      <x:c r="AY464" s="22"/>
+    </x:row>
+    <x:row r="465">
+      <x:c r="AN465" s="23"/>
+      <x:c r="AO465" s="22"/>
+      <x:c r="AP465" s="22"/>
+      <x:c r="AQ465" s="24"/>
+      <x:c r="AR465" s="24"/>
+      <x:c r="AS465" s="22"/>
+      <x:c r="AT465" s="25"/>
+      <x:c r="AU465" s="25"/>
+      <x:c r="AV465" s="22"/>
+      <x:c r="AW465" s="22"/>
+      <x:c r="AX465" s="22"/>
+      <x:c r="AY465" s="22"/>
+    </x:row>
+    <x:row r="466">
+      <x:c r="AN466" s="23"/>
+      <x:c r="AO466" s="22"/>
+      <x:c r="AP466" s="22"/>
+      <x:c r="AQ466" s="24"/>
+      <x:c r="AR466" s="24"/>
+      <x:c r="AS466" s="22"/>
+      <x:c r="AT466" s="25"/>
+      <x:c r="AU466" s="25"/>
+      <x:c r="AV466" s="22"/>
+      <x:c r="AW466" s="22"/>
+      <x:c r="AX466" s="22"/>
+      <x:c r="AY466" s="22"/>
+    </x:row>
+    <x:row r="467">
+      <x:c r="AN467" s="23"/>
+      <x:c r="AO467" s="22"/>
+      <x:c r="AP467" s="22"/>
+      <x:c r="AQ467" s="24"/>
+      <x:c r="AR467" s="24"/>
+      <x:c r="AS467" s="22"/>
+      <x:c r="AT467" s="25"/>
+      <x:c r="AU467" s="25"/>
+      <x:c r="AV467" s="22"/>
+      <x:c r="AW467" s="22"/>
+      <x:c r="AX467" s="22"/>
+      <x:c r="AY467" s="22"/>
+    </x:row>
+    <x:row r="468">
+      <x:c r="AN468" s="23"/>
+      <x:c r="AO468" s="22"/>
+      <x:c r="AP468" s="22"/>
+      <x:c r="AQ468" s="24"/>
+      <x:c r="AR468" s="24"/>
+      <x:c r="AS468" s="22"/>
+      <x:c r="AT468" s="25"/>
+      <x:c r="AU468" s="25"/>
+      <x:c r="AV468" s="22"/>
+      <x:c r="AW468" s="22"/>
+      <x:c r="AX468" s="22"/>
+      <x:c r="AY468" s="22"/>
+    </x:row>
+    <x:row r="469">
+      <x:c r="AN469" s="23"/>
+      <x:c r="AO469" s="22"/>
+      <x:c r="AP469" s="22"/>
+      <x:c r="AQ469" s="24"/>
+      <x:c r="AR469" s="24"/>
+      <x:c r="AS469" s="22"/>
+      <x:c r="AT469" s="25"/>
+      <x:c r="AU469" s="25"/>
+      <x:c r="AV469" s="22"/>
+      <x:c r="AW469" s="22"/>
+      <x:c r="AX469" s="22"/>
+      <x:c r="AY469" s="22"/>
+    </x:row>
+    <x:row r="470">
+      <x:c r="AN470" s="23"/>
+      <x:c r="AO470" s="22"/>
+      <x:c r="AP470" s="22"/>
+      <x:c r="AQ470" s="24"/>
+      <x:c r="AR470" s="24"/>
+      <x:c r="AS470" s="22"/>
+      <x:c r="AT470" s="25"/>
+      <x:c r="AU470" s="25"/>
+      <x:c r="AV470" s="22"/>
+      <x:c r="AW470" s="22"/>
+      <x:c r="AX470" s="22"/>
+      <x:c r="AY470" s="22"/>
+    </x:row>
+    <x:row r="471">
+      <x:c r="AN471" s="23"/>
+      <x:c r="AO471" s="22"/>
+      <x:c r="AP471" s="22"/>
+      <x:c r="AQ471" s="24"/>
+      <x:c r="AR471" s="24"/>
+      <x:c r="AS471" s="22"/>
+      <x:c r="AT471" s="25"/>
+      <x:c r="AU471" s="25"/>
+      <x:c r="AV471" s="22"/>
+      <x:c r="AW471" s="22"/>
+      <x:c r="AX471" s="22"/>
+      <x:c r="AY471" s="22"/>
+    </x:row>
+    <x:row r="472">
+      <x:c r="AN472" s="23"/>
+      <x:c r="AO472" s="22"/>
+      <x:c r="AP472" s="22"/>
+      <x:c r="AQ472" s="24"/>
+      <x:c r="AR472" s="24"/>
+      <x:c r="AS472" s="22"/>
+      <x:c r="AT472" s="25"/>
+      <x:c r="AU472" s="25"/>
+      <x:c r="AV472" s="22"/>
+      <x:c r="AW472" s="22"/>
+      <x:c r="AX472" s="22"/>
+      <x:c r="AY472" s="22"/>
+    </x:row>
+    <x:row r="473">
+      <x:c r="AN473" s="23"/>
+      <x:c r="AO473" s="22"/>
+      <x:c r="AP473" s="22"/>
+      <x:c r="AQ473" s="24"/>
+      <x:c r="AR473" s="24"/>
+      <x:c r="AS473" s="22"/>
+      <x:c r="AT473" s="25"/>
+      <x:c r="AU473" s="25"/>
+      <x:c r="AV473" s="22"/>
+      <x:c r="AW473" s="22"/>
+      <x:c r="AX473" s="22"/>
+      <x:c r="AY473" s="22"/>
+    </x:row>
+    <x:row r="474">
+      <x:c r="AN474" s="23"/>
+      <x:c r="AO474" s="22"/>
+      <x:c r="AP474" s="22"/>
+      <x:c r="AQ474" s="24"/>
+      <x:c r="AR474" s="24"/>
+      <x:c r="AS474" s="22"/>
+      <x:c r="AT474" s="25"/>
+      <x:c r="AU474" s="25"/>
+      <x:c r="AV474" s="22"/>
+      <x:c r="AW474" s="22"/>
+      <x:c r="AX474" s="22"/>
+      <x:c r="AY474" s="22"/>
+    </x:row>
+    <x:row r="475">
+      <x:c r="AN475" s="23"/>
+      <x:c r="AO475" s="22"/>
+      <x:c r="AP475" s="22"/>
+      <x:c r="AQ475" s="24"/>
+      <x:c r="AR475" s="24"/>
+      <x:c r="AS475" s="22"/>
+      <x:c r="AT475" s="25"/>
+      <x:c r="AU475" s="25"/>
+      <x:c r="AV475" s="22"/>
+      <x:c r="AW475" s="22"/>
+      <x:c r="AX475" s="22"/>
+      <x:c r="AY475" s="22"/>
+    </x:row>
+    <x:row r="476">
+      <x:c r="AN476" s="23"/>
+      <x:c r="AO476" s="22"/>
+      <x:c r="AP476" s="22"/>
+      <x:c r="AQ476" s="24"/>
+      <x:c r="AR476" s="24"/>
+      <x:c r="AS476" s="22"/>
+      <x:c r="AT476" s="25"/>
+      <x:c r="AU476" s="25"/>
+      <x:c r="AV476" s="22"/>
+      <x:c r="AW476" s="22"/>
+      <x:c r="AX476" s="22"/>
+      <x:c r="AY476" s="22"/>
+    </x:row>
+    <x:row r="477">
+      <x:c r="AN477" s="23"/>
+      <x:c r="AO477" s="22"/>
+      <x:c r="AP477" s="22"/>
+      <x:c r="AQ477" s="24"/>
+      <x:c r="AR477" s="24"/>
+      <x:c r="AS477" s="22"/>
+      <x:c r="AT477" s="25"/>
+      <x:c r="AU477" s="25"/>
+      <x:c r="AV477" s="22"/>
+      <x:c r="AW477" s="22"/>
+      <x:c r="AX477" s="22"/>
+      <x:c r="AY477" s="22"/>
+    </x:row>
+    <x:row r="478">
+      <x:c r="AN478" s="23"/>
+      <x:c r="AO478" s="22"/>
+      <x:c r="AP478" s="22"/>
+      <x:c r="AQ478" s="24"/>
+      <x:c r="AR478" s="24"/>
+      <x:c r="AS478" s="22"/>
+      <x:c r="AT478" s="25"/>
+      <x:c r="AU478" s="25"/>
+      <x:c r="AV478" s="22"/>
+      <x:c r="AW478" s="22"/>
+      <x:c r="AX478" s="22"/>
+      <x:c r="AY478" s="22"/>
+    </x:row>
+    <x:row r="479">
+      <x:c r="AN479" s="23"/>
+      <x:c r="AO479" s="22"/>
+      <x:c r="AP479" s="22"/>
+      <x:c r="AQ479" s="24"/>
+      <x:c r="AR479" s="24"/>
+      <x:c r="AS479" s="22"/>
+      <x:c r="AT479" s="25"/>
+      <x:c r="AU479" s="25"/>
+      <x:c r="AV479" s="22"/>
+      <x:c r="AW479" s="22"/>
+      <x:c r="AX479" s="22"/>
+      <x:c r="AY479" s="22"/>
+    </x:row>
+    <x:row r="480">
+      <x:c r="AN480" s="23"/>
+      <x:c r="AO480" s="22"/>
+      <x:c r="AP480" s="22"/>
+      <x:c r="AQ480" s="24"/>
+      <x:c r="AR480" s="24"/>
+      <x:c r="AS480" s="22"/>
+      <x:c r="AT480" s="25"/>
+      <x:c r="AU480" s="25"/>
+      <x:c r="AV480" s="22"/>
+      <x:c r="AW480" s="22"/>
+      <x:c r="AX480" s="22"/>
+      <x:c r="AY480" s="22"/>
+    </x:row>
+    <x:row r="481">
+      <x:c r="AN481" s="23"/>
+      <x:c r="AO481" s="22"/>
+      <x:c r="AP481" s="22"/>
+      <x:c r="AQ481" s="24"/>
+      <x:c r="AR481" s="24"/>
+      <x:c r="AS481" s="22"/>
+      <x:c r="AT481" s="25"/>
+      <x:c r="AU481" s="25"/>
+      <x:c r="AV481" s="22"/>
+      <x:c r="AW481" s="22"/>
+      <x:c r="AX481" s="22"/>
+      <x:c r="AY481" s="22"/>
+    </x:row>
+    <x:row r="482">
+      <x:c r="AN482" s="23"/>
+      <x:c r="AO482" s="22"/>
+      <x:c r="AP482" s="22"/>
+      <x:c r="AQ482" s="24"/>
+      <x:c r="AR482" s="24"/>
+      <x:c r="AS482" s="22"/>
+      <x:c r="AT482" s="25"/>
+      <x:c r="AU482" s="25"/>
+      <x:c r="AV482" s="22"/>
+      <x:c r="AW482" s="22"/>
+      <x:c r="AX482" s="22"/>
+      <x:c r="AY482" s="22"/>
+    </x:row>
+    <x:row r="483">
+      <x:c r="AN483" s="23"/>
+      <x:c r="AO483" s="22"/>
+      <x:c r="AP483" s="22"/>
+      <x:c r="AQ483" s="24"/>
+      <x:c r="AR483" s="24"/>
+      <x:c r="AS483" s="22"/>
+      <x:c r="AT483" s="25"/>
+      <x:c r="AU483" s="25"/>
+      <x:c r="AV483" s="22"/>
+      <x:c r="AW483" s="22"/>
+      <x:c r="AX483" s="22"/>
+      <x:c r="AY483" s="22"/>
+    </x:row>
+    <x:row r="484">
+      <x:c r="AN484" s="23"/>
+      <x:c r="AO484" s="22"/>
+      <x:c r="AP484" s="22"/>
+      <x:c r="AQ484" s="24"/>
+      <x:c r="AR484" s="24"/>
+      <x:c r="AS484" s="22"/>
+      <x:c r="AT484" s="25"/>
+      <x:c r="AU484" s="25"/>
+      <x:c r="AV484" s="22"/>
+      <x:c r="AW484" s="22"/>
+      <x:c r="AX484" s="22"/>
+      <x:c r="AY484" s="22"/>
+    </x:row>
+    <x:row r="485">
+      <x:c r="AN485" s="23"/>
+      <x:c r="AO485" s="22"/>
+      <x:c r="AP485" s="22"/>
+      <x:c r="AQ485" s="24"/>
+      <x:c r="AR485" s="24"/>
+      <x:c r="AS485" s="22"/>
+      <x:c r="AT485" s="25"/>
+      <x:c r="AU485" s="25"/>
+      <x:c r="AV485" s="22"/>
+      <x:c r="AW485" s="22"/>
+      <x:c r="AX485" s="22"/>
+      <x:c r="AY485" s="22"/>
+    </x:row>
+    <x:row r="486">
+      <x:c r="AN486" s="23"/>
+      <x:c r="AO486" s="22"/>
+      <x:c r="AP486" s="22"/>
+      <x:c r="AQ486" s="24"/>
+      <x:c r="AR486" s="24"/>
+      <x:c r="AS486" s="22"/>
+      <x:c r="AT486" s="25"/>
+      <x:c r="AU486" s="25"/>
+      <x:c r="AV486" s="22"/>
+      <x:c r="AW486" s="22"/>
+      <x:c r="AX486" s="22"/>
+      <x:c r="AY486" s="22"/>
+    </x:row>
+    <x:row r="487">
+      <x:c r="AN487" s="23"/>
+      <x:c r="AO487" s="22"/>
+      <x:c r="AP487" s="22"/>
+      <x:c r="AQ487" s="24"/>
+      <x:c r="AR487" s="24"/>
+      <x:c r="AS487" s="22"/>
+      <x:c r="AT487" s="25"/>
+      <x:c r="AU487" s="25"/>
+      <x:c r="AV487" s="22"/>
+      <x:c r="AW487" s="22"/>
+      <x:c r="AX487" s="22"/>
+      <x:c r="AY487" s="22"/>
+    </x:row>
+    <x:row r="488">
+      <x:c r="AN488" s="23"/>
+      <x:c r="AO488" s="22"/>
+      <x:c r="AP488" s="22"/>
+      <x:c r="AQ488" s="24"/>
+      <x:c r="AR488" s="24"/>
+      <x:c r="AS488" s="22"/>
+      <x:c r="AT488" s="25"/>
+      <x:c r="AU488" s="25"/>
+      <x:c r="AV488" s="22"/>
+      <x:c r="AW488" s="22"/>
+      <x:c r="AX488" s="22"/>
+      <x:c r="AY488" s="22"/>
+    </x:row>
+    <x:row r="489">
+      <x:c r="AN489" s="23"/>
+      <x:c r="AO489" s="22"/>
+      <x:c r="AP489" s="22"/>
+      <x:c r="AQ489" s="24"/>
+      <x:c r="AR489" s="24"/>
+      <x:c r="AS489" s="22"/>
+      <x:c r="AT489" s="25"/>
+      <x:c r="AU489" s="25"/>
+      <x:c r="AV489" s="22"/>
+      <x:c r="AW489" s="22"/>
+      <x:c r="AX489" s="22"/>
+      <x:c r="AY489" s="22"/>
+    </x:row>
+    <x:row r="490">
+      <x:c r="AN490" s="23"/>
+      <x:c r="AO490" s="22"/>
+      <x:c r="AP490" s="22"/>
+      <x:c r="AQ490" s="24"/>
+      <x:c r="AR490" s="24"/>
+      <x:c r="AS490" s="22"/>
+      <x:c r="AT490" s="25"/>
+      <x:c r="AU490" s="25"/>
+      <x:c r="AV490" s="22"/>
+      <x:c r="AW490" s="22"/>
+      <x:c r="AX490" s="22"/>
+      <x:c r="AY490" s="22"/>
+    </x:row>
+    <x:row r="491">
+      <x:c r="AN491" s="23"/>
+      <x:c r="AO491" s="22"/>
+      <x:c r="AP491" s="22"/>
+      <x:c r="AQ491" s="24"/>
+      <x:c r="AR491" s="24"/>
+      <x:c r="AS491" s="22"/>
+      <x:c r="AT491" s="25"/>
+      <x:c r="AU491" s="25"/>
+      <x:c r="AV491" s="22"/>
+      <x:c r="AW491" s="22"/>
+      <x:c r="AX491" s="22"/>
+      <x:c r="AY491" s="22"/>
+    </x:row>
+    <x:row r="492">
+      <x:c r="AN492" s="23"/>
+      <x:c r="AO492" s="22"/>
+      <x:c r="AP492" s="22"/>
+      <x:c r="AQ492" s="24"/>
+      <x:c r="AR492" s="24"/>
+      <x:c r="AS492" s="22"/>
+      <x:c r="AT492" s="25"/>
+      <x:c r="AU492" s="25"/>
+      <x:c r="AV492" s="22"/>
+      <x:c r="AW492" s="22"/>
+      <x:c r="AX492" s="22"/>
+      <x:c r="AY492" s="22"/>
+    </x:row>
+    <x:row r="493">
+      <x:c r="AN493" s="23"/>
+      <x:c r="AO493" s="22"/>
+      <x:c r="AP493" s="22"/>
+      <x:c r="AQ493" s="24"/>
+      <x:c r="AR493" s="24"/>
+      <x:c r="AS493" s="22"/>
+      <x:c r="AT493" s="25"/>
+      <x:c r="AU493" s="25"/>
+      <x:c r="AV493" s="22"/>
+      <x:c r="AW493" s="22"/>
+      <x:c r="AX493" s="22"/>
+      <x:c r="AY493" s="22"/>
+    </x:row>
+    <x:row r="494">
+      <x:c r="AN494" s="23"/>
+      <x:c r="AO494" s="22"/>
+      <x:c r="AP494" s="22"/>
+      <x:c r="AQ494" s="24"/>
+      <x:c r="AR494" s="24"/>
+      <x:c r="AS494" s="22"/>
+      <x:c r="AT494" s="25"/>
+      <x:c r="AU494" s="25"/>
+      <x:c r="AV494" s="22"/>
+      <x:c r="AW494" s="22"/>
+      <x:c r="AX494" s="22"/>
+      <x:c r="AY494" s="22"/>
+    </x:row>
+    <x:row r="495">
+      <x:c r="AN495" s="23"/>
+      <x:c r="AO495" s="22"/>
+      <x:c r="AP495" s="22"/>
+      <x:c r="AQ495" s="24"/>
+      <x:c r="AR495" s="24"/>
+      <x:c r="AS495" s="22"/>
+      <x:c r="AT495" s="25"/>
+      <x:c r="AU495" s="25"/>
+      <x:c r="AV495" s="22"/>
+      <x:c r="AW495" s="22"/>
+      <x:c r="AX495" s="22"/>
+      <x:c r="AY495" s="22"/>
+    </x:row>
+    <x:row r="496">
+      <x:c r="AN496" s="23"/>
+      <x:c r="AO496" s="22"/>
+      <x:c r="AP496" s="22"/>
+      <x:c r="AQ496" s="24"/>
+      <x:c r="AR496" s="24"/>
+      <x:c r="AS496" s="22"/>
+      <x:c r="AT496" s="25"/>
+      <x:c r="AU496" s="25"/>
+      <x:c r="AV496" s="22"/>
+      <x:c r="AW496" s="22"/>
+      <x:c r="AX496" s="22"/>
+      <x:c r="AY496" s="22"/>
+    </x:row>
+    <x:row r="497">
+      <x:c r="AN497" s="23"/>
+      <x:c r="AO497" s="22"/>
+      <x:c r="AP497" s="22"/>
+      <x:c r="AQ497" s="24"/>
+      <x:c r="AR497" s="24"/>
+      <x:c r="AS497" s="22"/>
+      <x:c r="AT497" s="25"/>
+      <x:c r="AU497" s="25"/>
+      <x:c r="AV497" s="22"/>
+      <x:c r="AW497" s="22"/>
+      <x:c r="AX497" s="22"/>
+      <x:c r="AY497" s="22"/>
+    </x:row>
+    <x:row r="498">
+      <x:c r="AN498" s="23"/>
+      <x:c r="AO498" s="22"/>
+      <x:c r="AP498" s="22"/>
+      <x:c r="AQ498" s="24"/>
+      <x:c r="AR498" s="24"/>
+      <x:c r="AS498" s="22"/>
+      <x:c r="AT498" s="25"/>
+      <x:c r="AU498" s="25"/>
+      <x:c r="AV498" s="22"/>
+      <x:c r="AW498" s="22"/>
+      <x:c r="AX498" s="22"/>
+      <x:c r="AY498" s="22"/>
+    </x:row>
+    <x:row r="499">
+      <x:c r="AN499" s="23"/>
+      <x:c r="AO499" s="22"/>
+      <x:c r="AP499" s="22"/>
+      <x:c r="AQ499" s="24"/>
+      <x:c r="AR499" s="24"/>
+      <x:c r="AS499" s="22"/>
+      <x:c r="AT499" s="25"/>
+      <x:c r="AU499" s="25"/>
+      <x:c r="AV499" s="22"/>
+      <x:c r="AW499" s="22"/>
+      <x:c r="AX499" s="22"/>
+      <x:c r="AY499" s="22"/>
+    </x:row>
+    <x:row r="500">
+      <x:c r="AN500" s="23"/>
+      <x:c r="AO500" s="22"/>
+      <x:c r="AP500" s="22"/>
+      <x:c r="AQ500" s="24"/>
+      <x:c r="AR500" s="24"/>
+      <x:c r="AS500" s="22"/>
+      <x:c r="AT500" s="25"/>
+      <x:c r="AU500" s="25"/>
+      <x:c r="AV500" s="22"/>
+      <x:c r="AW500" s="22"/>
+      <x:c r="AX500" s="22"/>
+      <x:c r="AY500" s="22"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="5">
+  <x:dataValidations count="9">
     <x:dataValidation type="list" sqref="K2:K200">
       <x:formula1>Listes!$A$2:$A$8</x:formula1>
     </x:dataValidation>
@@ -8806,10 +15501,22 @@
     <x:dataValidation type="list" sqref="AM2:AM200">
       <x:formula1>Listes!$E$2:$E$3</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="AS2:AS500">
+      <x:formula1>Listes!$F$2:$F$3</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="AV2:AV500">
+      <x:formula1>Listes!$G$2:$G$5</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="AW2:AW500">
+      <x:formula1>Listes!$H$2:$H$5</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="AX2:AX500">
+      <x:formula1>Listes!$I$2:$I$4</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3c630e576a34bdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43df4708360748e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8823,6 +15530,10 @@
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -8841,6 +15552,18 @@
       <x:c r="E1" s="3" t="str">
         <x:v>Publie</x:v>
       </x:c>
+      <x:c r="F1" s="21" t="str">
+        <x:v>Lieu_incertitude</x:v>
+      </x:c>
+      <x:c r="G1" s="21" t="str">
+        <x:v>Interet_patrimonial</x:v>
+      </x:c>
+      <x:c r="H1" s="21" t="str">
+        <x:v>Completude</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str">
+        <x:v>Illustre</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -8858,6 +15581,18 @@
       <x:c r="E2" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Courant</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Complet</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -8875,6 +15610,18 @@
       <x:c r="E3" t="str">
         <x:v>Non</x:v>
       </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>À signaler</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Incomplet</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Non</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -8889,6 +15636,16 @@
       <x:c r="D4" t="str">
         <x:v>faible</x:v>
       </x:c>
+      <x:c r="F4"/>
+      <x:c r="G4" t="str">
+        <x:v>Remarquable</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>À vérifier</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -8900,6 +15657,14 @@
       <x:c r="C5" t="str">
         <x:v>manuelle</x:v>
       </x:c>
+      <x:c r="F5"/>
+      <x:c r="G5" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -9093,7 +15858,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160ef18014174ccc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37163535b27f4145"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9149,7 +15914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5fa9d33d7b0478c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab36e1af7f934fe8"/>
   </x:tableParts>
 </x:worksheet>
 </file>